--- a/GeneralizationRules100K.xlsx
+++ b/GeneralizationRules100K.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Intersourcing\Malyasia\Gen_Carto\Gen_Carto\ArcgisPro_GenCarto\GenCarto_Dev\Share_100k\GenCarto100K_2026-01-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Intersourcing\Malyasia\Gen_Carto\Gen_Carto\ArcgisPro_GenCarto\GenCarto_Dev\share_dev_100K_main\Dev_Gencarto_100K\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE4636D-ED63-4C4C-99BD-F0714EAA6E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E4BCEA-2744-48A9-B454-12E6B12D5690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="16" r:id="rId1"/>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9352" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9533" uniqueCount="1148">
   <si>
     <t>Please read the following instructions carefully</t>
   </si>
@@ -3969,13 +3969,265 @@
     <t>Reference Scale 100000</t>
   </si>
   <si>
-    <t>Transport_Symbology_Filed</t>
-  </si>
-  <si>
     <t>Transport_Symbology_Road_Class</t>
   </si>
   <si>
     <t>RCS</t>
+  </si>
+  <si>
+    <t>Transport_short_delete_dangles_sql</t>
+  </si>
+  <si>
+    <t>Transport_Symbology_Field</t>
+  </si>
+  <si>
+    <t>Transportation_invisible_field</t>
+  </si>
+  <si>
+    <t>Transportation_hierarchy_field</t>
+  </si>
+  <si>
+    <t>Transportation_backlane_invisible_field</t>
+  </si>
+  <si>
+    <t>RoadCasing</t>
+  </si>
+  <si>
+    <t>Residential_Building_A</t>
+  </si>
+  <si>
+    <t>Residential_Building_P</t>
+  </si>
+  <si>
+    <t>Industrial_Building_A</t>
+  </si>
+  <si>
+    <t>Industrial_Building_P</t>
+  </si>
+  <si>
+    <t>Educational_Building_A</t>
+  </si>
+  <si>
+    <t>Educational_Building_P</t>
+  </si>
+  <si>
+    <t>Building_Of_Worship_A</t>
+  </si>
+  <si>
+    <t>Swimming_Pool_A</t>
+  </si>
+  <si>
+    <t>Rail_Terminal_Railway_Station_A</t>
+  </si>
+  <si>
+    <t>Rail_Terminal_Railway_Station_P</t>
+  </si>
+  <si>
+    <t>Town_Built_up_A</t>
+  </si>
+  <si>
+    <t>Historical_Site_A</t>
+  </si>
+  <si>
+    <t>Generalised_Buildings_A</t>
+  </si>
+  <si>
+    <t>State_Coverage_L</t>
+  </si>
+  <si>
+    <t>Local_Authority_Area_A</t>
+  </si>
+  <si>
+    <t>Mine_A</t>
+  </si>
+  <si>
+    <t>Quarry_Pit_A</t>
+  </si>
+  <si>
+    <t>Mud_Volcano_A</t>
+  </si>
+  <si>
+    <t>GF3100_Mud_Volcano_A</t>
+  </si>
+  <si>
+    <t>Rock_Outcrop_A</t>
+  </si>
+  <si>
+    <t>Rock_Boulders_A</t>
+  </si>
+  <si>
+    <t>Geohazard_Site_A</t>
+  </si>
+  <si>
+    <t>Landslide_Site_A</t>
+  </si>
+  <si>
+    <t>Shoreline_L</t>
+  </si>
+  <si>
+    <t>Jetty_Pier_P</t>
+  </si>
+  <si>
+    <t>Log_Pond_A</t>
+  </si>
+  <si>
+    <t>River_Bank_L</t>
+  </si>
+  <si>
+    <t>River_Coverage_A</t>
+  </si>
+  <si>
+    <t>Under_Ground_River_L</t>
+  </si>
+  <si>
+    <t>Natural_Spring_A</t>
+  </si>
+  <si>
+    <t>HH0130_Natural_Spring_A</t>
+  </si>
+  <si>
+    <t>Natural_Spring_P</t>
+  </si>
+  <si>
+    <t>Irrigation_Canal_L</t>
+  </si>
+  <si>
+    <t>Irrigation_Canal_Edge_L</t>
+  </si>
+  <si>
+    <t>Irrigation_Canal_Coverage_A</t>
+  </si>
+  <si>
+    <t>Tidal_Gate_P</t>
+  </si>
+  <si>
+    <t>Tidal_Gate_River_Bank_NearT2</t>
+  </si>
+  <si>
+    <t>HJ0070_Tidal_Gate_River_Bank_NearT2</t>
+  </si>
+  <si>
+    <t>Sea_Coverage_A</t>
+  </si>
+  <si>
+    <t>Inland_Island_A</t>
+  </si>
+  <si>
+    <t>Coastal_Island_A</t>
+  </si>
+  <si>
+    <t>Offshore_Island_A</t>
+  </si>
+  <si>
+    <t>Water_Flow_P</t>
+  </si>
+  <si>
+    <t>Water_flow_River_Bank_Near</t>
+  </si>
+  <si>
+    <t>HM0030_Water_flow_River_Bank_Near</t>
+  </si>
+  <si>
+    <t>Contour_Line_L</t>
+  </si>
+  <si>
+    <t>Rail_Line_L</t>
+  </si>
+  <si>
+    <t>Road_Surface_Physical_A</t>
+  </si>
+  <si>
+    <t>Toll_Plaza_A</t>
+  </si>
+  <si>
+    <t>Toll_Plaza_P</t>
+  </si>
+  <si>
+    <t>Kilometer_Post_P</t>
+  </si>
+  <si>
+    <t>Track_Surface_Physical_A</t>
+  </si>
+  <si>
+    <t>Electrical_Station_A</t>
+  </si>
+  <si>
+    <t>U_Electrical_Station_A</t>
+  </si>
+  <si>
+    <t>Power_Station_A</t>
+  </si>
+  <si>
+    <t>Sewage_Treatment_Plant_A</t>
+  </si>
+  <si>
+    <t>Mix_Traditional_Farming_A</t>
+  </si>
+  <si>
+    <t>Cocoa_A</t>
+  </si>
+  <si>
+    <t>Coconut_A</t>
+  </si>
+  <si>
+    <t>Coffee_A</t>
+  </si>
+  <si>
+    <t>Oil_Palm_A</t>
+  </si>
+  <si>
+    <t>Tea_A</t>
+  </si>
+  <si>
+    <t>Rumbia_A</t>
+  </si>
+  <si>
+    <t>Mixed_Fruit_Crops_A</t>
+  </si>
+  <si>
+    <t>Paddy_A</t>
+  </si>
+  <si>
+    <t>Sundry_Tree_A</t>
+  </si>
+  <si>
+    <t>Sundry_Non_Tree_A</t>
+  </si>
+  <si>
+    <t>Forest_A</t>
+  </si>
+  <si>
+    <t>Rubber_Trees_A</t>
+  </si>
+  <si>
+    <t>Bamboo_A</t>
+  </si>
+  <si>
+    <t>Scrub_Shrub_A</t>
+  </si>
+  <si>
+    <t>Riung_A</t>
+  </si>
+  <si>
+    <t>Global_Navigation_Satellite_System_Station_P</t>
+  </si>
+  <si>
+    <t>Trigonometry_Station_P</t>
+  </si>
+  <si>
+    <t>Height_Point_P</t>
+  </si>
+  <si>
+    <t>Base_Point_P</t>
+  </si>
+  <si>
+    <t>International_Boundary_Marker_P</t>
+  </si>
+  <si>
+    <t>State_Boundary_Marker_P</t>
+  </si>
+  <si>
+    <t>Cliff_Precipitous_L</t>
   </si>
 </sst>
 </file>
@@ -4207,7 +4459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4293,6 +4545,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4631,10 +4887,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="49"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
@@ -8089,8 +8345,8 @@
       <c r="G77" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="H77" s="49"/>
-      <c r="I77" s="48"/>
+      <c r="H77" s="51"/>
+      <c r="I77" s="50"/>
       <c r="J77" s="25" t="s">
         <v>697</v>
       </c>
@@ -8128,8 +8384,8 @@
       <c r="G78" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="H78" s="49"/>
-      <c r="I78" s="48"/>
+      <c r="H78" s="51"/>
+      <c r="I78" s="50"/>
       <c r="J78" s="25"/>
       <c r="K78" s="25" t="s">
         <v>700</v>
@@ -8161,8 +8417,8 @@
       <c r="E79" s="25"/>
       <c r="F79" s="25"/>
       <c r="G79" s="25"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
       <c r="J79" s="25"/>
       <c r="K79" s="25" t="s">
         <v>701</v>
@@ -8188,8 +8444,8 @@
       <c r="E80" s="25"/>
       <c r="F80" s="25"/>
       <c r="G80" s="25"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
       <c r="J80" s="25"/>
       <c r="K80" s="25"/>
       <c r="L80" s="25"/>
@@ -8211,8 +8467,8 @@
       <c r="E81" s="25"/>
       <c r="F81" s="25"/>
       <c r="G81" s="25"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
       <c r="J81" s="25"/>
       <c r="K81" s="25"/>
       <c r="L81" s="25"/>
@@ -8236,8 +8492,8 @@
       <c r="E82" s="25"/>
       <c r="F82" s="25"/>
       <c r="G82" s="25"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
       <c r="J82" s="25"/>
       <c r="K82" s="25"/>
       <c r="L82" s="25"/>
@@ -8263,8 +8519,8 @@
       <c r="E83" s="25"/>
       <c r="F83" s="25"/>
       <c r="G83" s="25"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="50"/>
       <c r="J83" s="25"/>
       <c r="K83" s="25"/>
       <c r="L83" s="25"/>
@@ -8290,8 +8546,8 @@
       <c r="E84" s="25"/>
       <c r="F84" s="25"/>
       <c r="G84" s="25"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="50"/>
       <c r="J84" s="25"/>
       <c r="K84" s="25"/>
       <c r="L84" s="25"/>
@@ -8317,8 +8573,8 @@
       <c r="E85" s="25"/>
       <c r="F85" s="25"/>
       <c r="G85" s="25"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
       <c r="J85" s="25"/>
       <c r="K85" s="25"/>
       <c r="L85" s="25"/>
@@ -8344,8 +8600,8 @@
       <c r="E86" s="25"/>
       <c r="F86" s="25"/>
       <c r="G86" s="25"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="50"/>
       <c r="J86" s="25"/>
       <c r="K86" s="25"/>
       <c r="L86" s="25"/>
@@ -8371,8 +8627,8 @@
       <c r="E87" s="25"/>
       <c r="F87" s="25"/>
       <c r="G87" s="25"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="50"/>
       <c r="J87" s="25"/>
       <c r="K87" s="25"/>
       <c r="L87" s="25"/>
@@ -8398,8 +8654,8 @@
       <c r="E88" s="25"/>
       <c r="F88" s="25"/>
       <c r="G88" s="25"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="H88" s="50"/>
+      <c r="I88" s="50"/>
       <c r="J88" s="25"/>
       <c r="K88" s="25"/>
       <c r="L88" s="25"/>
@@ -8425,8 +8681,8 @@
       <c r="E89" s="25"/>
       <c r="F89" s="25"/>
       <c r="G89" s="25"/>
-      <c r="H89" s="48"/>
-      <c r="I89" s="48"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="50"/>
       <c r="J89" s="25"/>
       <c r="K89" s="25"/>
       <c r="L89" s="25"/>
@@ -8452,8 +8708,8 @@
       <c r="E90" s="25"/>
       <c r="F90" s="25"/>
       <c r="G90" s="25"/>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
+      <c r="H90" s="50"/>
+      <c r="I90" s="50"/>
       <c r="J90" s="25"/>
       <c r="K90" s="25"/>
       <c r="L90" s="25"/>
@@ -8479,8 +8735,8 @@
       <c r="E91" s="25"/>
       <c r="F91" s="25"/>
       <c r="G91" s="25"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="50"/>
       <c r="J91" s="25"/>
       <c r="K91" s="25"/>
       <c r="L91" s="25"/>
@@ -8506,8 +8762,8 @@
       <c r="E92" s="25"/>
       <c r="F92" s="25"/>
       <c r="G92" s="25"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="50"/>
       <c r="J92" s="25"/>
       <c r="K92" s="25"/>
       <c r="L92" s="25"/>
@@ -8533,8 +8789,8 @@
       <c r="E93" s="25"/>
       <c r="F93" s="25"/>
       <c r="G93" s="25"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="50"/>
       <c r="J93" s="25"/>
       <c r="K93" s="25"/>
       <c r="L93" s="25"/>
@@ -8560,8 +8816,8 @@
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="25"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
+      <c r="H94" s="50"/>
+      <c r="I94" s="50"/>
       <c r="J94" s="25"/>
       <c r="K94" s="25"/>
       <c r="L94" s="25"/>
@@ -8587,8 +8843,8 @@
       <c r="E95" s="25"/>
       <c r="F95" s="25"/>
       <c r="G95" s="25"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
+      <c r="H95" s="50"/>
+      <c r="I95" s="50"/>
       <c r="J95" s="25"/>
       <c r="K95" s="25"/>
       <c r="L95" s="25"/>
@@ -8614,8 +8870,8 @@
       <c r="E96" s="25"/>
       <c r="F96" s="25"/>
       <c r="G96" s="25"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="50"/>
       <c r="J96" s="25"/>
       <c r="K96" s="25"/>
       <c r="L96" s="25"/>
@@ -8641,8 +8897,8 @@
       <c r="E97" s="25"/>
       <c r="F97" s="25"/>
       <c r="G97" s="25"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
+      <c r="H97" s="50"/>
+      <c r="I97" s="50"/>
       <c r="J97" s="25"/>
       <c r="K97" s="25"/>
       <c r="L97" s="25"/>
@@ -8668,8 +8924,8 @@
       <c r="E98" s="25"/>
       <c r="F98" s="25"/>
       <c r="G98" s="25"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
+      <c r="H98" s="50"/>
+      <c r="I98" s="50"/>
       <c r="J98" s="25"/>
       <c r="K98" s="25"/>
       <c r="L98" s="25"/>
@@ -8695,8 +8951,8 @@
       <c r="E99" s="25"/>
       <c r="F99" s="25"/>
       <c r="G99" s="25"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="50"/>
       <c r="J99" s="25"/>
       <c r="K99" s="25"/>
       <c r="L99" s="25"/>
@@ -8722,8 +8978,8 @@
       <c r="E100" s="25"/>
       <c r="F100" s="25"/>
       <c r="G100" s="25"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
       <c r="J100" s="25"/>
       <c r="K100" s="25"/>
       <c r="L100" s="25"/>
@@ -8749,8 +9005,8 @@
       <c r="E101" s="25"/>
       <c r="F101" s="25"/>
       <c r="G101" s="25"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
       <c r="J101" s="25"/>
       <c r="K101" s="25"/>
       <c r="L101" s="25"/>
@@ -8776,8 +9032,8 @@
       <c r="E102" s="25"/>
       <c r="F102" s="25"/>
       <c r="G102" s="25"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
+      <c r="H102" s="50"/>
+      <c r="I102" s="50"/>
       <c r="J102" s="25"/>
       <c r="K102" s="25"/>
       <c r="L102" s="25"/>
@@ -8803,8 +9059,8 @@
       <c r="E103" s="25"/>
       <c r="F103" s="25"/>
       <c r="G103" s="25"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
+      <c r="H103" s="50"/>
+      <c r="I103" s="50"/>
       <c r="J103" s="25"/>
       <c r="K103" s="25"/>
       <c r="L103" s="25"/>
@@ -8830,8 +9086,8 @@
       <c r="E104" s="25"/>
       <c r="F104" s="25"/>
       <c r="G104" s="25"/>
-      <c r="H104" s="48"/>
-      <c r="I104" s="48"/>
+      <c r="H104" s="50"/>
+      <c r="I104" s="50"/>
       <c r="J104" s="25"/>
       <c r="K104" s="25"/>
       <c r="L104" s="25"/>
@@ -8857,8 +9113,8 @@
       <c r="E105" s="25"/>
       <c r="F105" s="25"/>
       <c r="G105" s="25"/>
-      <c r="H105" s="48"/>
-      <c r="I105" s="48"/>
+      <c r="H105" s="50"/>
+      <c r="I105" s="50"/>
       <c r="J105" s="25"/>
       <c r="K105" s="25"/>
       <c r="L105" s="25"/>
@@ -8884,8 +9140,8 @@
       <c r="E106" s="25"/>
       <c r="F106" s="25"/>
       <c r="G106" s="25"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="48"/>
+      <c r="H106" s="50"/>
+      <c r="I106" s="50"/>
       <c r="J106" s="25"/>
       <c r="K106" s="25"/>
       <c r="L106" s="25"/>
@@ -8911,8 +9167,8 @@
       <c r="E107" s="25"/>
       <c r="F107" s="25"/>
       <c r="G107" s="25"/>
-      <c r="H107" s="48"/>
-      <c r="I107" s="48"/>
+      <c r="H107" s="50"/>
+      <c r="I107" s="50"/>
       <c r="J107" s="25"/>
       <c r="K107" s="25"/>
       <c r="L107" s="25"/>
@@ -8938,8 +9194,8 @@
       <c r="E108" s="25"/>
       <c r="F108" s="25"/>
       <c r="G108" s="25"/>
-      <c r="H108" s="48"/>
-      <c r="I108" s="48"/>
+      <c r="H108" s="50"/>
+      <c r="I108" s="50"/>
       <c r="J108" s="25"/>
       <c r="K108" s="25"/>
       <c r="L108" s="25"/>
@@ -8965,8 +9221,8 @@
       <c r="E109" s="25"/>
       <c r="F109" s="25"/>
       <c r="G109" s="25"/>
-      <c r="H109" s="48"/>
-      <c r="I109" s="48"/>
+      <c r="H109" s="50"/>
+      <c r="I109" s="50"/>
       <c r="J109" s="25"/>
       <c r="K109" s="25"/>
       <c r="L109" s="25"/>
@@ -8992,8 +9248,8 @@
       <c r="E110" s="25"/>
       <c r="F110" s="25"/>
       <c r="G110" s="25"/>
-      <c r="H110" s="48"/>
-      <c r="I110" s="48"/>
+      <c r="H110" s="50"/>
+      <c r="I110" s="50"/>
       <c r="J110" s="25"/>
       <c r="K110" s="25"/>
       <c r="L110" s="25"/>
@@ -9019,8 +9275,8 @@
       <c r="E111" s="25"/>
       <c r="F111" s="25"/>
       <c r="G111" s="25"/>
-      <c r="H111" s="48"/>
-      <c r="I111" s="48"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="50"/>
       <c r="J111" s="25"/>
       <c r="K111" s="25"/>
       <c r="L111" s="25"/>
@@ -9046,8 +9302,8 @@
       <c r="E112" s="25"/>
       <c r="F112" s="25"/>
       <c r="G112" s="25"/>
-      <c r="H112" s="48"/>
-      <c r="I112" s="48"/>
+      <c r="H112" s="50"/>
+      <c r="I112" s="50"/>
       <c r="J112" s="25"/>
       <c r="K112" s="25"/>
       <c r="L112" s="25"/>
@@ -9073,8 +9329,8 @@
       <c r="E113" s="25"/>
       <c r="F113" s="25"/>
       <c r="G113" s="25"/>
-      <c r="H113" s="48"/>
-      <c r="I113" s="48"/>
+      <c r="H113" s="50"/>
+      <c r="I113" s="50"/>
       <c r="J113" s="25"/>
       <c r="K113" s="25"/>
       <c r="L113" s="25"/>
@@ -9100,8 +9356,8 @@
       <c r="E114" s="25"/>
       <c r="F114" s="25"/>
       <c r="G114" s="25"/>
-      <c r="H114" s="48"/>
-      <c r="I114" s="48"/>
+      <c r="H114" s="50"/>
+      <c r="I114" s="50"/>
       <c r="J114" s="25"/>
       <c r="K114" s="25"/>
       <c r="L114" s="25"/>
@@ -9127,8 +9383,8 @@
       <c r="E115" s="25"/>
       <c r="F115" s="25"/>
       <c r="G115" s="25"/>
-      <c r="H115" s="48"/>
-      <c r="I115" s="48"/>
+      <c r="H115" s="50"/>
+      <c r="I115" s="50"/>
       <c r="J115" s="25"/>
       <c r="K115" s="25"/>
       <c r="L115" s="25"/>
@@ -9154,8 +9410,8 @@
       <c r="E116" s="25"/>
       <c r="F116" s="25"/>
       <c r="G116" s="25"/>
-      <c r="H116" s="48"/>
-      <c r="I116" s="48"/>
+      <c r="H116" s="50"/>
+      <c r="I116" s="50"/>
       <c r="J116" s="25"/>
       <c r="K116" s="25"/>
       <c r="L116" s="25"/>
@@ -9181,8 +9437,8 @@
       <c r="E117" s="25"/>
       <c r="F117" s="25"/>
       <c r="G117" s="25"/>
-      <c r="H117" s="48"/>
-      <c r="I117" s="48"/>
+      <c r="H117" s="50"/>
+      <c r="I117" s="50"/>
       <c r="J117" s="25"/>
       <c r="K117" s="25"/>
       <c r="L117" s="25"/>
@@ -9208,8 +9464,8 @@
       <c r="E118" s="25"/>
       <c r="F118" s="25"/>
       <c r="G118" s="25"/>
-      <c r="H118" s="48"/>
-      <c r="I118" s="48"/>
+      <c r="H118" s="50"/>
+      <c r="I118" s="50"/>
       <c r="J118" s="25"/>
       <c r="K118" s="25"/>
       <c r="L118" s="25"/>
@@ -9235,8 +9491,8 @@
       <c r="E119" s="25"/>
       <c r="F119" s="25"/>
       <c r="G119" s="25"/>
-      <c r="H119" s="48"/>
-      <c r="I119" s="48"/>
+      <c r="H119" s="50"/>
+      <c r="I119" s="50"/>
       <c r="J119" s="25"/>
       <c r="K119" s="25"/>
       <c r="L119" s="25"/>
@@ -9264,8 +9520,8 @@
       <c r="E120" s="25"/>
       <c r="F120" s="25"/>
       <c r="G120" s="25"/>
-      <c r="H120" s="48"/>
-      <c r="I120" s="48"/>
+      <c r="H120" s="50"/>
+      <c r="I120" s="50"/>
       <c r="J120" s="25"/>
       <c r="K120" s="25"/>
       <c r="L120" s="25"/>
@@ -9291,8 +9547,8 @@
       <c r="E121" s="25"/>
       <c r="F121" s="25"/>
       <c r="G121" s="25"/>
-      <c r="H121" s="48"/>
-      <c r="I121" s="48"/>
+      <c r="H121" s="50"/>
+      <c r="I121" s="50"/>
       <c r="J121" s="25"/>
       <c r="K121" s="25"/>
       <c r="L121" s="25"/>
@@ -9318,8 +9574,8 @@
       <c r="E122" s="25"/>
       <c r="F122" s="25"/>
       <c r="G122" s="25"/>
-      <c r="H122" s="48"/>
-      <c r="I122" s="48"/>
+      <c r="H122" s="50"/>
+      <c r="I122" s="50"/>
       <c r="J122" s="25"/>
       <c r="K122" s="25"/>
       <c r="L122" s="25"/>
@@ -9345,8 +9601,8 @@
       <c r="E123" s="25"/>
       <c r="F123" s="25"/>
       <c r="G123" s="25"/>
-      <c r="H123" s="48"/>
-      <c r="I123" s="48"/>
+      <c r="H123" s="50"/>
+      <c r="I123" s="50"/>
       <c r="J123" s="25"/>
       <c r="K123" s="25"/>
       <c r="L123" s="25"/>
@@ -9372,8 +9628,8 @@
       <c r="E124" s="25"/>
       <c r="F124" s="25"/>
       <c r="G124" s="25"/>
-      <c r="H124" s="48"/>
-      <c r="I124" s="48"/>
+      <c r="H124" s="50"/>
+      <c r="I124" s="50"/>
       <c r="J124" s="25"/>
       <c r="K124" s="25"/>
       <c r="L124" s="25"/>
@@ -9399,8 +9655,8 @@
       <c r="E125" s="25"/>
       <c r="F125" s="25"/>
       <c r="G125" s="25"/>
-      <c r="H125" s="48"/>
-      <c r="I125" s="48"/>
+      <c r="H125" s="50"/>
+      <c r="I125" s="50"/>
       <c r="J125" s="25"/>
       <c r="K125" s="25"/>
       <c r="L125" s="25"/>
@@ -9426,8 +9682,8 @@
       <c r="E126" s="25"/>
       <c r="F126" s="25"/>
       <c r="G126" s="25"/>
-      <c r="H126" s="48"/>
-      <c r="I126" s="48"/>
+      <c r="H126" s="50"/>
+      <c r="I126" s="50"/>
       <c r="J126" s="25"/>
       <c r="K126" s="25"/>
       <c r="L126" s="25"/>
@@ -9453,8 +9709,8 @@
       <c r="E127" s="25"/>
       <c r="F127" s="25"/>
       <c r="G127" s="25"/>
-      <c r="H127" s="48"/>
-      <c r="I127" s="48"/>
+      <c r="H127" s="50"/>
+      <c r="I127" s="50"/>
       <c r="J127" s="25"/>
       <c r="K127" s="25"/>
       <c r="L127" s="25"/>
@@ -9480,8 +9736,8 @@
       <c r="E128" s="25"/>
       <c r="F128" s="25"/>
       <c r="G128" s="25"/>
-      <c r="H128" s="48"/>
-      <c r="I128" s="48"/>
+      <c r="H128" s="50"/>
+      <c r="I128" s="50"/>
       <c r="J128" s="25"/>
       <c r="K128" s="25"/>
       <c r="L128" s="25"/>
@@ -9507,8 +9763,8 @@
       <c r="E129" s="25"/>
       <c r="F129" s="25"/>
       <c r="G129" s="25"/>
-      <c r="H129" s="48"/>
-      <c r="I129" s="48"/>
+      <c r="H129" s="50"/>
+      <c r="I129" s="50"/>
       <c r="J129" s="25"/>
       <c r="K129" s="25"/>
       <c r="L129" s="25"/>
@@ -9534,8 +9790,8 @@
       <c r="E130" s="25"/>
       <c r="F130" s="25"/>
       <c r="G130" s="25"/>
-      <c r="H130" s="48"/>
-      <c r="I130" s="48"/>
+      <c r="H130" s="50"/>
+      <c r="I130" s="50"/>
       <c r="J130" s="25"/>
       <c r="K130" s="25"/>
       <c r="L130" s="25"/>
@@ -9561,8 +9817,8 @@
       <c r="E131" s="25"/>
       <c r="F131" s="25"/>
       <c r="G131" s="25"/>
-      <c r="H131" s="48"/>
-      <c r="I131" s="48"/>
+      <c r="H131" s="50"/>
+      <c r="I131" s="50"/>
       <c r="J131" s="25"/>
       <c r="K131" s="25"/>
       <c r="L131" s="25"/>
@@ -9588,8 +9844,8 @@
       <c r="E132" s="25"/>
       <c r="F132" s="25"/>
       <c r="G132" s="25"/>
-      <c r="H132" s="48"/>
-      <c r="I132" s="48"/>
+      <c r="H132" s="50"/>
+      <c r="I132" s="50"/>
       <c r="J132" s="25"/>
       <c r="K132" s="25"/>
       <c r="L132" s="25"/>
@@ -9615,8 +9871,8 @@
       <c r="E133" s="25"/>
       <c r="F133" s="25"/>
       <c r="G133" s="25"/>
-      <c r="H133" s="48"/>
-      <c r="I133" s="48"/>
+      <c r="H133" s="50"/>
+      <c r="I133" s="50"/>
       <c r="J133" s="25"/>
       <c r="K133" s="25"/>
       <c r="L133" s="25"/>
@@ -9642,8 +9898,8 @@
       <c r="E134" s="25"/>
       <c r="F134" s="25"/>
       <c r="G134" s="25"/>
-      <c r="H134" s="48"/>
-      <c r="I134" s="48"/>
+      <c r="H134" s="50"/>
+      <c r="I134" s="50"/>
       <c r="J134" s="25"/>
       <c r="K134" s="25"/>
       <c r="L134" s="25"/>
@@ -9669,8 +9925,8 @@
       <c r="E135" s="25"/>
       <c r="F135" s="25"/>
       <c r="G135" s="25"/>
-      <c r="H135" s="48"/>
-      <c r="I135" s="48"/>
+      <c r="H135" s="50"/>
+      <c r="I135" s="50"/>
       <c r="J135" s="25"/>
       <c r="K135" s="25"/>
       <c r="L135" s="25"/>
@@ -9696,8 +9952,8 @@
       <c r="E136" s="25"/>
       <c r="F136" s="25"/>
       <c r="G136" s="25"/>
-      <c r="H136" s="48"/>
-      <c r="I136" s="48"/>
+      <c r="H136" s="50"/>
+      <c r="I136" s="50"/>
       <c r="J136" s="25"/>
       <c r="K136" s="25"/>
       <c r="L136" s="25"/>
@@ -9723,8 +9979,8 @@
       <c r="E137" s="25"/>
       <c r="F137" s="25"/>
       <c r="G137" s="25"/>
-      <c r="H137" s="48"/>
-      <c r="I137" s="48"/>
+      <c r="H137" s="50"/>
+      <c r="I137" s="50"/>
       <c r="J137" s="25"/>
       <c r="K137" s="25"/>
       <c r="L137" s="25"/>
@@ -9750,8 +10006,8 @@
       <c r="E138" s="25"/>
       <c r="F138" s="25"/>
       <c r="G138" s="25"/>
-      <c r="H138" s="48"/>
-      <c r="I138" s="48"/>
+      <c r="H138" s="50"/>
+      <c r="I138" s="50"/>
       <c r="J138" s="25"/>
       <c r="K138" s="25"/>
       <c r="L138" s="25"/>
@@ -9777,8 +10033,8 @@
       <c r="E139" s="25"/>
       <c r="F139" s="25"/>
       <c r="G139" s="25"/>
-      <c r="H139" s="48"/>
-      <c r="I139" s="48"/>
+      <c r="H139" s="50"/>
+      <c r="I139" s="50"/>
       <c r="J139" s="25"/>
       <c r="K139" s="25"/>
       <c r="L139" s="25"/>
@@ -9804,8 +10060,8 @@
       <c r="E140" s="25"/>
       <c r="F140" s="25"/>
       <c r="G140" s="25"/>
-      <c r="H140" s="48"/>
-      <c r="I140" s="48"/>
+      <c r="H140" s="50"/>
+      <c r="I140" s="50"/>
       <c r="J140" s="25"/>
       <c r="K140" s="25"/>
       <c r="L140" s="25"/>
@@ -9831,8 +10087,8 @@
       <c r="E141" s="25"/>
       <c r="F141" s="25"/>
       <c r="G141" s="25"/>
-      <c r="H141" s="48"/>
-      <c r="I141" s="48"/>
+      <c r="H141" s="50"/>
+      <c r="I141" s="50"/>
       <c r="J141" s="25"/>
       <c r="K141" s="25"/>
       <c r="L141" s="25"/>
@@ -9858,8 +10114,8 @@
       <c r="E142" s="25"/>
       <c r="F142" s="25"/>
       <c r="G142" s="25"/>
-      <c r="H142" s="48"/>
-      <c r="I142" s="48"/>
+      <c r="H142" s="50"/>
+      <c r="I142" s="50"/>
       <c r="J142" s="25"/>
       <c r="K142" s="25"/>
       <c r="L142" s="25"/>
@@ -9885,8 +10141,8 @@
       <c r="E143" s="25"/>
       <c r="F143" s="25"/>
       <c r="G143" s="25"/>
-      <c r="H143" s="48"/>
-      <c r="I143" s="48"/>
+      <c r="H143" s="50"/>
+      <c r="I143" s="50"/>
       <c r="J143" s="25"/>
       <c r="K143" s="25"/>
       <c r="L143" s="25"/>
@@ -9912,8 +10168,8 @@
       <c r="E144" s="25"/>
       <c r="F144" s="25"/>
       <c r="G144" s="25"/>
-      <c r="H144" s="48"/>
-      <c r="I144" s="48"/>
+      <c r="H144" s="50"/>
+      <c r="I144" s="50"/>
       <c r="J144" s="25"/>
       <c r="K144" s="25"/>
       <c r="L144" s="25"/>
@@ -9939,8 +10195,8 @@
       <c r="E145" s="25"/>
       <c r="F145" s="25"/>
       <c r="G145" s="25"/>
-      <c r="H145" s="48"/>
-      <c r="I145" s="48"/>
+      <c r="H145" s="50"/>
+      <c r="I145" s="50"/>
       <c r="J145" s="25"/>
       <c r="K145" s="25"/>
       <c r="L145" s="25"/>
@@ -9966,8 +10222,8 @@
       <c r="E146" s="25"/>
       <c r="F146" s="25"/>
       <c r="G146" s="25"/>
-      <c r="H146" s="48"/>
-      <c r="I146" s="48"/>
+      <c r="H146" s="50"/>
+      <c r="I146" s="50"/>
       <c r="J146" s="25"/>
       <c r="K146" s="25"/>
       <c r="L146" s="25"/>
@@ -9993,8 +10249,8 @@
       <c r="E147" s="25"/>
       <c r="F147" s="25"/>
       <c r="G147" s="25"/>
-      <c r="H147" s="48"/>
-      <c r="I147" s="48"/>
+      <c r="H147" s="50"/>
+      <c r="I147" s="50"/>
       <c r="J147" s="25"/>
       <c r="K147" s="25"/>
       <c r="L147" s="25"/>
@@ -10020,8 +10276,8 @@
       <c r="E148" s="25"/>
       <c r="F148" s="25"/>
       <c r="G148" s="25"/>
-      <c r="H148" s="48"/>
-      <c r="I148" s="48"/>
+      <c r="H148" s="50"/>
+      <c r="I148" s="50"/>
       <c r="J148" s="25"/>
       <c r="K148" s="25"/>
       <c r="L148" s="25"/>
@@ -10047,8 +10303,8 @@
       <c r="E149" s="25"/>
       <c r="F149" s="25"/>
       <c r="G149" s="25"/>
-      <c r="H149" s="48"/>
-      <c r="I149" s="48"/>
+      <c r="H149" s="50"/>
+      <c r="I149" s="50"/>
       <c r="J149" s="25"/>
       <c r="K149" s="25"/>
       <c r="L149" s="25"/>
@@ -10074,8 +10330,8 @@
       <c r="E150" s="25"/>
       <c r="F150" s="25"/>
       <c r="G150" s="25"/>
-      <c r="H150" s="48"/>
-      <c r="I150" s="48"/>
+      <c r="H150" s="50"/>
+      <c r="I150" s="50"/>
       <c r="J150" s="25"/>
       <c r="K150" s="25"/>
       <c r="L150" s="25"/>
@@ -10101,8 +10357,8 @@
       <c r="E151" s="25"/>
       <c r="F151" s="25"/>
       <c r="G151" s="25"/>
-      <c r="H151" s="48"/>
-      <c r="I151" s="48"/>
+      <c r="H151" s="50"/>
+      <c r="I151" s="50"/>
       <c r="J151" s="25"/>
       <c r="K151" s="25"/>
       <c r="L151" s="25"/>
@@ -10128,8 +10384,8 @@
       <c r="E152" s="25"/>
       <c r="F152" s="25"/>
       <c r="G152" s="25"/>
-      <c r="H152" s="48"/>
-      <c r="I152" s="48"/>
+      <c r="H152" s="50"/>
+      <c r="I152" s="50"/>
       <c r="J152" s="25"/>
       <c r="K152" s="25"/>
       <c r="L152" s="25"/>
@@ -10155,8 +10411,8 @@
       <c r="E153" s="25"/>
       <c r="F153" s="25"/>
       <c r="G153" s="25"/>
-      <c r="H153" s="48"/>
-      <c r="I153" s="48"/>
+      <c r="H153" s="50"/>
+      <c r="I153" s="50"/>
       <c r="J153" s="25"/>
       <c r="K153" s="25"/>
       <c r="L153" s="25"/>
@@ -10182,8 +10438,8 @@
       <c r="E154" s="25"/>
       <c r="F154" s="25"/>
       <c r="G154" s="25"/>
-      <c r="H154" s="48"/>
-      <c r="I154" s="48"/>
+      <c r="H154" s="50"/>
+      <c r="I154" s="50"/>
       <c r="J154" s="25"/>
       <c r="K154" s="25"/>
       <c r="L154" s="25"/>
@@ -10209,8 +10465,8 @@
       <c r="E155" s="25"/>
       <c r="F155" s="25"/>
       <c r="G155" s="25"/>
-      <c r="H155" s="48"/>
-      <c r="I155" s="48"/>
+      <c r="H155" s="50"/>
+      <c r="I155" s="50"/>
       <c r="J155" s="25"/>
       <c r="K155" s="25"/>
       <c r="L155" s="25"/>
@@ -10236,8 +10492,8 @@
       <c r="E156" s="25"/>
       <c r="F156" s="25"/>
       <c r="G156" s="25"/>
-      <c r="H156" s="48"/>
-      <c r="I156" s="48"/>
+      <c r="H156" s="50"/>
+      <c r="I156" s="50"/>
       <c r="J156" s="25"/>
       <c r="K156" s="25"/>
       <c r="L156" s="25"/>
@@ -10263,8 +10519,8 @@
       <c r="E157" s="25"/>
       <c r="F157" s="25"/>
       <c r="G157" s="25"/>
-      <c r="H157" s="48"/>
-      <c r="I157" s="48"/>
+      <c r="H157" s="50"/>
+      <c r="I157" s="50"/>
       <c r="J157" s="25"/>
       <c r="K157" s="25"/>
       <c r="L157" s="25"/>
@@ -10290,8 +10546,8 @@
       <c r="E158" s="25"/>
       <c r="F158" s="25"/>
       <c r="G158" s="25"/>
-      <c r="H158" s="48"/>
-      <c r="I158" s="48"/>
+      <c r="H158" s="50"/>
+      <c r="I158" s="50"/>
       <c r="J158" s="25"/>
       <c r="K158" s="25"/>
       <c r="L158" s="25"/>
@@ -10317,8 +10573,8 @@
       <c r="E159" s="25"/>
       <c r="F159" s="25"/>
       <c r="G159" s="25"/>
-      <c r="H159" s="48"/>
-      <c r="I159" s="48"/>
+      <c r="H159" s="50"/>
+      <c r="I159" s="50"/>
       <c r="J159" s="25"/>
       <c r="K159" s="25"/>
       <c r="L159" s="25"/>
@@ -10344,8 +10600,8 @@
       <c r="E160" s="25"/>
       <c r="F160" s="25"/>
       <c r="G160" s="25"/>
-      <c r="H160" s="48"/>
-      <c r="I160" s="48"/>
+      <c r="H160" s="50"/>
+      <c r="I160" s="50"/>
       <c r="J160" s="25"/>
       <c r="K160" s="25"/>
       <c r="L160" s="25"/>
@@ -10371,8 +10627,8 @@
       <c r="E161" s="25"/>
       <c r="F161" s="25"/>
       <c r="G161" s="25"/>
-      <c r="H161" s="48"/>
-      <c r="I161" s="48"/>
+      <c r="H161" s="50"/>
+      <c r="I161" s="50"/>
       <c r="J161" s="25"/>
       <c r="K161" s="25"/>
       <c r="L161" s="25"/>
@@ -10398,8 +10654,8 @@
       <c r="E162" s="25"/>
       <c r="F162" s="25"/>
       <c r="G162" s="25"/>
-      <c r="H162" s="48"/>
-      <c r="I162" s="48"/>
+      <c r="H162" s="50"/>
+      <c r="I162" s="50"/>
       <c r="J162" s="25"/>
       <c r="K162" s="25"/>
       <c r="L162" s="25"/>
@@ -10425,8 +10681,8 @@
       <c r="E163" s="25"/>
       <c r="F163" s="25"/>
       <c r="G163" s="25"/>
-      <c r="H163" s="48"/>
-      <c r="I163" s="48"/>
+      <c r="H163" s="50"/>
+      <c r="I163" s="50"/>
       <c r="J163" s="25"/>
       <c r="K163" s="25"/>
       <c r="L163" s="25"/>
@@ -10452,8 +10708,8 @@
       <c r="E164" s="25"/>
       <c r="F164" s="25"/>
       <c r="G164" s="25"/>
-      <c r="H164" s="48"/>
-      <c r="I164" s="48"/>
+      <c r="H164" s="50"/>
+      <c r="I164" s="50"/>
       <c r="J164" s="25"/>
       <c r="K164" s="25"/>
       <c r="L164" s="25"/>
@@ -10479,8 +10735,8 @@
       <c r="E165" s="25"/>
       <c r="F165" s="25"/>
       <c r="G165" s="25"/>
-      <c r="H165" s="48"/>
-      <c r="I165" s="48"/>
+      <c r="H165" s="50"/>
+      <c r="I165" s="50"/>
       <c r="J165" s="25"/>
       <c r="K165" s="25"/>
       <c r="L165" s="25"/>
@@ -10506,8 +10762,8 @@
       <c r="E166" s="25"/>
       <c r="F166" s="25"/>
       <c r="G166" s="25"/>
-      <c r="H166" s="48"/>
-      <c r="I166" s="48"/>
+      <c r="H166" s="50"/>
+      <c r="I166" s="50"/>
       <c r="J166" s="25"/>
       <c r="K166" s="25"/>
       <c r="L166" s="25"/>
@@ -10533,8 +10789,8 @@
       <c r="E167" s="25"/>
       <c r="F167" s="25"/>
       <c r="G167" s="25"/>
-      <c r="H167" s="48"/>
-      <c r="I167" s="48"/>
+      <c r="H167" s="50"/>
+      <c r="I167" s="50"/>
       <c r="J167" s="25"/>
       <c r="K167" s="25"/>
       <c r="L167" s="25"/>
@@ -10560,8 +10816,8 @@
       <c r="E168" s="25"/>
       <c r="F168" s="25"/>
       <c r="G168" s="25"/>
-      <c r="H168" s="48"/>
-      <c r="I168" s="48"/>
+      <c r="H168" s="50"/>
+      <c r="I168" s="50"/>
       <c r="J168" s="25"/>
       <c r="K168" s="25"/>
       <c r="L168" s="25"/>
@@ -10587,8 +10843,8 @@
       <c r="E169" s="25"/>
       <c r="F169" s="25"/>
       <c r="G169" s="25"/>
-      <c r="H169" s="48"/>
-      <c r="I169" s="48"/>
+      <c r="H169" s="50"/>
+      <c r="I169" s="50"/>
       <c r="J169" s="25"/>
       <c r="K169" s="25"/>
       <c r="L169" s="25"/>
@@ -10614,8 +10870,8 @@
       <c r="E170" s="25"/>
       <c r="F170" s="25"/>
       <c r="G170" s="25"/>
-      <c r="H170" s="48"/>
-      <c r="I170" s="48"/>
+      <c r="H170" s="50"/>
+      <c r="I170" s="50"/>
       <c r="J170" s="25"/>
       <c r="K170" s="25"/>
       <c r="L170" s="25"/>
@@ -10641,8 +10897,8 @@
       <c r="E171" s="25"/>
       <c r="F171" s="25"/>
       <c r="G171" s="25"/>
-      <c r="H171" s="48"/>
-      <c r="I171" s="48"/>
+      <c r="H171" s="50"/>
+      <c r="I171" s="50"/>
       <c r="J171" s="25"/>
       <c r="K171" s="25"/>
       <c r="L171" s="25"/>
@@ -10668,8 +10924,8 @@
       <c r="E172" s="25"/>
       <c r="F172" s="25"/>
       <c r="G172" s="25"/>
-      <c r="H172" s="48"/>
-      <c r="I172" s="48"/>
+      <c r="H172" s="50"/>
+      <c r="I172" s="50"/>
       <c r="J172" s="25"/>
       <c r="K172" s="25"/>
       <c r="L172" s="25"/>
@@ -10695,8 +10951,8 @@
       <c r="E173" s="25"/>
       <c r="F173" s="25"/>
       <c r="G173" s="25"/>
-      <c r="H173" s="48"/>
-      <c r="I173" s="48"/>
+      <c r="H173" s="50"/>
+      <c r="I173" s="50"/>
       <c r="J173" s="25"/>
       <c r="K173" s="25"/>
       <c r="L173" s="25"/>
@@ -10722,8 +10978,8 @@
       <c r="E174" s="25"/>
       <c r="F174" s="25"/>
       <c r="G174" s="25"/>
-      <c r="H174" s="48"/>
-      <c r="I174" s="48"/>
+      <c r="H174" s="50"/>
+      <c r="I174" s="50"/>
       <c r="J174" s="25"/>
       <c r="K174" s="25"/>
       <c r="L174" s="25"/>
@@ -10749,8 +11005,8 @@
       <c r="E175" s="25"/>
       <c r="F175" s="25"/>
       <c r="G175" s="25"/>
-      <c r="H175" s="48"/>
-      <c r="I175" s="48"/>
+      <c r="H175" s="50"/>
+      <c r="I175" s="50"/>
       <c r="J175" s="25"/>
       <c r="K175" s="25"/>
       <c r="L175" s="25"/>
@@ -10776,8 +11032,8 @@
       <c r="E176" s="25"/>
       <c r="F176" s="25"/>
       <c r="G176" s="25"/>
-      <c r="H176" s="48"/>
-      <c r="I176" s="48"/>
+      <c r="H176" s="50"/>
+      <c r="I176" s="50"/>
       <c r="J176" s="25"/>
       <c r="K176" s="25"/>
       <c r="L176" s="25"/>
@@ -10803,8 +11059,8 @@
       <c r="E177" s="25"/>
       <c r="F177" s="25"/>
       <c r="G177" s="25"/>
-      <c r="H177" s="48"/>
-      <c r="I177" s="48"/>
+      <c r="H177" s="50"/>
+      <c r="I177" s="50"/>
       <c r="J177" s="25"/>
       <c r="K177" s="25"/>
       <c r="L177" s="25"/>
@@ -10830,8 +11086,8 @@
       <c r="E178" s="25"/>
       <c r="F178" s="25"/>
       <c r="G178" s="25"/>
-      <c r="H178" s="48"/>
-      <c r="I178" s="48"/>
+      <c r="H178" s="50"/>
+      <c r="I178" s="50"/>
       <c r="J178" s="25"/>
       <c r="K178" s="25"/>
       <c r="L178" s="25"/>
@@ -10857,8 +11113,8 @@
       <c r="E179" s="25"/>
       <c r="F179" s="25"/>
       <c r="G179" s="25"/>
-      <c r="H179" s="48"/>
-      <c r="I179" s="48"/>
+      <c r="H179" s="50"/>
+      <c r="I179" s="50"/>
       <c r="J179" s="25"/>
       <c r="K179" s="25"/>
       <c r="L179" s="25"/>
@@ -10884,8 +11140,8 @@
       <c r="E180" s="25"/>
       <c r="F180" s="25"/>
       <c r="G180" s="25"/>
-      <c r="H180" s="48"/>
-      <c r="I180" s="48"/>
+      <c r="H180" s="50"/>
+      <c r="I180" s="50"/>
       <c r="J180" s="25"/>
       <c r="K180" s="25"/>
       <c r="L180" s="25"/>
@@ -10911,8 +11167,8 @@
       <c r="E181" s="25"/>
       <c r="F181" s="25"/>
       <c r="G181" s="25"/>
-      <c r="H181" s="48"/>
-      <c r="I181" s="48"/>
+      <c r="H181" s="50"/>
+      <c r="I181" s="50"/>
       <c r="J181" s="25"/>
       <c r="K181" s="25"/>
       <c r="L181" s="25"/>
@@ -10938,8 +11194,8 @@
       <c r="E182" s="25"/>
       <c r="F182" s="25"/>
       <c r="G182" s="25"/>
-      <c r="H182" s="48"/>
-      <c r="I182" s="48"/>
+      <c r="H182" s="50"/>
+      <c r="I182" s="50"/>
       <c r="J182" s="25"/>
       <c r="K182" s="25"/>
       <c r="L182" s="25"/>
@@ -10965,8 +11221,8 @@
       <c r="E183" s="25"/>
       <c r="F183" s="25"/>
       <c r="G183" s="25"/>
-      <c r="H183" s="48"/>
-      <c r="I183" s="48"/>
+      <c r="H183" s="50"/>
+      <c r="I183" s="50"/>
       <c r="J183" s="25"/>
       <c r="K183" s="25"/>
       <c r="L183" s="25"/>
@@ -10992,8 +11248,8 @@
       <c r="E184" s="25"/>
       <c r="F184" s="25"/>
       <c r="G184" s="25"/>
-      <c r="H184" s="48"/>
-      <c r="I184" s="48"/>
+      <c r="H184" s="50"/>
+      <c r="I184" s="50"/>
       <c r="J184" s="25"/>
       <c r="K184" s="25"/>
       <c r="L184" s="25"/>
@@ -11019,8 +11275,8 @@
       <c r="E185" s="25"/>
       <c r="F185" s="25"/>
       <c r="G185" s="25"/>
-      <c r="H185" s="48"/>
-      <c r="I185" s="48"/>
+      <c r="H185" s="50"/>
+      <c r="I185" s="50"/>
       <c r="J185" s="25"/>
       <c r="K185" s="25"/>
       <c r="L185" s="25"/>
@@ -11046,8 +11302,8 @@
       <c r="E186" s="25"/>
       <c r="F186" s="25"/>
       <c r="G186" s="25"/>
-      <c r="H186" s="48"/>
-      <c r="I186" s="48"/>
+      <c r="H186" s="50"/>
+      <c r="I186" s="50"/>
       <c r="J186" s="25"/>
       <c r="K186" s="25"/>
       <c r="L186" s="25"/>
@@ -11072,8 +11328,8 @@
       <c r="E187" s="25"/>
       <c r="F187" s="25"/>
       <c r="G187" s="25"/>
-      <c r="H187" s="48"/>
-      <c r="I187" s="48"/>
+      <c r="H187" s="50"/>
+      <c r="I187" s="50"/>
       <c r="J187" s="25"/>
       <c r="K187" s="25"/>
       <c r="L187" s="25"/>
@@ -11101,8 +11357,8 @@
       <c r="E188" s="25"/>
       <c r="F188" s="25"/>
       <c r="G188" s="25"/>
-      <c r="H188" s="48"/>
-      <c r="I188" s="48"/>
+      <c r="H188" s="50"/>
+      <c r="I188" s="50"/>
       <c r="J188" s="25"/>
       <c r="K188" s="25"/>
       <c r="L188" s="25"/>
@@ -11128,8 +11384,8 @@
       <c r="E189" s="25"/>
       <c r="F189" s="25"/>
       <c r="G189" s="25"/>
-      <c r="H189" s="48"/>
-      <c r="I189" s="48"/>
+      <c r="H189" s="50"/>
+      <c r="I189" s="50"/>
       <c r="J189" s="25"/>
       <c r="K189" s="25"/>
       <c r="L189" s="25"/>
@@ -11155,8 +11411,8 @@
       <c r="E190" s="25"/>
       <c r="F190" s="25"/>
       <c r="G190" s="25"/>
-      <c r="H190" s="48"/>
-      <c r="I190" s="48"/>
+      <c r="H190" s="50"/>
+      <c r="I190" s="50"/>
       <c r="J190" s="25"/>
       <c r="K190" s="25"/>
       <c r="L190" s="25"/>
@@ -11182,8 +11438,8 @@
       <c r="E191" s="25"/>
       <c r="F191" s="25"/>
       <c r="G191" s="25"/>
-      <c r="H191" s="48"/>
-      <c r="I191" s="48"/>
+      <c r="H191" s="50"/>
+      <c r="I191" s="50"/>
       <c r="J191" s="25"/>
       <c r="K191" s="25"/>
       <c r="L191" s="25"/>
@@ -11209,8 +11465,8 @@
       <c r="E192" s="25"/>
       <c r="F192" s="25"/>
       <c r="G192" s="25"/>
-      <c r="H192" s="48"/>
-      <c r="I192" s="48"/>
+      <c r="H192" s="50"/>
+      <c r="I192" s="50"/>
       <c r="J192" s="25"/>
       <c r="K192" s="25"/>
       <c r="L192" s="25"/>
@@ -11236,8 +11492,8 @@
       <c r="E193" s="25"/>
       <c r="F193" s="25"/>
       <c r="G193" s="25"/>
-      <c r="H193" s="48"/>
-      <c r="I193" s="48"/>
+      <c r="H193" s="50"/>
+      <c r="I193" s="50"/>
       <c r="J193" s="25"/>
       <c r="K193" s="25"/>
       <c r="L193" s="25"/>
@@ -11263,8 +11519,8 @@
       <c r="E194" s="25"/>
       <c r="F194" s="25"/>
       <c r="G194" s="25"/>
-      <c r="H194" s="48"/>
-      <c r="I194" s="48"/>
+      <c r="H194" s="50"/>
+      <c r="I194" s="50"/>
       <c r="J194" s="25"/>
       <c r="K194" s="25"/>
       <c r="L194" s="25"/>
@@ -11290,8 +11546,8 @@
       <c r="E195" s="25"/>
       <c r="F195" s="25"/>
       <c r="G195" s="25"/>
-      <c r="H195" s="48"/>
-      <c r="I195" s="48"/>
+      <c r="H195" s="50"/>
+      <c r="I195" s="50"/>
       <c r="J195" s="25"/>
       <c r="K195" s="25"/>
       <c r="L195" s="25"/>
@@ -11317,8 +11573,8 @@
       <c r="E196" s="25"/>
       <c r="F196" s="25"/>
       <c r="G196" s="25"/>
-      <c r="H196" s="48"/>
-      <c r="I196" s="48"/>
+      <c r="H196" s="50"/>
+      <c r="I196" s="50"/>
       <c r="J196" s="25"/>
       <c r="K196" s="25"/>
       <c r="L196" s="25"/>
@@ -11344,8 +11600,8 @@
       <c r="E197" s="25"/>
       <c r="F197" s="25"/>
       <c r="G197" s="25"/>
-      <c r="H197" s="48"/>
-      <c r="I197" s="48"/>
+      <c r="H197" s="50"/>
+      <c r="I197" s="50"/>
       <c r="J197" s="25"/>
       <c r="K197" s="25"/>
       <c r="L197" s="25"/>
@@ -11371,8 +11627,8 @@
       <c r="E198" s="25"/>
       <c r="F198" s="25"/>
       <c r="G198" s="25"/>
-      <c r="H198" s="48"/>
-      <c r="I198" s="48"/>
+      <c r="H198" s="50"/>
+      <c r="I198" s="50"/>
       <c r="J198" s="25"/>
       <c r="K198" s="25"/>
       <c r="L198" s="25"/>
@@ -11398,8 +11654,8 @@
       <c r="E199" s="25"/>
       <c r="F199" s="25"/>
       <c r="G199" s="25"/>
-      <c r="H199" s="48"/>
-      <c r="I199" s="48"/>
+      <c r="H199" s="50"/>
+      <c r="I199" s="50"/>
       <c r="J199" s="25"/>
       <c r="K199" s="25"/>
       <c r="L199" s="25"/>
@@ -11425,8 +11681,8 @@
       <c r="E200" s="25"/>
       <c r="F200" s="25"/>
       <c r="G200" s="25"/>
-      <c r="H200" s="48"/>
-      <c r="I200" s="48"/>
+      <c r="H200" s="50"/>
+      <c r="I200" s="50"/>
       <c r="J200" s="25"/>
       <c r="K200" s="25"/>
       <c r="L200" s="25"/>
@@ -11452,8 +11708,8 @@
       <c r="E201" s="25"/>
       <c r="F201" s="25"/>
       <c r="G201" s="25"/>
-      <c r="H201" s="48"/>
-      <c r="I201" s="48"/>
+      <c r="H201" s="50"/>
+      <c r="I201" s="50"/>
       <c r="J201" s="25"/>
       <c r="K201" s="25"/>
       <c r="L201" s="25"/>
@@ -11479,8 +11735,8 @@
       <c r="E202" s="25"/>
       <c r="F202" s="25"/>
       <c r="G202" s="25"/>
-      <c r="H202" s="48"/>
-      <c r="I202" s="48"/>
+      <c r="H202" s="50"/>
+      <c r="I202" s="50"/>
       <c r="J202" s="25"/>
       <c r="K202" s="25"/>
       <c r="L202" s="25"/>
@@ -11506,8 +11762,8 @@
       <c r="E203" s="25"/>
       <c r="F203" s="25"/>
       <c r="G203" s="25"/>
-      <c r="H203" s="48"/>
-      <c r="I203" s="48"/>
+      <c r="H203" s="50"/>
+      <c r="I203" s="50"/>
       <c r="J203" s="25"/>
       <c r="K203" s="25"/>
       <c r="L203" s="25"/>
@@ -11533,8 +11789,8 @@
       <c r="E204" s="25"/>
       <c r="F204" s="25"/>
       <c r="G204" s="29"/>
-      <c r="H204" s="49"/>
-      <c r="I204" s="48"/>
+      <c r="H204" s="51"/>
+      <c r="I204" s="50"/>
       <c r="J204" s="25"/>
       <c r="K204" s="37"/>
       <c r="L204" s="25"/>
@@ -11564,8 +11820,8 @@
       <c r="G205" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="H205" s="50"/>
-      <c r="I205" s="50"/>
+      <c r="H205" s="52"/>
+      <c r="I205" s="52"/>
       <c r="J205" s="41" t="s">
         <v>697</v>
       </c>
@@ -11601,8 +11857,8 @@
       <c r="E206" s="25"/>
       <c r="F206" s="25"/>
       <c r="G206" s="25"/>
-      <c r="H206" s="48"/>
-      <c r="I206" s="48"/>
+      <c r="H206" s="50"/>
+      <c r="I206" s="50"/>
       <c r="J206" s="25"/>
       <c r="K206" s="25" t="s">
         <v>710</v>
@@ -11636,8 +11892,8 @@
       <c r="E207" s="25"/>
       <c r="F207" s="25"/>
       <c r="G207" s="25"/>
-      <c r="H207" s="48"/>
-      <c r="I207" s="48"/>
+      <c r="H207" s="50"/>
+      <c r="I207" s="50"/>
       <c r="J207" s="25"/>
       <c r="K207" s="25" t="s">
         <v>711</v>
@@ -11667,8 +11923,8 @@
       <c r="E208" s="25"/>
       <c r="F208" s="25"/>
       <c r="G208" s="25"/>
-      <c r="H208" s="48"/>
-      <c r="I208" s="48"/>
+      <c r="H208" s="50"/>
+      <c r="I208" s="50"/>
       <c r="J208" s="25"/>
       <c r="K208" s="25" t="s">
         <v>1060</v>
@@ -11698,8 +11954,8 @@
       <c r="E209" s="25"/>
       <c r="F209" s="25"/>
       <c r="G209" s="25"/>
-      <c r="H209" s="48"/>
-      <c r="I209" s="48"/>
+      <c r="H209" s="50"/>
+      <c r="I209" s="50"/>
       <c r="J209" s="25"/>
       <c r="K209" s="25"/>
       <c r="L209" s="25"/>
@@ -11725,8 +11981,8 @@
       <c r="E210" s="25"/>
       <c r="F210" s="25"/>
       <c r="G210" s="25"/>
-      <c r="H210" s="48"/>
-      <c r="I210" s="48"/>
+      <c r="H210" s="50"/>
+      <c r="I210" s="50"/>
       <c r="J210" s="25"/>
       <c r="K210" s="25"/>
       <c r="L210" s="25"/>
@@ -11752,8 +12008,8 @@
       <c r="E211" s="25"/>
       <c r="F211" s="25"/>
       <c r="G211" s="25"/>
-      <c r="H211" s="48"/>
-      <c r="I211" s="48"/>
+      <c r="H211" s="50"/>
+      <c r="I211" s="50"/>
       <c r="J211" s="25"/>
       <c r="K211" s="25"/>
       <c r="L211" s="25"/>
@@ -11779,8 +12035,8 @@
       <c r="E212" s="25"/>
       <c r="F212" s="25"/>
       <c r="G212" s="25"/>
-      <c r="H212" s="48"/>
-      <c r="I212" s="48"/>
+      <c r="H212" s="50"/>
+      <c r="I212" s="50"/>
       <c r="J212" s="25"/>
       <c r="K212" s="25"/>
       <c r="L212" s="25"/>
@@ -11806,8 +12062,8 @@
       <c r="E213" s="25"/>
       <c r="F213" s="25"/>
       <c r="G213" s="25"/>
-      <c r="H213" s="48"/>
-      <c r="I213" s="48"/>
+      <c r="H213" s="50"/>
+      <c r="I213" s="50"/>
       <c r="J213" s="25"/>
       <c r="K213" s="25"/>
       <c r="L213" s="25"/>
@@ -11833,8 +12089,8 @@
       <c r="E214" s="25"/>
       <c r="F214" s="25"/>
       <c r="G214" s="25"/>
-      <c r="H214" s="48"/>
-      <c r="I214" s="48"/>
+      <c r="H214" s="50"/>
+      <c r="I214" s="50"/>
       <c r="J214" s="25"/>
       <c r="K214" s="25"/>
       <c r="L214" s="25"/>
@@ -11860,8 +12116,8 @@
       <c r="E215" s="25"/>
       <c r="F215" s="25"/>
       <c r="G215" s="25"/>
-      <c r="H215" s="48"/>
-      <c r="I215" s="48"/>
+      <c r="H215" s="50"/>
+      <c r="I215" s="50"/>
       <c r="J215" s="25"/>
       <c r="K215" s="25"/>
       <c r="L215" s="25"/>
@@ -11889,8 +12145,8 @@
       <c r="G216" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="H216" s="48"/>
-      <c r="I216" s="48"/>
+      <c r="H216" s="50"/>
+      <c r="I216" s="50"/>
       <c r="J216" s="25"/>
       <c r="K216" s="25"/>
       <c r="L216" s="25"/>
@@ -11914,8 +12170,8 @@
       <c r="E217" s="25"/>
       <c r="F217" s="25"/>
       <c r="G217" s="25"/>
-      <c r="H217" s="48"/>
-      <c r="I217" s="48"/>
+      <c r="H217" s="50"/>
+      <c r="I217" s="50"/>
       <c r="J217" s="25"/>
       <c r="K217" s="25"/>
       <c r="L217" s="25"/>
@@ -11939,8 +12195,8 @@
       <c r="E218" s="25"/>
       <c r="F218" s="25"/>
       <c r="G218" s="25"/>
-      <c r="H218" s="48"/>
-      <c r="I218" s="48"/>
+      <c r="H218" s="50"/>
+      <c r="I218" s="50"/>
       <c r="J218" s="25"/>
       <c r="K218" s="25"/>
       <c r="L218" s="25"/>
@@ -11964,8 +12220,8 @@
       <c r="E219" s="25"/>
       <c r="F219" s="25"/>
       <c r="G219" s="25"/>
-      <c r="H219" s="48"/>
-      <c r="I219" s="48"/>
+      <c r="H219" s="50"/>
+      <c r="I219" s="50"/>
       <c r="J219" s="25"/>
       <c r="K219" s="25"/>
       <c r="L219" s="25"/>
@@ -11989,8 +12245,8 @@
       <c r="E220" s="25"/>
       <c r="F220" s="25"/>
       <c r="G220" s="25"/>
-      <c r="H220" s="48"/>
-      <c r="I220" s="48"/>
+      <c r="H220" s="50"/>
+      <c r="I220" s="50"/>
       <c r="J220" s="25"/>
       <c r="K220" s="25"/>
       <c r="L220" s="25"/>
@@ -12014,8 +12270,8 @@
       <c r="E221" s="25"/>
       <c r="F221" s="25"/>
       <c r="G221" s="25"/>
-      <c r="H221" s="48"/>
-      <c r="I221" s="48"/>
+      <c r="H221" s="50"/>
+      <c r="I221" s="50"/>
       <c r="J221" s="25"/>
       <c r="K221" s="25"/>
       <c r="L221" s="25"/>
@@ -12039,8 +12295,8 @@
       <c r="E222" s="25"/>
       <c r="F222" s="25"/>
       <c r="G222" s="25"/>
-      <c r="H222" s="48"/>
-      <c r="I222" s="48"/>
+      <c r="H222" s="50"/>
+      <c r="I222" s="50"/>
       <c r="J222" s="25"/>
       <c r="K222" s="25"/>
       <c r="L222" s="25"/>
@@ -12064,8 +12320,8 @@
       <c r="E223" s="25"/>
       <c r="F223" s="25"/>
       <c r="G223" s="25"/>
-      <c r="H223" s="48"/>
-      <c r="I223" s="48"/>
+      <c r="H223" s="50"/>
+      <c r="I223" s="50"/>
       <c r="J223" s="25"/>
       <c r="K223" s="25"/>
       <c r="L223" s="25"/>
@@ -12089,8 +12345,8 @@
       <c r="E224" s="25"/>
       <c r="F224" s="25"/>
       <c r="G224" s="25"/>
-      <c r="H224" s="48"/>
-      <c r="I224" s="48"/>
+      <c r="H224" s="50"/>
+      <c r="I224" s="50"/>
       <c r="J224" s="25"/>
       <c r="K224" s="25"/>
       <c r="L224" s="25"/>
@@ -12114,8 +12370,8 @@
       <c r="E225" s="25"/>
       <c r="F225" s="25"/>
       <c r="G225" s="25"/>
-      <c r="H225" s="48"/>
-      <c r="I225" s="48"/>
+      <c r="H225" s="50"/>
+      <c r="I225" s="50"/>
       <c r="J225" s="25"/>
       <c r="K225" s="25"/>
       <c r="L225" s="25"/>
@@ -12139,8 +12395,8 @@
       <c r="E226" s="25"/>
       <c r="F226" s="25"/>
       <c r="G226" s="25"/>
-      <c r="H226" s="48"/>
-      <c r="I226" s="48"/>
+      <c r="H226" s="50"/>
+      <c r="I226" s="50"/>
       <c r="J226" s="25"/>
       <c r="K226" s="25"/>
       <c r="L226" s="25"/>
@@ -12164,8 +12420,8 @@
       <c r="E227" s="25"/>
       <c r="F227" s="25"/>
       <c r="G227" s="25"/>
-      <c r="H227" s="48"/>
-      <c r="I227" s="48"/>
+      <c r="H227" s="50"/>
+      <c r="I227" s="50"/>
       <c r="J227" s="25"/>
       <c r="K227" s="25"/>
       <c r="L227" s="25"/>
@@ -12189,8 +12445,8 @@
       <c r="E228" s="25"/>
       <c r="F228" s="25"/>
       <c r="G228" s="25"/>
-      <c r="H228" s="48"/>
-      <c r="I228" s="48"/>
+      <c r="H228" s="50"/>
+      <c r="I228" s="50"/>
       <c r="J228" s="25"/>
       <c r="K228" s="25"/>
       <c r="L228" s="25"/>
@@ -12214,8 +12470,8 @@
       <c r="E229" s="25"/>
       <c r="F229" s="25"/>
       <c r="G229" s="25"/>
-      <c r="H229" s="48"/>
-      <c r="I229" s="48"/>
+      <c r="H229" s="50"/>
+      <c r="I229" s="50"/>
       <c r="J229" s="25"/>
       <c r="K229" s="25"/>
       <c r="L229" s="25"/>
@@ -12239,8 +12495,8 @@
       <c r="E230" s="25"/>
       <c r="F230" s="25"/>
       <c r="G230" s="25"/>
-      <c r="H230" s="48"/>
-      <c r="I230" s="48"/>
+      <c r="H230" s="50"/>
+      <c r="I230" s="50"/>
       <c r="J230" s="25"/>
       <c r="K230" s="25"/>
       <c r="L230" s="25"/>
@@ -12264,8 +12520,8 @@
       <c r="E231" s="25"/>
       <c r="F231" s="25"/>
       <c r="G231" s="25"/>
-      <c r="H231" s="48"/>
-      <c r="I231" s="48"/>
+      <c r="H231" s="50"/>
+      <c r="I231" s="50"/>
       <c r="J231" s="25"/>
       <c r="K231" s="25"/>
       <c r="L231" s="25"/>
@@ -12289,8 +12545,8 @@
       <c r="E232" s="25"/>
       <c r="F232" s="25"/>
       <c r="G232" s="25"/>
-      <c r="H232" s="48"/>
-      <c r="I232" s="48"/>
+      <c r="H232" s="50"/>
+      <c r="I232" s="50"/>
       <c r="J232" s="25"/>
       <c r="K232" s="25"/>
       <c r="L232" s="25"/>
@@ -12314,8 +12570,8 @@
       <c r="E233" s="25"/>
       <c r="F233" s="25"/>
       <c r="G233" s="25"/>
-      <c r="H233" s="48"/>
-      <c r="I233" s="48"/>
+      <c r="H233" s="50"/>
+      <c r="I233" s="50"/>
       <c r="J233" s="25"/>
       <c r="K233" s="25"/>
       <c r="L233" s="25"/>
@@ -12339,8 +12595,8 @@
       <c r="E234" s="25"/>
       <c r="F234" s="25"/>
       <c r="G234" s="25"/>
-      <c r="H234" s="48"/>
-      <c r="I234" s="48"/>
+      <c r="H234" s="50"/>
+      <c r="I234" s="50"/>
       <c r="J234" s="25"/>
       <c r="K234" s="25"/>
       <c r="L234" s="25"/>
@@ -12364,8 +12620,8 @@
       <c r="E235" s="25"/>
       <c r="F235" s="25"/>
       <c r="G235" s="25"/>
-      <c r="H235" s="48"/>
-      <c r="I235" s="48"/>
+      <c r="H235" s="50"/>
+      <c r="I235" s="50"/>
       <c r="J235" s="25"/>
       <c r="K235" s="25"/>
       <c r="L235" s="25"/>
@@ -12389,8 +12645,8 @@
       <c r="E236" s="25"/>
       <c r="F236" s="25"/>
       <c r="G236" s="25"/>
-      <c r="H236" s="48"/>
-      <c r="I236" s="48"/>
+      <c r="H236" s="50"/>
+      <c r="I236" s="50"/>
       <c r="J236" s="25"/>
       <c r="K236" s="25"/>
       <c r="L236" s="25"/>
@@ -12414,8 +12670,8 @@
       <c r="E237" s="25"/>
       <c r="F237" s="25"/>
       <c r="G237" s="25"/>
-      <c r="H237" s="48"/>
-      <c r="I237" s="48"/>
+      <c r="H237" s="50"/>
+      <c r="I237" s="50"/>
       <c r="J237" s="25"/>
       <c r="K237" s="25"/>
       <c r="L237" s="25"/>
@@ -12439,8 +12695,8 @@
       <c r="E238" s="25"/>
       <c r="F238" s="25"/>
       <c r="G238" s="25"/>
-      <c r="H238" s="48"/>
-      <c r="I238" s="48"/>
+      <c r="H238" s="50"/>
+      <c r="I238" s="50"/>
       <c r="J238" s="25"/>
       <c r="K238" s="25"/>
       <c r="L238" s="25"/>
@@ -12464,8 +12720,8 @@
       <c r="E239" s="25"/>
       <c r="F239" s="25"/>
       <c r="G239" s="25"/>
-      <c r="H239" s="48"/>
-      <c r="I239" s="48"/>
+      <c r="H239" s="50"/>
+      <c r="I239" s="50"/>
       <c r="J239" s="25"/>
       <c r="K239" s="25"/>
       <c r="L239" s="25"/>
@@ -12489,8 +12745,8 @@
       <c r="E240" s="25"/>
       <c r="F240" s="25"/>
       <c r="G240" s="25"/>
-      <c r="H240" s="48"/>
-      <c r="I240" s="48"/>
+      <c r="H240" s="50"/>
+      <c r="I240" s="50"/>
       <c r="J240" s="25"/>
       <c r="K240" s="25"/>
       <c r="L240" s="25"/>
@@ -12514,8 +12770,8 @@
       <c r="E241" s="25"/>
       <c r="F241" s="25"/>
       <c r="G241" s="25"/>
-      <c r="H241" s="48"/>
-      <c r="I241" s="48"/>
+      <c r="H241" s="50"/>
+      <c r="I241" s="50"/>
       <c r="J241" s="25"/>
       <c r="K241" s="25"/>
       <c r="L241" s="25"/>
@@ -12539,8 +12795,8 @@
       <c r="E242" s="25"/>
       <c r="F242" s="25"/>
       <c r="G242" s="25"/>
-      <c r="H242" s="48"/>
-      <c r="I242" s="48"/>
+      <c r="H242" s="50"/>
+      <c r="I242" s="50"/>
       <c r="J242" s="25"/>
       <c r="K242" s="25"/>
       <c r="L242" s="25"/>
@@ -12564,8 +12820,8 @@
       <c r="E243" s="25"/>
       <c r="F243" s="25"/>
       <c r="G243" s="25"/>
-      <c r="H243" s="48"/>
-      <c r="I243" s="48"/>
+      <c r="H243" s="50"/>
+      <c r="I243" s="50"/>
       <c r="J243" s="25"/>
       <c r="K243" s="25"/>
       <c r="L243" s="25"/>
@@ -12589,8 +12845,8 @@
       <c r="E244" s="25"/>
       <c r="F244" s="25"/>
       <c r="G244" s="25"/>
-      <c r="H244" s="48"/>
-      <c r="I244" s="48"/>
+      <c r="H244" s="50"/>
+      <c r="I244" s="50"/>
       <c r="J244" s="25"/>
       <c r="K244" s="25"/>
       <c r="L244" s="25"/>
@@ -12614,8 +12870,8 @@
       <c r="E245" s="25"/>
       <c r="F245" s="25"/>
       <c r="G245" s="25"/>
-      <c r="H245" s="48"/>
-      <c r="I245" s="48"/>
+      <c r="H245" s="50"/>
+      <c r="I245" s="50"/>
       <c r="J245" s="25"/>
       <c r="K245" s="25"/>
       <c r="L245" s="25"/>
@@ -12639,8 +12895,8 @@
       <c r="E246" s="25"/>
       <c r="F246" s="25"/>
       <c r="G246" s="25"/>
-      <c r="H246" s="48"/>
-      <c r="I246" s="48"/>
+      <c r="H246" s="50"/>
+      <c r="I246" s="50"/>
       <c r="J246" s="25"/>
       <c r="K246" s="25"/>
       <c r="L246" s="25"/>
@@ -12664,8 +12920,8 @@
       <c r="E247" s="25"/>
       <c r="F247" s="25"/>
       <c r="G247" s="25"/>
-      <c r="H247" s="48"/>
-      <c r="I247" s="48"/>
+      <c r="H247" s="50"/>
+      <c r="I247" s="50"/>
       <c r="J247" s="25"/>
       <c r="K247" s="25"/>
       <c r="L247" s="25"/>
@@ -12689,8 +12945,8 @@
       <c r="E248" s="25"/>
       <c r="F248" s="25"/>
       <c r="G248" s="25"/>
-      <c r="H248" s="48"/>
-      <c r="I248" s="48"/>
+      <c r="H248" s="50"/>
+      <c r="I248" s="50"/>
       <c r="J248" s="25"/>
       <c r="K248" s="25"/>
       <c r="L248" s="25"/>
@@ -12714,8 +12970,8 @@
       <c r="E249" s="25"/>
       <c r="F249" s="25"/>
       <c r="G249" s="25"/>
-      <c r="H249" s="48"/>
-      <c r="I249" s="48"/>
+      <c r="H249" s="50"/>
+      <c r="I249" s="50"/>
       <c r="J249" s="25"/>
       <c r="K249" s="25"/>
       <c r="L249" s="25"/>
@@ -12739,8 +12995,8 @@
       <c r="E250" s="25"/>
       <c r="F250" s="25"/>
       <c r="G250" s="25"/>
-      <c r="H250" s="48"/>
-      <c r="I250" s="48"/>
+      <c r="H250" s="50"/>
+      <c r="I250" s="50"/>
       <c r="J250" s="25"/>
       <c r="K250" s="25"/>
       <c r="L250" s="25"/>
@@ -12764,8 +13020,8 @@
       <c r="E251" s="25"/>
       <c r="F251" s="25"/>
       <c r="G251" s="25"/>
-      <c r="H251" s="48"/>
-      <c r="I251" s="48"/>
+      <c r="H251" s="50"/>
+      <c r="I251" s="50"/>
       <c r="J251" s="25"/>
       <c r="K251" s="25"/>
       <c r="L251" s="25"/>
@@ -12789,8 +13045,8 @@
       <c r="E252" s="25"/>
       <c r="F252" s="25"/>
       <c r="G252" s="25"/>
-      <c r="H252" s="48"/>
-      <c r="I252" s="48"/>
+      <c r="H252" s="50"/>
+      <c r="I252" s="50"/>
       <c r="J252" s="25"/>
       <c r="K252" s="25"/>
       <c r="L252" s="25"/>
@@ -12814,8 +13070,8 @@
       <c r="E253" s="25"/>
       <c r="F253" s="25"/>
       <c r="G253" s="25"/>
-      <c r="H253" s="48"/>
-      <c r="I253" s="48"/>
+      <c r="H253" s="50"/>
+      <c r="I253" s="50"/>
       <c r="J253" s="25"/>
       <c r="K253" s="25"/>
       <c r="L253" s="25"/>
@@ -12839,8 +13095,8 @@
       <c r="E254" s="25"/>
       <c r="F254" s="25"/>
       <c r="G254" s="25"/>
-      <c r="H254" s="48"/>
-      <c r="I254" s="48"/>
+      <c r="H254" s="50"/>
+      <c r="I254" s="50"/>
       <c r="J254" s="25"/>
       <c r="K254" s="25"/>
       <c r="L254" s="25"/>
@@ -12864,8 +13120,8 @@
       <c r="E255" s="25"/>
       <c r="F255" s="25"/>
       <c r="G255" s="25"/>
-      <c r="H255" s="48"/>
-      <c r="I255" s="48"/>
+      <c r="H255" s="50"/>
+      <c r="I255" s="50"/>
       <c r="J255" s="25"/>
       <c r="K255" s="25"/>
       <c r="L255" s="25"/>
@@ -12889,8 +13145,8 @@
       <c r="E256" s="25"/>
       <c r="F256" s="25"/>
       <c r="G256" s="25"/>
-      <c r="H256" s="48"/>
-      <c r="I256" s="48"/>
+      <c r="H256" s="50"/>
+      <c r="I256" s="50"/>
       <c r="J256" s="25"/>
       <c r="K256" s="25"/>
       <c r="L256" s="25"/>
@@ -12914,8 +13170,8 @@
       <c r="E257" s="25"/>
       <c r="F257" s="25"/>
       <c r="G257" s="25"/>
-      <c r="H257" s="48"/>
-      <c r="I257" s="48"/>
+      <c r="H257" s="50"/>
+      <c r="I257" s="50"/>
       <c r="J257" s="25"/>
       <c r="K257" s="25"/>
       <c r="L257" s="25"/>
@@ -12939,8 +13195,8 @@
       <c r="E258" s="25"/>
       <c r="F258" s="25"/>
       <c r="G258" s="25"/>
-      <c r="H258" s="48"/>
-      <c r="I258" s="48"/>
+      <c r="H258" s="50"/>
+      <c r="I258" s="50"/>
       <c r="J258" s="25"/>
       <c r="K258" s="25"/>
       <c r="L258" s="25"/>
@@ -12964,8 +13220,8 @@
       <c r="E259" s="25"/>
       <c r="F259" s="25"/>
       <c r="G259" s="25"/>
-      <c r="H259" s="48"/>
-      <c r="I259" s="48"/>
+      <c r="H259" s="50"/>
+      <c r="I259" s="50"/>
       <c r="J259" s="25"/>
       <c r="K259" s="25"/>
       <c r="L259" s="25"/>
@@ -12989,8 +13245,8 @@
       <c r="E260" s="25"/>
       <c r="F260" s="25"/>
       <c r="G260" s="25"/>
-      <c r="H260" s="48"/>
-      <c r="I260" s="48"/>
+      <c r="H260" s="50"/>
+      <c r="I260" s="50"/>
       <c r="J260" s="25"/>
       <c r="K260" s="25"/>
       <c r="L260" s="25"/>
@@ -13014,8 +13270,8 @@
       <c r="E261" s="25"/>
       <c r="F261" s="25"/>
       <c r="G261" s="25"/>
-      <c r="H261" s="48"/>
-      <c r="I261" s="48"/>
+      <c r="H261" s="50"/>
+      <c r="I261" s="50"/>
       <c r="J261" s="25"/>
       <c r="K261" s="25"/>
       <c r="L261" s="25"/>
@@ -13039,8 +13295,8 @@
       <c r="E262" s="25"/>
       <c r="F262" s="25"/>
       <c r="G262" s="25"/>
-      <c r="H262" s="48"/>
-      <c r="I262" s="48"/>
+      <c r="H262" s="50"/>
+      <c r="I262" s="50"/>
       <c r="J262" s="25"/>
       <c r="K262" s="25"/>
       <c r="L262" s="25"/>
@@ -13064,8 +13320,8 @@
       <c r="E263" s="25"/>
       <c r="F263" s="25"/>
       <c r="G263" s="25"/>
-      <c r="H263" s="48"/>
-      <c r="I263" s="48"/>
+      <c r="H263" s="50"/>
+      <c r="I263" s="50"/>
       <c r="J263" s="25"/>
       <c r="K263" s="25"/>
       <c r="L263" s="25"/>
@@ -13089,8 +13345,8 @@
       <c r="E264" s="25"/>
       <c r="F264" s="25"/>
       <c r="G264" s="25"/>
-      <c r="H264" s="48"/>
-      <c r="I264" s="48"/>
+      <c r="H264" s="50"/>
+      <c r="I264" s="50"/>
       <c r="J264" s="25"/>
       <c r="K264" s="25"/>
       <c r="L264" s="25"/>
@@ -13114,8 +13370,8 @@
       <c r="E265" s="25"/>
       <c r="F265" s="25"/>
       <c r="G265" s="25"/>
-      <c r="H265" s="48"/>
-      <c r="I265" s="48"/>
+      <c r="H265" s="50"/>
+      <c r="I265" s="50"/>
       <c r="J265" s="25"/>
       <c r="K265" s="25"/>
       <c r="L265" s="25"/>
@@ -13139,8 +13395,8 @@
       <c r="E266" s="25"/>
       <c r="F266" s="25"/>
       <c r="G266" s="25"/>
-      <c r="H266" s="48"/>
-      <c r="I266" s="48"/>
+      <c r="H266" s="50"/>
+      <c r="I266" s="50"/>
       <c r="J266" s="25"/>
       <c r="K266" s="25"/>
       <c r="L266" s="25"/>
@@ -13164,8 +13420,8 @@
       <c r="E267" s="25"/>
       <c r="F267" s="25"/>
       <c r="G267" s="25"/>
-      <c r="H267" s="48"/>
-      <c r="I267" s="48"/>
+      <c r="H267" s="50"/>
+      <c r="I267" s="50"/>
       <c r="J267" s="25"/>
       <c r="K267" s="25"/>
       <c r="L267" s="25"/>
@@ -13189,8 +13445,8 @@
       <c r="E268" s="25"/>
       <c r="F268" s="25"/>
       <c r="G268" s="25"/>
-      <c r="H268" s="48"/>
-      <c r="I268" s="48"/>
+      <c r="H268" s="50"/>
+      <c r="I268" s="50"/>
       <c r="J268" s="25"/>
       <c r="K268" s="25"/>
       <c r="L268" s="25"/>
@@ -13214,8 +13470,8 @@
       <c r="E269" s="25"/>
       <c r="F269" s="25"/>
       <c r="G269" s="25"/>
-      <c r="H269" s="48"/>
-      <c r="I269" s="48"/>
+      <c r="H269" s="50"/>
+      <c r="I269" s="50"/>
       <c r="J269" s="25"/>
       <c r="K269" s="25"/>
       <c r="L269" s="25"/>
@@ -13239,8 +13495,8 @@
       <c r="E270" s="25"/>
       <c r="F270" s="25"/>
       <c r="G270" s="25"/>
-      <c r="H270" s="48"/>
-      <c r="I270" s="48"/>
+      <c r="H270" s="50"/>
+      <c r="I270" s="50"/>
       <c r="J270" s="25"/>
       <c r="K270" s="25"/>
       <c r="L270" s="25"/>
@@ -13264,8 +13520,8 @@
       <c r="E271" s="25"/>
       <c r="F271" s="25"/>
       <c r="G271" s="25"/>
-      <c r="H271" s="48"/>
-      <c r="I271" s="48"/>
+      <c r="H271" s="50"/>
+      <c r="I271" s="50"/>
       <c r="J271" s="25"/>
       <c r="K271" s="25"/>
       <c r="L271" s="25"/>
@@ -13289,8 +13545,8 @@
       <c r="E272" s="25"/>
       <c r="F272" s="25"/>
       <c r="G272" s="25"/>
-      <c r="H272" s="48"/>
-      <c r="I272" s="48"/>
+      <c r="H272" s="50"/>
+      <c r="I272" s="50"/>
       <c r="J272" s="25"/>
       <c r="K272" s="25"/>
       <c r="L272" s="25"/>
@@ -13314,8 +13570,8 @@
       <c r="E273" s="25"/>
       <c r="F273" s="25"/>
       <c r="G273" s="25"/>
-      <c r="H273" s="48"/>
-      <c r="I273" s="48"/>
+      <c r="H273" s="50"/>
+      <c r="I273" s="50"/>
       <c r="J273" s="25"/>
       <c r="K273" s="25"/>
       <c r="L273" s="25"/>
@@ -13339,8 +13595,8 @@
       <c r="E274" s="25"/>
       <c r="F274" s="25"/>
       <c r="G274" s="25"/>
-      <c r="H274" s="48"/>
-      <c r="I274" s="48"/>
+      <c r="H274" s="50"/>
+      <c r="I274" s="50"/>
       <c r="J274" s="25"/>
       <c r="K274" s="25"/>
       <c r="L274" s="25"/>
@@ -13364,8 +13620,8 @@
       <c r="E275" s="25"/>
       <c r="F275" s="25"/>
       <c r="G275" s="25"/>
-      <c r="H275" s="48"/>
-      <c r="I275" s="48"/>
+      <c r="H275" s="50"/>
+      <c r="I275" s="50"/>
       <c r="J275" s="25"/>
       <c r="K275" s="25"/>
       <c r="L275" s="25"/>
@@ -13389,8 +13645,8 @@
       <c r="E276" s="25"/>
       <c r="F276" s="25"/>
       <c r="G276" s="25"/>
-      <c r="H276" s="48"/>
-      <c r="I276" s="48"/>
+      <c r="H276" s="50"/>
+      <c r="I276" s="50"/>
       <c r="J276" s="25"/>
       <c r="K276" s="25"/>
       <c r="L276" s="25"/>
@@ -13414,8 +13670,8 @@
       <c r="E277" s="25"/>
       <c r="F277" s="25"/>
       <c r="G277" s="25"/>
-      <c r="H277" s="48"/>
-      <c r="I277" s="48"/>
+      <c r="H277" s="50"/>
+      <c r="I277" s="50"/>
       <c r="J277" s="25"/>
       <c r="K277" s="25"/>
       <c r="L277" s="25"/>
@@ -13439,8 +13695,8 @@
       <c r="E278" s="25"/>
       <c r="F278" s="25"/>
       <c r="G278" s="25"/>
-      <c r="H278" s="48"/>
-      <c r="I278" s="48"/>
+      <c r="H278" s="50"/>
+      <c r="I278" s="50"/>
       <c r="J278" s="25"/>
       <c r="N278" s="25"/>
       <c r="O278" s="25"/>
@@ -13461,8 +13717,8 @@
       <c r="E279" s="25"/>
       <c r="F279" s="25"/>
       <c r="G279" s="25"/>
-      <c r="H279" s="48"/>
-      <c r="I279" s="48"/>
+      <c r="H279" s="50"/>
+      <c r="I279" s="50"/>
       <c r="J279" s="25"/>
       <c r="N279" s="25"/>
       <c r="O279" s="25"/>
@@ -13483,8 +13739,8 @@
       <c r="E280" s="29"/>
       <c r="F280" s="25"/>
       <c r="G280" s="25"/>
-      <c r="H280" s="48"/>
-      <c r="I280" s="48"/>
+      <c r="H280" s="50"/>
+      <c r="I280" s="50"/>
       <c r="J280" s="25"/>
       <c r="N280" s="25"/>
       <c r="O280" s="25"/>
@@ -13509,8 +13765,8 @@
       </c>
       <c r="F281" s="25"/>
       <c r="G281" s="25"/>
-      <c r="H281" s="48"/>
-      <c r="I281" s="48"/>
+      <c r="H281" s="50"/>
+      <c r="I281" s="50"/>
       <c r="J281" s="25"/>
       <c r="K281" s="25" t="s">
         <v>724</v>
@@ -13544,8 +13800,8 @@
       </c>
       <c r="F282" s="25"/>
       <c r="G282" s="25"/>
-      <c r="H282" s="48"/>
-      <c r="I282" s="48"/>
+      <c r="H282" s="50"/>
+      <c r="I282" s="50"/>
       <c r="J282" s="25"/>
       <c r="K282" s="25" t="s">
         <v>725</v>
@@ -13573,8 +13829,8 @@
       <c r="E283" s="25"/>
       <c r="F283" s="25"/>
       <c r="G283" s="25"/>
-      <c r="H283" s="48"/>
-      <c r="I283" s="48"/>
+      <c r="H283" s="50"/>
+      <c r="I283" s="50"/>
       <c r="J283" s="25"/>
       <c r="K283" s="25"/>
       <c r="L283" s="25"/>
@@ -13598,8 +13854,8 @@
       <c r="E284" s="25"/>
       <c r="F284" s="25"/>
       <c r="G284" s="25"/>
-      <c r="H284" s="48"/>
-      <c r="I284" s="48"/>
+      <c r="H284" s="50"/>
+      <c r="I284" s="50"/>
       <c r="J284" s="25"/>
       <c r="K284" s="25"/>
       <c r="L284" s="25"/>
@@ -13623,8 +13879,8 @@
       <c r="E285" s="25"/>
       <c r="F285" s="25"/>
       <c r="G285" s="25"/>
-      <c r="H285" s="48"/>
-      <c r="I285" s="48"/>
+      <c r="H285" s="50"/>
+      <c r="I285" s="50"/>
       <c r="J285" s="25"/>
       <c r="K285" s="25"/>
       <c r="L285" s="25"/>
@@ -13648,8 +13904,8 @@
       <c r="E286" s="25"/>
       <c r="F286" s="25"/>
       <c r="G286" s="25"/>
-      <c r="H286" s="48"/>
-      <c r="I286" s="48"/>
+      <c r="H286" s="50"/>
+      <c r="I286" s="50"/>
       <c r="J286" s="25"/>
       <c r="K286" s="25"/>
       <c r="L286" s="25"/>
@@ -13673,8 +13929,8 @@
       <c r="E287" s="25"/>
       <c r="F287" s="25"/>
       <c r="G287" s="25"/>
-      <c r="H287" s="48"/>
-      <c r="I287" s="48"/>
+      <c r="H287" s="50"/>
+      <c r="I287" s="50"/>
       <c r="J287" s="25"/>
       <c r="K287" s="25"/>
       <c r="L287" s="25"/>
@@ -13698,8 +13954,8 @@
       <c r="E288" s="25"/>
       <c r="F288" s="25"/>
       <c r="G288" s="25"/>
-      <c r="H288" s="48"/>
-      <c r="I288" s="48"/>
+      <c r="H288" s="50"/>
+      <c r="I288" s="50"/>
       <c r="J288" s="25"/>
       <c r="K288" s="25"/>
       <c r="L288" s="25"/>
@@ -13723,8 +13979,8 @@
       <c r="E289" s="25"/>
       <c r="F289" s="25"/>
       <c r="G289" s="25"/>
-      <c r="H289" s="48"/>
-      <c r="I289" s="48"/>
+      <c r="H289" s="50"/>
+      <c r="I289" s="50"/>
       <c r="J289" s="25"/>
       <c r="K289" s="25"/>
       <c r="L289" s="25"/>
@@ -13748,8 +14004,8 @@
       <c r="E290" s="25"/>
       <c r="F290" s="25"/>
       <c r="G290" s="25"/>
-      <c r="H290" s="48"/>
-      <c r="I290" s="48"/>
+      <c r="H290" s="50"/>
+      <c r="I290" s="50"/>
       <c r="J290" s="25"/>
       <c r="K290" s="25"/>
       <c r="L290" s="25"/>
@@ -13773,8 +14029,8 @@
       <c r="E291" s="25"/>
       <c r="F291" s="25"/>
       <c r="G291" s="25"/>
-      <c r="H291" s="48"/>
-      <c r="I291" s="48"/>
+      <c r="H291" s="50"/>
+      <c r="I291" s="50"/>
       <c r="J291" s="25"/>
       <c r="K291" s="25"/>
       <c r="L291" s="25"/>
@@ -13798,8 +14054,8 @@
       <c r="E292" s="25"/>
       <c r="F292" s="25"/>
       <c r="G292" s="25"/>
-      <c r="H292" s="48"/>
-      <c r="I292" s="48"/>
+      <c r="H292" s="50"/>
+      <c r="I292" s="50"/>
       <c r="J292" s="25"/>
       <c r="K292" s="25"/>
       <c r="L292" s="25"/>
@@ -13823,8 +14079,8 @@
       <c r="E293" s="25"/>
       <c r="F293" s="25"/>
       <c r="G293" s="25"/>
-      <c r="H293" s="48"/>
-      <c r="I293" s="48"/>
+      <c r="H293" s="50"/>
+      <c r="I293" s="50"/>
       <c r="J293" s="25"/>
       <c r="K293" s="25"/>
       <c r="L293" s="25"/>
@@ -13848,8 +14104,8 @@
       <c r="E294" s="25"/>
       <c r="F294" s="25"/>
       <c r="G294" s="25"/>
-      <c r="H294" s="48"/>
-      <c r="I294" s="48"/>
+      <c r="H294" s="50"/>
+      <c r="I294" s="50"/>
       <c r="J294" s="25"/>
       <c r="K294" s="25"/>
       <c r="L294" s="25"/>
@@ -13873,8 +14129,8 @@
       <c r="E295" s="25"/>
       <c r="F295" s="25"/>
       <c r="G295" s="25"/>
-      <c r="H295" s="48"/>
-      <c r="I295" s="48"/>
+      <c r="H295" s="50"/>
+      <c r="I295" s="50"/>
       <c r="J295" s="25"/>
       <c r="K295" s="25"/>
       <c r="L295" s="25"/>
@@ -13898,8 +14154,8 @@
       <c r="E296" s="25"/>
       <c r="F296" s="25"/>
       <c r="G296" s="25"/>
-      <c r="H296" s="48"/>
-      <c r="I296" s="48"/>
+      <c r="H296" s="50"/>
+      <c r="I296" s="50"/>
       <c r="J296" s="25"/>
       <c r="K296" s="25"/>
       <c r="L296" s="25"/>
@@ -13923,8 +14179,8 @@
       <c r="E297" s="25"/>
       <c r="F297" s="25"/>
       <c r="G297" s="25"/>
-      <c r="H297" s="48"/>
-      <c r="I297" s="48"/>
+      <c r="H297" s="50"/>
+      <c r="I297" s="50"/>
       <c r="J297" s="25"/>
       <c r="K297" s="25"/>
       <c r="L297" s="25"/>
@@ -13948,8 +14204,8 @@
       <c r="E298" s="25"/>
       <c r="F298" s="25"/>
       <c r="G298" s="25"/>
-      <c r="H298" s="48"/>
-      <c r="I298" s="48"/>
+      <c r="H298" s="50"/>
+      <c r="I298" s="50"/>
       <c r="J298" s="25"/>
       <c r="K298" s="25"/>
       <c r="L298" s="25"/>
@@ -13973,8 +14229,8 @@
       <c r="E299" s="25"/>
       <c r="F299" s="25"/>
       <c r="G299" s="25"/>
-      <c r="H299" s="48"/>
-      <c r="I299" s="48"/>
+      <c r="H299" s="50"/>
+      <c r="I299" s="50"/>
       <c r="J299" s="25"/>
       <c r="K299" s="25"/>
       <c r="L299" s="25"/>
@@ -13998,8 +14254,8 @@
       <c r="E300" s="25"/>
       <c r="F300" s="25"/>
       <c r="G300" s="25"/>
-      <c r="H300" s="48"/>
-      <c r="I300" s="48"/>
+      <c r="H300" s="50"/>
+      <c r="I300" s="50"/>
       <c r="J300" s="25"/>
       <c r="K300" s="25"/>
       <c r="L300" s="25"/>
@@ -14023,8 +14279,8 @@
       <c r="E301" s="25"/>
       <c r="F301" s="25"/>
       <c r="G301" s="25"/>
-      <c r="H301" s="48"/>
-      <c r="I301" s="48"/>
+      <c r="H301" s="50"/>
+      <c r="I301" s="50"/>
       <c r="J301" s="25"/>
       <c r="K301" s="25"/>
       <c r="L301" s="25"/>
@@ -14048,8 +14304,8 @@
       <c r="E302" s="25"/>
       <c r="F302" s="25"/>
       <c r="G302" s="25"/>
-      <c r="H302" s="48"/>
-      <c r="I302" s="48"/>
+      <c r="H302" s="50"/>
+      <c r="I302" s="50"/>
       <c r="J302" s="25"/>
       <c r="K302" s="25"/>
       <c r="L302" s="25"/>
@@ -14073,8 +14329,8 @@
       <c r="E303" s="25"/>
       <c r="F303" s="25"/>
       <c r="G303" s="25"/>
-      <c r="H303" s="48"/>
-      <c r="I303" s="48"/>
+      <c r="H303" s="50"/>
+      <c r="I303" s="50"/>
       <c r="J303" s="25"/>
       <c r="K303" s="25"/>
       <c r="L303" s="25"/>
@@ -14098,8 +14354,8 @@
       <c r="E304" s="25"/>
       <c r="F304" s="25"/>
       <c r="G304" s="25"/>
-      <c r="H304" s="48"/>
-      <c r="I304" s="48"/>
+      <c r="H304" s="50"/>
+      <c r="I304" s="50"/>
       <c r="J304" s="25"/>
       <c r="K304" s="25"/>
       <c r="L304" s="25"/>
@@ -14123,8 +14379,8 @@
       <c r="E305" s="25"/>
       <c r="F305" s="25"/>
       <c r="G305" s="25"/>
-      <c r="H305" s="48"/>
-      <c r="I305" s="48"/>
+      <c r="H305" s="50"/>
+      <c r="I305" s="50"/>
       <c r="J305" s="25"/>
       <c r="K305" s="25"/>
       <c r="L305" s="25"/>
@@ -14148,8 +14404,8 @@
       <c r="E306" s="25"/>
       <c r="F306" s="25"/>
       <c r="G306" s="25"/>
-      <c r="H306" s="48"/>
-      <c r="I306" s="48"/>
+      <c r="H306" s="50"/>
+      <c r="I306" s="50"/>
       <c r="J306" s="25"/>
       <c r="K306" s="25"/>
       <c r="L306" s="25"/>
@@ -14173,8 +14429,8 @@
       <c r="E307" s="25"/>
       <c r="F307" s="25"/>
       <c r="G307" s="25"/>
-      <c r="H307" s="48"/>
-      <c r="I307" s="48"/>
+      <c r="H307" s="50"/>
+      <c r="I307" s="50"/>
       <c r="J307" s="25"/>
       <c r="K307" s="25"/>
       <c r="L307" s="25"/>
@@ -14198,8 +14454,8 @@
       <c r="E308" s="25"/>
       <c r="F308" s="25"/>
       <c r="G308" s="25"/>
-      <c r="H308" s="48"/>
-      <c r="I308" s="48"/>
+      <c r="H308" s="50"/>
+      <c r="I308" s="50"/>
       <c r="J308" s="25"/>
       <c r="K308" s="25"/>
       <c r="L308" s="25"/>
@@ -14223,8 +14479,8 @@
       <c r="E309" s="25"/>
       <c r="F309" s="25"/>
       <c r="G309" s="25"/>
-      <c r="H309" s="48"/>
-      <c r="I309" s="48"/>
+      <c r="H309" s="50"/>
+      <c r="I309" s="50"/>
       <c r="J309" s="25"/>
       <c r="K309" s="25"/>
       <c r="L309" s="25"/>
@@ -14248,8 +14504,8 @@
       <c r="E310" s="25"/>
       <c r="F310" s="25"/>
       <c r="G310" s="25"/>
-      <c r="H310" s="48"/>
-      <c r="I310" s="48"/>
+      <c r="H310" s="50"/>
+      <c r="I310" s="50"/>
       <c r="J310" s="25"/>
       <c r="K310" s="25"/>
       <c r="L310" s="25"/>
@@ -14273,8 +14529,8 @@
       <c r="E311" s="25"/>
       <c r="F311" s="25"/>
       <c r="G311" s="25"/>
-      <c r="H311" s="48"/>
-      <c r="I311" s="48"/>
+      <c r="H311" s="50"/>
+      <c r="I311" s="50"/>
       <c r="J311" s="25"/>
       <c r="K311" s="25"/>
       <c r="L311" s="25"/>
@@ -14298,8 +14554,8 @@
       <c r="E312" s="25"/>
       <c r="F312" s="25"/>
       <c r="G312" s="25"/>
-      <c r="H312" s="48"/>
-      <c r="I312" s="48"/>
+      <c r="H312" s="50"/>
+      <c r="I312" s="50"/>
       <c r="J312" s="25"/>
       <c r="K312" s="25"/>
       <c r="L312" s="25"/>
@@ -14323,8 +14579,8 @@
       <c r="E313" s="25"/>
       <c r="F313" s="25"/>
       <c r="G313" s="25"/>
-      <c r="H313" s="48"/>
-      <c r="I313" s="48"/>
+      <c r="H313" s="50"/>
+      <c r="I313" s="50"/>
       <c r="J313" s="25"/>
       <c r="K313" s="25"/>
       <c r="L313" s="25"/>
@@ -14348,8 +14604,8 @@
       <c r="E314" s="25"/>
       <c r="F314" s="25"/>
       <c r="G314" s="25"/>
-      <c r="H314" s="48"/>
-      <c r="I314" s="48"/>
+      <c r="H314" s="50"/>
+      <c r="I314" s="50"/>
       <c r="J314" s="25"/>
       <c r="K314" s="25"/>
       <c r="L314" s="25"/>
@@ -14373,8 +14629,8 @@
       <c r="E315" s="25"/>
       <c r="F315" s="25"/>
       <c r="G315" s="25"/>
-      <c r="H315" s="48"/>
-      <c r="I315" s="48"/>
+      <c r="H315" s="50"/>
+      <c r="I315" s="50"/>
       <c r="J315" s="25"/>
       <c r="K315" s="25"/>
       <c r="L315" s="25"/>
@@ -14398,8 +14654,8 @@
       <c r="E316" s="25"/>
       <c r="F316" s="25"/>
       <c r="G316" s="25"/>
-      <c r="H316" s="48"/>
-      <c r="I316" s="48"/>
+      <c r="H316" s="50"/>
+      <c r="I316" s="50"/>
       <c r="J316" s="25"/>
       <c r="K316" s="25"/>
       <c r="L316" s="25"/>
@@ -14423,8 +14679,8 @@
       <c r="E317" s="25"/>
       <c r="F317" s="25"/>
       <c r="G317" s="25"/>
-      <c r="H317" s="48"/>
-      <c r="I317" s="48"/>
+      <c r="H317" s="50"/>
+      <c r="I317" s="50"/>
       <c r="J317" s="25"/>
       <c r="K317" s="25"/>
       <c r="L317" s="25"/>
@@ -14448,8 +14704,8 @@
       <c r="E318" s="25"/>
       <c r="F318" s="25"/>
       <c r="G318" s="25"/>
-      <c r="H318" s="48"/>
-      <c r="I318" s="48"/>
+      <c r="H318" s="50"/>
+      <c r="I318" s="50"/>
       <c r="J318" s="25"/>
       <c r="K318" s="25"/>
       <c r="L318" s="25"/>
@@ -14473,8 +14729,8 @@
       <c r="E319" s="25"/>
       <c r="F319" s="25"/>
       <c r="G319" s="25"/>
-      <c r="H319" s="48"/>
-      <c r="I319" s="48"/>
+      <c r="H319" s="50"/>
+      <c r="I319" s="50"/>
       <c r="J319" s="25"/>
       <c r="K319" s="25"/>
       <c r="L319" s="25"/>
@@ -14498,8 +14754,8 @@
       <c r="E320" s="25"/>
       <c r="F320" s="25"/>
       <c r="G320" s="25"/>
-      <c r="H320" s="48"/>
-      <c r="I320" s="48"/>
+      <c r="H320" s="50"/>
+      <c r="I320" s="50"/>
       <c r="J320" s="25"/>
       <c r="K320" s="25"/>
       <c r="L320" s="25"/>
@@ -14523,8 +14779,8 @@
       <c r="E321" s="25"/>
       <c r="F321" s="25"/>
       <c r="G321" s="25"/>
-      <c r="H321" s="48"/>
-      <c r="I321" s="48"/>
+      <c r="H321" s="50"/>
+      <c r="I321" s="50"/>
       <c r="J321" s="25"/>
       <c r="K321" s="25"/>
       <c r="L321" s="25"/>
@@ -14548,8 +14804,8 @@
       <c r="E322" s="25"/>
       <c r="F322" s="25"/>
       <c r="G322" s="25"/>
-      <c r="H322" s="48"/>
-      <c r="I322" s="48"/>
+      <c r="H322" s="50"/>
+      <c r="I322" s="50"/>
       <c r="J322" s="25"/>
       <c r="K322" s="25"/>
       <c r="L322" s="25"/>
@@ -14573,8 +14829,8 @@
       <c r="E323" s="25"/>
       <c r="F323" s="25"/>
       <c r="G323" s="25"/>
-      <c r="H323" s="48"/>
-      <c r="I323" s="48"/>
+      <c r="H323" s="50"/>
+      <c r="I323" s="50"/>
       <c r="J323" s="25"/>
       <c r="K323" s="25"/>
       <c r="L323" s="25"/>
@@ -14598,8 +14854,8 @@
       <c r="E324" s="25"/>
       <c r="F324" s="25"/>
       <c r="G324" s="25"/>
-      <c r="H324" s="48"/>
-      <c r="I324" s="48"/>
+      <c r="H324" s="50"/>
+      <c r="I324" s="50"/>
       <c r="J324" s="25"/>
       <c r="K324" s="25"/>
       <c r="L324" s="25"/>
@@ -14623,8 +14879,8 @@
       <c r="E325" s="25"/>
       <c r="F325" s="25"/>
       <c r="G325" s="25"/>
-      <c r="H325" s="48"/>
-      <c r="I325" s="48"/>
+      <c r="H325" s="50"/>
+      <c r="I325" s="50"/>
       <c r="J325" s="25"/>
       <c r="K325" s="25"/>
       <c r="L325" s="25"/>
@@ -14648,8 +14904,8 @@
       <c r="E326" s="25"/>
       <c r="F326" s="25"/>
       <c r="G326" s="25"/>
-      <c r="H326" s="48"/>
-      <c r="I326" s="48"/>
+      <c r="H326" s="50"/>
+      <c r="I326" s="50"/>
       <c r="J326" s="25"/>
       <c r="K326" s="25"/>
       <c r="L326" s="25"/>
@@ -14673,8 +14929,8 @@
       <c r="E327" s="25"/>
       <c r="F327" s="25"/>
       <c r="G327" s="25"/>
-      <c r="H327" s="48"/>
-      <c r="I327" s="48"/>
+      <c r="H327" s="50"/>
+      <c r="I327" s="50"/>
       <c r="J327" s="25"/>
       <c r="K327" s="25"/>
       <c r="L327" s="25"/>
@@ -14698,8 +14954,8 @@
       <c r="E328" s="25"/>
       <c r="F328" s="25"/>
       <c r="G328" s="25"/>
-      <c r="H328" s="48"/>
-      <c r="I328" s="48"/>
+      <c r="H328" s="50"/>
+      <c r="I328" s="50"/>
       <c r="J328" s="25"/>
       <c r="K328" s="25"/>
       <c r="L328" s="25"/>
@@ -14723,8 +14979,8 @@
       <c r="E329" s="25"/>
       <c r="F329" s="25"/>
       <c r="G329" s="25"/>
-      <c r="H329" s="48"/>
-      <c r="I329" s="48"/>
+      <c r="H329" s="50"/>
+      <c r="I329" s="50"/>
       <c r="J329" s="25"/>
       <c r="K329" s="25"/>
       <c r="L329" s="25"/>
@@ -14748,8 +15004,8 @@
       <c r="E330" s="25"/>
       <c r="F330" s="25"/>
       <c r="G330" s="25"/>
-      <c r="H330" s="48"/>
-      <c r="I330" s="48"/>
+      <c r="H330" s="50"/>
+      <c r="I330" s="50"/>
       <c r="J330" s="25"/>
       <c r="K330" s="25"/>
       <c r="L330" s="25"/>
@@ -14773,8 +15029,8 @@
       <c r="E331" s="25"/>
       <c r="F331" s="25"/>
       <c r="G331" s="25"/>
-      <c r="H331" s="48"/>
-      <c r="I331" s="48"/>
+      <c r="H331" s="50"/>
+      <c r="I331" s="50"/>
       <c r="J331" s="25"/>
       <c r="K331" s="25"/>
       <c r="L331" s="25"/>
@@ -14798,8 +15054,8 @@
       <c r="E332" s="25"/>
       <c r="F332" s="25"/>
       <c r="G332" s="25"/>
-      <c r="H332" s="48"/>
-      <c r="I332" s="48"/>
+      <c r="H332" s="50"/>
+      <c r="I332" s="50"/>
       <c r="J332" s="25"/>
       <c r="K332" s="25"/>
       <c r="L332" s="25"/>
@@ -14823,8 +15079,8 @@
       <c r="E333" s="25"/>
       <c r="F333" s="25"/>
       <c r="G333" s="25"/>
-      <c r="H333" s="48"/>
-      <c r="I333" s="48"/>
+      <c r="H333" s="50"/>
+      <c r="I333" s="50"/>
       <c r="J333" s="25"/>
       <c r="K333" s="25"/>
       <c r="L333" s="25"/>
@@ -14848,8 +15104,8 @@
       <c r="E334" s="25"/>
       <c r="F334" s="25"/>
       <c r="G334" s="25"/>
-      <c r="H334" s="48"/>
-      <c r="I334" s="48"/>
+      <c r="H334" s="50"/>
+      <c r="I334" s="50"/>
       <c r="J334" s="25"/>
       <c r="K334" s="25"/>
       <c r="L334" s="25"/>
@@ -14873,8 +15129,8 @@
       <c r="E335" s="25"/>
       <c r="F335" s="25"/>
       <c r="G335" s="25"/>
-      <c r="H335" s="48"/>
-      <c r="I335" s="48"/>
+      <c r="H335" s="50"/>
+      <c r="I335" s="50"/>
       <c r="J335" s="25"/>
       <c r="K335" s="25"/>
       <c r="L335" s="25"/>
@@ -14898,8 +15154,8 @@
       <c r="E336" s="25"/>
       <c r="F336" s="25"/>
       <c r="G336" s="25"/>
-      <c r="H336" s="48"/>
-      <c r="I336" s="48"/>
+      <c r="H336" s="50"/>
+      <c r="I336" s="50"/>
       <c r="J336" s="25"/>
       <c r="K336" s="25"/>
       <c r="L336" s="25"/>
@@ -14923,8 +15179,8 @@
       <c r="E337" s="25"/>
       <c r="F337" s="25"/>
       <c r="G337" s="25"/>
-      <c r="H337" s="48"/>
-      <c r="I337" s="48"/>
+      <c r="H337" s="50"/>
+      <c r="I337" s="50"/>
       <c r="J337" s="25"/>
       <c r="K337" s="25"/>
       <c r="L337" s="25"/>
@@ -14948,8 +15204,8 @@
       <c r="E338" s="25"/>
       <c r="F338" s="25"/>
       <c r="G338" s="25"/>
-      <c r="H338" s="48"/>
-      <c r="I338" s="48"/>
+      <c r="H338" s="50"/>
+      <c r="I338" s="50"/>
       <c r="J338" s="25"/>
       <c r="K338" s="25"/>
       <c r="L338" s="25"/>
@@ -14973,8 +15229,8 @@
       <c r="E339" s="25"/>
       <c r="F339" s="25"/>
       <c r="G339" s="25"/>
-      <c r="H339" s="48"/>
-      <c r="I339" s="48"/>
+      <c r="H339" s="50"/>
+      <c r="I339" s="50"/>
       <c r="J339" s="25"/>
       <c r="K339" s="25"/>
       <c r="L339" s="25"/>
@@ -14998,8 +15254,8 @@
       <c r="E340" s="25"/>
       <c r="F340" s="25"/>
       <c r="G340" s="25"/>
-      <c r="H340" s="48"/>
-      <c r="I340" s="48"/>
+      <c r="H340" s="50"/>
+      <c r="I340" s="50"/>
       <c r="J340" s="25"/>
       <c r="K340" s="25"/>
       <c r="L340" s="25"/>
@@ -15377,10 +15633,10 @@
       <c r="C2" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
       <c r="J2" s="25" t="s">
@@ -15403,10 +15659,10 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="25"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25" t="s">
@@ -15429,10 +15685,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="25"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
       <c r="H4" s="25"/>
       <c r="I4" s="25"/>
       <c r="J4" s="25" t="s">
@@ -15455,10 +15711,10 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="25"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="J5" s="25" t="s">
@@ -15485,10 +15741,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="25"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
@@ -15507,10 +15763,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="25"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
@@ -15529,10 +15785,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="25"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="J8" s="25"/>
@@ -15551,10 +15807,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="25"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="J9" s="25"/>
@@ -15573,10 +15829,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="25"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
@@ -15595,10 +15851,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="25"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="J11" s="25"/>
@@ -15617,10 +15873,10 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="25"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
@@ -15639,10 +15895,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
       <c r="J13" s="25"/>
@@ -15661,10 +15917,10 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
       <c r="J14" s="25"/>
@@ -15683,10 +15939,10 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="J15" s="25"/>
@@ -15705,10 +15961,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="25"/>
@@ -15727,10 +15983,10 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
       <c r="H17" s="25"/>
       <c r="I17" s="25"/>
       <c r="J17" s="25"/>
@@ -15749,10 +16005,10 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
       <c r="H18" s="25"/>
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
@@ -15771,10 +16027,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
@@ -15793,10 +16049,10 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
       <c r="H20" s="25"/>
       <c r="I20" s="25"/>
       <c r="J20" s="25"/>
@@ -15815,10 +16071,10 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
       <c r="J21" s="25"/>
@@ -15837,10 +16093,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="25"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
       <c r="J22" s="25"/>
@@ -15859,10 +16115,10 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
       <c r="J23" s="25"/>
@@ -15881,10 +16137,10 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
       <c r="J24" s="25"/>
@@ -15903,10 +16159,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
       <c r="J25" s="25"/>
@@ -15925,10 +16181,10 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="25"/>
@@ -15947,10 +16203,10 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="25"/>
@@ -15969,10 +16225,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="25"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
       <c r="H28" s="25"/>
       <c r="I28" s="25"/>
       <c r="J28" s="25"/>
@@ -15991,10 +16247,10 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="25"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="J29" s="25"/>
@@ -16013,10 +16269,10 @@
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="J30" s="25"/>
@@ -16035,10 +16291,10 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
@@ -16057,10 +16313,10 @@
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
@@ -16079,10 +16335,10 @@
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
@@ -16101,10 +16357,10 @@
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
@@ -16123,10 +16379,10 @@
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
@@ -16145,10 +16401,10 @@
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="25"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="J36" s="25"/>
@@ -16167,10 +16423,10 @@
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
@@ -16189,10 +16445,10 @@
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
       <c r="H38" s="25"/>
       <c r="I38" s="25"/>
       <c r="J38" s="25"/>
@@ -16211,10 +16467,10 @@
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
       <c r="H39" s="25"/>
       <c r="I39" s="25"/>
       <c r="J39" s="25"/>
@@ -16233,10 +16489,10 @@
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
       <c r="H40" s="25"/>
       <c r="I40" s="25"/>
       <c r="J40" s="25"/>
@@ -16255,10 +16511,10 @@
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
       <c r="H41" s="25"/>
       <c r="I41" s="25"/>
       <c r="J41" s="25"/>
@@ -16277,10 +16533,10 @@
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
       <c r="H42" s="25"/>
       <c r="I42" s="25"/>
       <c r="J42" s="25"/>
@@ -16299,10 +16555,10 @@
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
       <c r="H43" s="25"/>
       <c r="I43" s="25"/>
       <c r="J43" s="25"/>
@@ -16321,10 +16577,10 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
       <c r="H44" s="25"/>
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
@@ -16343,10 +16599,10 @@
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
       <c r="H45" s="25"/>
       <c r="I45" s="25"/>
       <c r="J45" s="25"/>
@@ -16365,10 +16621,10 @@
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="25"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
       <c r="H46" s="25"/>
       <c r="I46" s="25"/>
       <c r="J46" s="25"/>
@@ -16387,10 +16643,10 @@
       </c>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
       <c r="H47" s="25"/>
       <c r="I47" s="25"/>
       <c r="J47" s="25"/>
@@ -16409,10 +16665,10 @@
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
       <c r="H48" s="25"/>
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
@@ -16431,10 +16687,10 @@
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="25"/>
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
@@ -16453,10 +16709,10 @@
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
       <c r="H50" s="25"/>
       <c r="I50" s="25"/>
       <c r="J50" s="25"/>
@@ -16475,10 +16731,10 @@
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="25"/>
       <c r="I51" s="25"/>
       <c r="J51" s="25"/>
@@ -16497,10 +16753,10 @@
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="25"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
       <c r="H52" s="25"/>
       <c r="I52" s="25"/>
       <c r="J52" s="25"/>
@@ -16519,10 +16775,10 @@
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
       <c r="H53" s="25"/>
       <c r="I53" s="25"/>
       <c r="J53" s="25"/>
@@ -16541,10 +16797,10 @@
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="25"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
+      <c r="D54" s="50"/>
+      <c r="E54" s="50"/>
+      <c r="F54" s="50"/>
+      <c r="G54" s="50"/>
       <c r="H54" s="25"/>
       <c r="I54" s="25"/>
       <c r="J54" s="25"/>
@@ -16563,10 +16819,10 @@
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
       <c r="H55" s="25"/>
       <c r="I55" s="25"/>
       <c r="J55" s="25"/>
@@ -16585,10 +16841,10 @@
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="25"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
       <c r="H56" s="25"/>
       <c r="I56" s="25"/>
       <c r="J56" s="25"/>
@@ -16607,10 +16863,10 @@
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
       <c r="H57" s="25"/>
       <c r="I57" s="25"/>
       <c r="J57" s="25"/>
@@ -16629,10 +16885,10 @@
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="25"/>
       <c r="I58" s="25"/>
       <c r="J58" s="25"/>
@@ -16651,10 +16907,10 @@
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
+      <c r="D59" s="50"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
       <c r="H59" s="25"/>
       <c r="I59" s="25"/>
       <c r="J59" s="25"/>
@@ -16673,10 +16929,10 @@
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
       <c r="H60" s="25"/>
       <c r="I60" s="25"/>
       <c r="J60" s="25"/>
@@ -16695,10 +16951,10 @@
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
+      <c r="D61" s="50"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
       <c r="H61" s="25"/>
       <c r="I61" s="25"/>
       <c r="J61" s="25"/>
@@ -16717,10 +16973,10 @@
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
+      <c r="D62" s="50"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
       <c r="H62" s="25"/>
       <c r="I62" s="25"/>
       <c r="J62" s="25"/>
@@ -16739,10 +16995,10 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
       <c r="H63" s="25"/>
       <c r="I63" s="25"/>
       <c r="J63" s="25"/>
@@ -16761,10 +17017,10 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="25"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50"/>
       <c r="H64" s="25"/>
       <c r="I64" s="25"/>
       <c r="J64" s="25"/>
@@ -16783,10 +17039,10 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="25"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
       <c r="H65" s="25"/>
       <c r="I65" s="25"/>
       <c r="J65" s="25"/>
@@ -16805,10 +17061,10 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="25"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
       <c r="H66" s="25"/>
       <c r="I66" s="25"/>
       <c r="J66" s="25"/>
@@ -16827,10 +17083,10 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="25"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
       <c r="H67" s="25"/>
       <c r="I67" s="25"/>
       <c r="J67" s="25"/>
@@ -16849,10 +17105,10 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
+      <c r="D68" s="50"/>
+      <c r="E68" s="50"/>
+      <c r="F68" s="50"/>
+      <c r="G68" s="50"/>
       <c r="H68" s="25"/>
       <c r="I68" s="25"/>
       <c r="J68" s="25"/>
@@ -16871,10 +17127,10 @@
       </c>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="25"/>
       <c r="I69" s="25"/>
       <c r="J69" s="25"/>
@@ -16893,8 +17149,8 @@
       </c>
       <c r="B70" s="25"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
       <c r="F70" s="31"/>
       <c r="G70" s="31"/>
       <c r="H70" s="31"/>
@@ -16915,8 +17171,8 @@
       </c>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
       <c r="F71" s="31"/>
       <c r="G71" s="31"/>
       <c r="H71" s="31"/>
@@ -16937,8 +17193,8 @@
       </c>
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
       <c r="F72" s="31"/>
       <c r="G72" s="31"/>
       <c r="H72" s="31"/>
@@ -16959,10 +17215,10 @@
       </c>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
       <c r="H73" s="25"/>
       <c r="I73" s="25"/>
       <c r="J73" s="25"/>
@@ -16981,8 +17237,8 @@
       </c>
       <c r="B74" s="25"/>
       <c r="C74" s="25"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
       <c r="F74" s="31"/>
       <c r="G74" s="31"/>
       <c r="H74" s="31"/>
@@ -17003,8 +17259,8 @@
       </c>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
       <c r="F75" s="31"/>
       <c r="G75" s="31"/>
       <c r="H75" s="31"/>
@@ -17025,8 +17281,8 @@
       </c>
       <c r="B76" s="25"/>
       <c r="C76" s="25"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
       <c r="F76" s="31"/>
       <c r="G76" s="31"/>
       <c r="H76" s="31"/>
@@ -17047,8 +17303,8 @@
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
+      <c r="D77" s="50"/>
+      <c r="E77" s="50"/>
       <c r="F77" s="31"/>
       <c r="G77" s="31"/>
       <c r="H77" s="31"/>
@@ -17069,8 +17325,8 @@
       </c>
       <c r="B78" s="25"/>
       <c r="C78" s="25"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
       <c r="F78" s="31"/>
       <c r="G78" s="31"/>
       <c r="H78" s="31"/>
@@ -17091,10 +17347,10 @@
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
       <c r="H79" s="25"/>
       <c r="I79" s="25"/>
       <c r="J79" s="25"/>
@@ -17113,10 +17369,10 @@
       </c>
       <c r="B80" s="25"/>
       <c r="C80" s="25"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
       <c r="H80" s="25"/>
       <c r="I80" s="25"/>
       <c r="J80" s="25"/>
@@ -17135,10 +17391,10 @@
       </c>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
       <c r="H81" s="25"/>
       <c r="I81" s="25"/>
       <c r="J81" s="25"/>
@@ -17157,10 +17413,10 @@
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="25"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
       <c r="H82" s="25"/>
       <c r="I82" s="25"/>
       <c r="J82" s="25"/>
@@ -17179,10 +17435,10 @@
       </c>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
       <c r="H83" s="25"/>
       <c r="I83" s="25"/>
       <c r="J83" s="25"/>
@@ -17201,10 +17457,10 @@
       </c>
       <c r="B84" s="25"/>
       <c r="C84" s="25"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
       <c r="H84" s="25"/>
       <c r="I84" s="25"/>
       <c r="J84" s="25"/>
@@ -17223,10 +17479,10 @@
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
       <c r="H85" s="25"/>
       <c r="I85" s="25"/>
       <c r="J85" s="25"/>
@@ -17245,10 +17501,10 @@
       </c>
       <c r="B86" s="25"/>
       <c r="C86" s="25"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
       <c r="H86" s="25"/>
       <c r="I86" s="25"/>
       <c r="J86" s="25"/>
@@ -17267,10 +17523,10 @@
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
       <c r="H87" s="25"/>
       <c r="I87" s="25"/>
       <c r="J87" s="25"/>
@@ -17289,10 +17545,10 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="25"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
       <c r="H88" s="25"/>
       <c r="I88" s="25"/>
       <c r="J88" s="25"/>
@@ -17311,10 +17567,10 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="25"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="48"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
       <c r="H89" s="25"/>
       <c r="I89" s="25"/>
       <c r="J89" s="25"/>
@@ -17333,10 +17589,10 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="25"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="48"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50"/>
       <c r="H90" s="25"/>
       <c r="I90" s="25"/>
       <c r="J90" s="25"/>
@@ -17355,10 +17611,10 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="25"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
       <c r="H91" s="25"/>
       <c r="I91" s="25"/>
       <c r="J91" s="25"/>
@@ -17377,10 +17633,10 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="25"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="50"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
       <c r="H92" s="25"/>
       <c r="I92" s="25"/>
       <c r="J92" s="25"/>
@@ -17399,10 +17655,10 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="25"/>
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
       <c r="H93" s="25"/>
       <c r="I93" s="25"/>
       <c r="J93" s="25"/>
@@ -17421,10 +17677,10 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="25"/>
-      <c r="D94" s="48"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="50"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
       <c r="H94" s="25"/>
       <c r="I94" s="25"/>
       <c r="J94" s="25"/>
@@ -17443,10 +17699,10 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="25"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
+      <c r="D95" s="50"/>
+      <c r="E95" s="50"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50"/>
       <c r="H95" s="25"/>
       <c r="I95" s="25"/>
       <c r="J95" s="25"/>
@@ -17465,10 +17721,10 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="25"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
       <c r="H96" s="25"/>
       <c r="I96" s="25"/>
       <c r="J96" s="25"/>
@@ -17487,10 +17743,10 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="25"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
       <c r="H97" s="25"/>
       <c r="I97" s="25"/>
       <c r="J97" s="25"/>
@@ -17509,10 +17765,10 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="25"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="50"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
       <c r="H98" s="25"/>
       <c r="I98" s="25"/>
       <c r="J98" s="25"/>
@@ -17531,10 +17787,10 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="25"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
       <c r="H99" s="25"/>
       <c r="I99" s="25"/>
       <c r="J99" s="25"/>
@@ -17553,10 +17809,10 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="25"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
       <c r="H100" s="25"/>
       <c r="I100" s="25"/>
       <c r="J100" s="25"/>
@@ -17575,10 +17831,10 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="25"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
       <c r="H101" s="25"/>
       <c r="I101" s="25"/>
       <c r="J101" s="25"/>
@@ -17597,10 +17853,10 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="25"/>
-      <c r="D102" s="48"/>
-      <c r="E102" s="48"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50"/>
       <c r="H102" s="25"/>
       <c r="I102" s="25"/>
       <c r="J102" s="25"/>
@@ -17619,10 +17875,10 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="25"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="48"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="50"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50"/>
       <c r="H103" s="25"/>
       <c r="I103" s="25"/>
       <c r="J103" s="25"/>
@@ -17641,10 +17897,10 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="25"/>
-      <c r="D104" s="48"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="48"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="50"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50"/>
       <c r="H104" s="25"/>
       <c r="I104" s="25"/>
       <c r="J104" s="25"/>
@@ -17663,10 +17919,10 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="25"/>
-      <c r="D105" s="48"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="48"/>
+      <c r="D105" s="50"/>
+      <c r="E105" s="50"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50"/>
       <c r="H105" s="25"/>
       <c r="I105" s="25"/>
       <c r="J105" s="25"/>
@@ -17685,10 +17941,10 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="25"/>
-      <c r="D106" s="48"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="48"/>
+      <c r="D106" s="50"/>
+      <c r="E106" s="50"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50"/>
       <c r="H106" s="25"/>
       <c r="I106" s="25"/>
       <c r="J106" s="25"/>
@@ -17707,10 +17963,10 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="25"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="48"/>
-      <c r="F107" s="48"/>
-      <c r="G107" s="48"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="50"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50"/>
       <c r="H107" s="25"/>
       <c r="I107" s="25"/>
       <c r="J107" s="25"/>
@@ -17729,10 +17985,10 @@
       </c>
       <c r="B108" s="25"/>
       <c r="C108" s="25"/>
-      <c r="D108" s="48"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="48"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
+      <c r="F108" s="50"/>
+      <c r="G108" s="50"/>
       <c r="H108" s="25"/>
       <c r="I108" s="25"/>
       <c r="J108" s="25"/>
@@ -17751,10 +18007,10 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="25"/>
-      <c r="D109" s="48"/>
-      <c r="E109" s="48"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="48"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="25"/>
       <c r="I109" s="25"/>
       <c r="J109" s="25"/>
@@ -17773,10 +18029,10 @@
       </c>
       <c r="B110" s="25"/>
       <c r="C110" s="25"/>
-      <c r="D110" s="48"/>
-      <c r="E110" s="48"/>
-      <c r="F110" s="48"/>
-      <c r="G110" s="48"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="50"/>
+      <c r="F110" s="50"/>
+      <c r="G110" s="50"/>
       <c r="H110" s="25"/>
       <c r="I110" s="25"/>
       <c r="J110" s="25"/>
@@ -17795,10 +18051,10 @@
       </c>
       <c r="B111" s="25"/>
       <c r="C111" s="25"/>
-      <c r="D111" s="48"/>
-      <c r="E111" s="48"/>
-      <c r="F111" s="48"/>
-      <c r="G111" s="48"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="50"/>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
       <c r="H111" s="25"/>
       <c r="I111" s="25"/>
       <c r="J111" s="25"/>
@@ -17819,10 +18075,10 @@
       <c r="C112" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D112" s="49"/>
-      <c r="E112" s="48"/>
-      <c r="F112" s="48"/>
-      <c r="G112" s="48"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="50"/>
+      <c r="F112" s="50"/>
+      <c r="G112" s="50"/>
       <c r="H112" s="25"/>
       <c r="I112" s="25"/>
       <c r="J112" s="25" t="s">
@@ -17845,10 +18101,10 @@
       </c>
       <c r="B113" s="25"/>
       <c r="C113" s="25"/>
-      <c r="D113" s="48"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="48"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="50"/>
+      <c r="G113" s="50"/>
       <c r="H113" s="25"/>
       <c r="I113" s="25"/>
       <c r="J113" s="25" t="s">
@@ -17871,10 +18127,10 @@
       </c>
       <c r="B114" s="25"/>
       <c r="C114" s="25"/>
-      <c r="D114" s="48"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="48"/>
+      <c r="D114" s="50"/>
+      <c r="E114" s="50"/>
+      <c r="F114" s="50"/>
+      <c r="G114" s="50"/>
       <c r="H114" s="25"/>
       <c r="I114" s="25"/>
       <c r="J114" s="25" t="s">
@@ -17897,10 +18153,10 @@
       </c>
       <c r="B115" s="25"/>
       <c r="C115" s="25"/>
-      <c r="D115" s="48"/>
-      <c r="E115" s="48"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="48"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="50"/>
+      <c r="F115" s="50"/>
+      <c r="G115" s="50"/>
       <c r="H115" s="25"/>
       <c r="I115" s="25"/>
       <c r="J115" s="25" t="s">
@@ -17927,10 +18183,10 @@
       </c>
       <c r="B116" s="25"/>
       <c r="C116" s="25"/>
-      <c r="D116" s="48"/>
-      <c r="E116" s="48"/>
-      <c r="F116" s="48"/>
-      <c r="G116" s="48"/>
+      <c r="D116" s="50"/>
+      <c r="E116" s="50"/>
+      <c r="F116" s="50"/>
+      <c r="G116" s="50"/>
       <c r="H116" s="25"/>
       <c r="I116" s="25"/>
       <c r="J116" s="25"/>
@@ -17949,10 +18205,10 @@
       </c>
       <c r="B117" s="25"/>
       <c r="C117" s="25"/>
-      <c r="D117" s="48"/>
-      <c r="E117" s="48"/>
-      <c r="F117" s="48"/>
-      <c r="G117" s="48"/>
+      <c r="D117" s="50"/>
+      <c r="E117" s="50"/>
+      <c r="F117" s="50"/>
+      <c r="G117" s="50"/>
       <c r="H117" s="25"/>
       <c r="I117" s="25"/>
       <c r="J117" s="25"/>
@@ -17971,10 +18227,10 @@
       </c>
       <c r="B118" s="25"/>
       <c r="C118" s="25"/>
-      <c r="D118" s="48"/>
-      <c r="E118" s="48"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="48"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="50"/>
+      <c r="F118" s="50"/>
+      <c r="G118" s="50"/>
       <c r="H118" s="25"/>
       <c r="I118" s="25"/>
       <c r="J118" s="25"/>
@@ -17993,10 +18249,10 @@
       </c>
       <c r="B119" s="25"/>
       <c r="C119" s="25"/>
-      <c r="D119" s="48"/>
-      <c r="E119" s="48"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="48"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="50"/>
+      <c r="F119" s="50"/>
+      <c r="G119" s="50"/>
       <c r="H119" s="25"/>
       <c r="I119" s="25"/>
       <c r="J119" s="25"/>
@@ -18015,10 +18271,10 @@
       </c>
       <c r="B120" s="25"/>
       <c r="C120" s="25"/>
-      <c r="D120" s="48"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
+      <c r="D120" s="50"/>
+      <c r="E120" s="50"/>
+      <c r="F120" s="50"/>
+      <c r="G120" s="50"/>
       <c r="H120" s="25"/>
       <c r="I120" s="25"/>
       <c r="J120" s="25"/>
@@ -18037,10 +18293,10 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="25"/>
-      <c r="D121" s="48"/>
-      <c r="E121" s="48"/>
-      <c r="F121" s="48"/>
-      <c r="G121" s="48"/>
+      <c r="D121" s="50"/>
+      <c r="E121" s="50"/>
+      <c r="F121" s="50"/>
+      <c r="G121" s="50"/>
       <c r="H121" s="25"/>
       <c r="I121" s="25"/>
       <c r="J121" s="25" t="s">
@@ -18065,10 +18321,10 @@
       <c r="C122" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D122" s="49"/>
-      <c r="E122" s="48"/>
-      <c r="F122" s="48"/>
-      <c r="G122" s="48"/>
+      <c r="D122" s="51"/>
+      <c r="E122" s="50"/>
+      <c r="F122" s="50"/>
+      <c r="G122" s="50"/>
       <c r="H122" s="25"/>
       <c r="I122" s="25"/>
       <c r="J122" s="25" t="s">
@@ -18091,10 +18347,10 @@
       </c>
       <c r="B123" s="25"/>
       <c r="C123" s="25"/>
-      <c r="D123" s="48"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="48"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
+      <c r="G123" s="50"/>
       <c r="H123" s="25"/>
       <c r="I123" s="25"/>
       <c r="J123" s="25" t="s">
@@ -18117,10 +18373,10 @@
       </c>
       <c r="B124" s="25"/>
       <c r="C124" s="25"/>
-      <c r="D124" s="48"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="48"/>
-      <c r="G124" s="48"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="50"/>
+      <c r="G124" s="50"/>
       <c r="H124" s="25"/>
       <c r="I124" s="25"/>
       <c r="J124" s="25" t="s">
@@ -18147,10 +18403,10 @@
       </c>
       <c r="B125" s="25"/>
       <c r="C125" s="25"/>
-      <c r="D125" s="48"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="48"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
+      <c r="F125" s="50"/>
+      <c r="G125" s="50"/>
       <c r="H125" s="25"/>
       <c r="I125" s="25"/>
       <c r="J125" s="25"/>
@@ -18169,10 +18425,10 @@
       </c>
       <c r="B126" s="25"/>
       <c r="C126" s="25"/>
-      <c r="D126" s="48"/>
-      <c r="E126" s="48"/>
-      <c r="F126" s="48"/>
-      <c r="G126" s="48"/>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50"/>
+      <c r="F126" s="50"/>
+      <c r="G126" s="50"/>
       <c r="H126" s="25"/>
       <c r="I126" s="25"/>
       <c r="J126" s="25"/>
@@ -18191,10 +18447,10 @@
       </c>
       <c r="B127" s="25"/>
       <c r="C127" s="25"/>
-      <c r="D127" s="48"/>
-      <c r="E127" s="48"/>
-      <c r="F127" s="48"/>
-      <c r="G127" s="48"/>
+      <c r="D127" s="50"/>
+      <c r="E127" s="50"/>
+      <c r="F127" s="50"/>
+      <c r="G127" s="50"/>
       <c r="H127" s="25"/>
       <c r="I127" s="25"/>
       <c r="J127" s="25"/>
@@ -18213,10 +18469,10 @@
       </c>
       <c r="B128" s="25"/>
       <c r="C128" s="25"/>
-      <c r="D128" s="48"/>
-      <c r="E128" s="48"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="48"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="50"/>
+      <c r="F128" s="50"/>
+      <c r="G128" s="50"/>
       <c r="H128" s="25"/>
       <c r="I128" s="25"/>
       <c r="J128" s="25"/>
@@ -18235,10 +18491,10 @@
       </c>
       <c r="B129" s="25"/>
       <c r="C129" s="25"/>
-      <c r="D129" s="48"/>
-      <c r="E129" s="48"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="48"/>
+      <c r="D129" s="50"/>
+      <c r="E129" s="50"/>
+      <c r="F129" s="50"/>
+      <c r="G129" s="50"/>
       <c r="H129" s="25"/>
       <c r="I129" s="25"/>
       <c r="J129" s="25"/>
@@ -18257,10 +18513,10 @@
       </c>
       <c r="B130" s="25"/>
       <c r="C130" s="25"/>
-      <c r="D130" s="48"/>
-      <c r="E130" s="48"/>
-      <c r="F130" s="48"/>
-      <c r="G130" s="48"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="50"/>
+      <c r="F130" s="50"/>
+      <c r="G130" s="50"/>
       <c r="H130" s="25"/>
       <c r="I130" s="25"/>
       <c r="J130" s="25"/>
@@ -18279,10 +18535,10 @@
       </c>
       <c r="B131" s="25"/>
       <c r="C131" s="25"/>
-      <c r="D131" s="48"/>
-      <c r="E131" s="48"/>
-      <c r="F131" s="48"/>
-      <c r="G131" s="48"/>
+      <c r="D131" s="50"/>
+      <c r="E131" s="50"/>
+      <c r="F131" s="50"/>
+      <c r="G131" s="50"/>
       <c r="H131" s="25"/>
       <c r="I131" s="25"/>
       <c r="J131" s="25"/>
@@ -18301,10 +18557,10 @@
       </c>
       <c r="B132" s="25"/>
       <c r="C132" s="25"/>
-      <c r="D132" s="48"/>
-      <c r="E132" s="48"/>
-      <c r="F132" s="48"/>
-      <c r="G132" s="48"/>
+      <c r="D132" s="50"/>
+      <c r="E132" s="50"/>
+      <c r="F132" s="50"/>
+      <c r="G132" s="50"/>
       <c r="H132" s="25"/>
       <c r="I132" s="25"/>
       <c r="J132" s="25"/>
@@ -18323,10 +18579,10 @@
       </c>
       <c r="B133" s="25"/>
       <c r="C133" s="25"/>
-      <c r="D133" s="48"/>
-      <c r="E133" s="48"/>
-      <c r="F133" s="48"/>
-      <c r="G133" s="48"/>
+      <c r="D133" s="50"/>
+      <c r="E133" s="50"/>
+      <c r="F133" s="50"/>
+      <c r="G133" s="50"/>
       <c r="H133" s="25"/>
       <c r="I133" s="25"/>
       <c r="J133" s="25"/>
@@ -18345,10 +18601,10 @@
       </c>
       <c r="B134" s="25"/>
       <c r="C134" s="25"/>
-      <c r="D134" s="48"/>
-      <c r="E134" s="48"/>
-      <c r="F134" s="48"/>
-      <c r="G134" s="48"/>
+      <c r="D134" s="50"/>
+      <c r="E134" s="50"/>
+      <c r="F134" s="50"/>
+      <c r="G134" s="50"/>
       <c r="H134" s="25"/>
       <c r="I134" s="25"/>
       <c r="J134" s="25"/>
@@ -18367,10 +18623,10 @@
       </c>
       <c r="B135" s="25"/>
       <c r="C135" s="25"/>
-      <c r="D135" s="48"/>
-      <c r="E135" s="48"/>
-      <c r="F135" s="48"/>
-      <c r="G135" s="48"/>
+      <c r="D135" s="50"/>
+      <c r="E135" s="50"/>
+      <c r="F135" s="50"/>
+      <c r="G135" s="50"/>
       <c r="H135" s="25"/>
       <c r="I135" s="25"/>
       <c r="J135" s="25"/>
@@ -18389,10 +18645,10 @@
       </c>
       <c r="B136" s="25"/>
       <c r="C136" s="25"/>
-      <c r="D136" s="48"/>
-      <c r="E136" s="48"/>
-      <c r="F136" s="48"/>
-      <c r="G136" s="48"/>
+      <c r="D136" s="50"/>
+      <c r="E136" s="50"/>
+      <c r="F136" s="50"/>
+      <c r="G136" s="50"/>
       <c r="H136" s="25"/>
       <c r="I136" s="25"/>
       <c r="J136" s="25"/>
@@ -18411,10 +18667,10 @@
       </c>
       <c r="B137" s="25"/>
       <c r="C137" s="25"/>
-      <c r="D137" s="48"/>
-      <c r="E137" s="48"/>
-      <c r="F137" s="48"/>
-      <c r="G137" s="48"/>
+      <c r="D137" s="50"/>
+      <c r="E137" s="50"/>
+      <c r="F137" s="50"/>
+      <c r="G137" s="50"/>
       <c r="H137" s="25"/>
       <c r="I137" s="25"/>
       <c r="J137" s="25"/>
@@ -18433,10 +18689,10 @@
       </c>
       <c r="B138" s="25"/>
       <c r="C138" s="25"/>
-      <c r="D138" s="48"/>
-      <c r="E138" s="48"/>
-      <c r="F138" s="48"/>
-      <c r="G138" s="48"/>
+      <c r="D138" s="50"/>
+      <c r="E138" s="50"/>
+      <c r="F138" s="50"/>
+      <c r="G138" s="50"/>
       <c r="H138" s="25"/>
       <c r="I138" s="25"/>
       <c r="J138" s="25"/>
@@ -18455,10 +18711,10 @@
       </c>
       <c r="B139" s="25"/>
       <c r="C139" s="25"/>
-      <c r="D139" s="48"/>
-      <c r="E139" s="48"/>
-      <c r="F139" s="48"/>
-      <c r="G139" s="48"/>
+      <c r="D139" s="50"/>
+      <c r="E139" s="50"/>
+      <c r="F139" s="50"/>
+      <c r="G139" s="50"/>
       <c r="H139" s="25"/>
       <c r="I139" s="25"/>
       <c r="J139" s="25"/>
@@ -18477,10 +18733,10 @@
       </c>
       <c r="B140" s="25"/>
       <c r="C140" s="25"/>
-      <c r="D140" s="48"/>
-      <c r="E140" s="48"/>
-      <c r="F140" s="48"/>
-      <c r="G140" s="48"/>
+      <c r="D140" s="50"/>
+      <c r="E140" s="50"/>
+      <c r="F140" s="50"/>
+      <c r="G140" s="50"/>
       <c r="H140" s="25"/>
       <c r="I140" s="25"/>
       <c r="J140" s="25"/>
@@ -18499,10 +18755,10 @@
       </c>
       <c r="B141" s="25"/>
       <c r="C141" s="25"/>
-      <c r="D141" s="48"/>
-      <c r="E141" s="48"/>
-      <c r="F141" s="48"/>
-      <c r="G141" s="48"/>
+      <c r="D141" s="50"/>
+      <c r="E141" s="50"/>
+      <c r="F141" s="50"/>
+      <c r="G141" s="50"/>
       <c r="H141" s="25"/>
       <c r="I141" s="25"/>
       <c r="J141" s="25"/>
@@ -18521,10 +18777,10 @@
       </c>
       <c r="B142" s="25"/>
       <c r="C142" s="25"/>
-      <c r="D142" s="48"/>
-      <c r="E142" s="48"/>
-      <c r="F142" s="48"/>
-      <c r="G142" s="48"/>
+      <c r="D142" s="50"/>
+      <c r="E142" s="50"/>
+      <c r="F142" s="50"/>
+      <c r="G142" s="50"/>
       <c r="H142" s="25"/>
       <c r="I142" s="25"/>
       <c r="J142" s="25"/>
@@ -18543,10 +18799,10 @@
       </c>
       <c r="B143" s="25"/>
       <c r="C143" s="25"/>
-      <c r="D143" s="48"/>
-      <c r="E143" s="48"/>
-      <c r="F143" s="48"/>
-      <c r="G143" s="48"/>
+      <c r="D143" s="50"/>
+      <c r="E143" s="50"/>
+      <c r="F143" s="50"/>
+      <c r="G143" s="50"/>
       <c r="H143" s="25"/>
       <c r="I143" s="25"/>
       <c r="J143" s="25"/>
@@ -18567,10 +18823,10 @@
       <c r="C144" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D144" s="49"/>
-      <c r="E144" s="48"/>
-      <c r="F144" s="48"/>
-      <c r="G144" s="48"/>
+      <c r="D144" s="51"/>
+      <c r="E144" s="50"/>
+      <c r="F144" s="50"/>
+      <c r="G144" s="50"/>
       <c r="H144" s="25"/>
       <c r="I144" s="25"/>
       <c r="J144" s="25" t="s">
@@ -18593,10 +18849,10 @@
       </c>
       <c r="B145" s="25"/>
       <c r="C145" s="25"/>
-      <c r="D145" s="48"/>
-      <c r="E145" s="48"/>
-      <c r="F145" s="48"/>
-      <c r="G145" s="48"/>
+      <c r="D145" s="50"/>
+      <c r="E145" s="50"/>
+      <c r="F145" s="50"/>
+      <c r="G145" s="50"/>
       <c r="H145" s="25"/>
       <c r="I145" s="25"/>
       <c r="J145" s="25" t="s">
@@ -18619,10 +18875,10 @@
       </c>
       <c r="B146" s="25"/>
       <c r="C146" s="25"/>
-      <c r="D146" s="48"/>
-      <c r="E146" s="48"/>
-      <c r="F146" s="48"/>
-      <c r="G146" s="48"/>
+      <c r="D146" s="50"/>
+      <c r="E146" s="50"/>
+      <c r="F146" s="50"/>
+      <c r="G146" s="50"/>
       <c r="H146" s="25"/>
       <c r="I146" s="25"/>
       <c r="J146" s="25" t="s">
@@ -18645,10 +18901,10 @@
       </c>
       <c r="B147" s="25"/>
       <c r="C147" s="25"/>
-      <c r="D147" s="48"/>
-      <c r="E147" s="48"/>
-      <c r="F147" s="48"/>
-      <c r="G147" s="48"/>
+      <c r="D147" s="50"/>
+      <c r="E147" s="50"/>
+      <c r="F147" s="50"/>
+      <c r="G147" s="50"/>
       <c r="H147" s="25"/>
       <c r="I147" s="25"/>
       <c r="J147" s="25" t="s">
@@ -18675,10 +18931,10 @@
       </c>
       <c r="B148" s="25"/>
       <c r="C148" s="25"/>
-      <c r="D148" s="48"/>
-      <c r="E148" s="48"/>
-      <c r="F148" s="48"/>
-      <c r="G148" s="48"/>
+      <c r="D148" s="50"/>
+      <c r="E148" s="50"/>
+      <c r="F148" s="50"/>
+      <c r="G148" s="50"/>
       <c r="H148" s="25"/>
       <c r="I148" s="25"/>
       <c r="J148" s="25"/>
@@ -18697,10 +18953,10 @@
       </c>
       <c r="B149" s="25"/>
       <c r="C149" s="25"/>
-      <c r="D149" s="48"/>
-      <c r="E149" s="48"/>
-      <c r="F149" s="48"/>
-      <c r="G149" s="48"/>
+      <c r="D149" s="50"/>
+      <c r="E149" s="50"/>
+      <c r="F149" s="50"/>
+      <c r="G149" s="50"/>
       <c r="H149" s="25"/>
       <c r="I149" s="25"/>
       <c r="J149" s="25"/>
@@ -18719,10 +18975,10 @@
       </c>
       <c r="B150" s="25"/>
       <c r="C150" s="25"/>
-      <c r="D150" s="48"/>
-      <c r="E150" s="48"/>
-      <c r="F150" s="48"/>
-      <c r="G150" s="48"/>
+      <c r="D150" s="50"/>
+      <c r="E150" s="50"/>
+      <c r="F150" s="50"/>
+      <c r="G150" s="50"/>
       <c r="H150" s="25"/>
       <c r="I150" s="25"/>
       <c r="J150" s="25"/>
@@ -18741,10 +18997,10 @@
       </c>
       <c r="B151" s="25"/>
       <c r="C151" s="25"/>
-      <c r="D151" s="48"/>
-      <c r="E151" s="48"/>
-      <c r="F151" s="48"/>
-      <c r="G151" s="48"/>
+      <c r="D151" s="50"/>
+      <c r="E151" s="50"/>
+      <c r="F151" s="50"/>
+      <c r="G151" s="50"/>
       <c r="H151" s="25"/>
       <c r="I151" s="25"/>
       <c r="J151" s="25"/>
@@ -18763,10 +19019,10 @@
       </c>
       <c r="B152" s="25"/>
       <c r="C152" s="25"/>
-      <c r="D152" s="48"/>
-      <c r="E152" s="48"/>
-      <c r="F152" s="48"/>
-      <c r="G152" s="48"/>
+      <c r="D152" s="50"/>
+      <c r="E152" s="50"/>
+      <c r="F152" s="50"/>
+      <c r="G152" s="50"/>
       <c r="H152" s="25"/>
       <c r="I152" s="25"/>
       <c r="J152" s="25"/>
@@ -18785,10 +19041,10 @@
       </c>
       <c r="B153" s="25"/>
       <c r="C153" s="25"/>
-      <c r="D153" s="48"/>
-      <c r="E153" s="48"/>
-      <c r="F153" s="48"/>
-      <c r="G153" s="48"/>
+      <c r="D153" s="50"/>
+      <c r="E153" s="50"/>
+      <c r="F153" s="50"/>
+      <c r="G153" s="50"/>
       <c r="H153" s="25"/>
       <c r="I153" s="25"/>
       <c r="J153" s="25"/>
@@ -18807,10 +19063,10 @@
       </c>
       <c r="B154" s="25"/>
       <c r="C154" s="25"/>
-      <c r="D154" s="48"/>
-      <c r="E154" s="48"/>
-      <c r="F154" s="48"/>
-      <c r="G154" s="48"/>
+      <c r="D154" s="50"/>
+      <c r="E154" s="50"/>
+      <c r="F154" s="50"/>
+      <c r="G154" s="50"/>
       <c r="H154" s="25"/>
       <c r="I154" s="25"/>
       <c r="J154" s="25"/>
@@ -18829,10 +19085,10 @@
       </c>
       <c r="B155" s="25"/>
       <c r="C155" s="25"/>
-      <c r="D155" s="48"/>
-      <c r="E155" s="48"/>
-      <c r="F155" s="48"/>
-      <c r="G155" s="48"/>
+      <c r="D155" s="50"/>
+      <c r="E155" s="50"/>
+      <c r="F155" s="50"/>
+      <c r="G155" s="50"/>
       <c r="H155" s="25"/>
       <c r="I155" s="25"/>
       <c r="J155" s="25"/>
@@ -18851,10 +19107,10 @@
       </c>
       <c r="B156" s="25"/>
       <c r="C156" s="25"/>
-      <c r="D156" s="48"/>
-      <c r="E156" s="48"/>
-      <c r="F156" s="48"/>
-      <c r="G156" s="48"/>
+      <c r="D156" s="50"/>
+      <c r="E156" s="50"/>
+      <c r="F156" s="50"/>
+      <c r="G156" s="50"/>
       <c r="H156" s="25"/>
       <c r="I156" s="25"/>
       <c r="J156" s="25"/>
@@ -18873,10 +19129,10 @@
       </c>
       <c r="B157" s="25"/>
       <c r="C157" s="25"/>
-      <c r="D157" s="48"/>
-      <c r="E157" s="48"/>
-      <c r="F157" s="48"/>
-      <c r="G157" s="48"/>
+      <c r="D157" s="50"/>
+      <c r="E157" s="50"/>
+      <c r="F157" s="50"/>
+      <c r="G157" s="50"/>
       <c r="H157" s="25"/>
       <c r="I157" s="25"/>
       <c r="J157" s="25"/>
@@ -18895,10 +19151,10 @@
       </c>
       <c r="B158" s="25"/>
       <c r="C158" s="25"/>
-      <c r="D158" s="48"/>
-      <c r="E158" s="48"/>
-      <c r="F158" s="48"/>
-      <c r="G158" s="48"/>
+      <c r="D158" s="50"/>
+      <c r="E158" s="50"/>
+      <c r="F158" s="50"/>
+      <c r="G158" s="50"/>
       <c r="H158" s="25"/>
       <c r="I158" s="25"/>
       <c r="J158" s="25"/>
@@ -18917,10 +19173,10 @@
       </c>
       <c r="B159" s="25"/>
       <c r="C159" s="25"/>
-      <c r="D159" s="48"/>
-      <c r="E159" s="48"/>
-      <c r="F159" s="48"/>
-      <c r="G159" s="48"/>
+      <c r="D159" s="50"/>
+      <c r="E159" s="50"/>
+      <c r="F159" s="50"/>
+      <c r="G159" s="50"/>
       <c r="H159" s="25"/>
       <c r="I159" s="25"/>
       <c r="J159" s="25"/>
@@ -18939,10 +19195,10 @@
       </c>
       <c r="B160" s="25"/>
       <c r="C160" s="25"/>
-      <c r="D160" s="48"/>
-      <c r="E160" s="48"/>
-      <c r="F160" s="48"/>
-      <c r="G160" s="48"/>
+      <c r="D160" s="50"/>
+      <c r="E160" s="50"/>
+      <c r="F160" s="50"/>
+      <c r="G160" s="50"/>
       <c r="H160" s="25"/>
       <c r="I160" s="25"/>
       <c r="J160" s="25"/>
@@ -18961,10 +19217,10 @@
       </c>
       <c r="B161" s="25"/>
       <c r="C161" s="25"/>
-      <c r="D161" s="48"/>
-      <c r="E161" s="48"/>
-      <c r="F161" s="48"/>
-      <c r="G161" s="48"/>
+      <c r="D161" s="50"/>
+      <c r="E161" s="50"/>
+      <c r="F161" s="50"/>
+      <c r="G161" s="50"/>
       <c r="H161" s="25"/>
       <c r="I161" s="25"/>
       <c r="J161" s="25"/>
@@ -18983,10 +19239,10 @@
       </c>
       <c r="B162" s="25"/>
       <c r="C162" s="25"/>
-      <c r="D162" s="48"/>
-      <c r="E162" s="48"/>
-      <c r="F162" s="48"/>
-      <c r="G162" s="48"/>
+      <c r="D162" s="50"/>
+      <c r="E162" s="50"/>
+      <c r="F162" s="50"/>
+      <c r="G162" s="50"/>
       <c r="H162" s="25"/>
       <c r="I162" s="25"/>
       <c r="J162" s="25"/>
@@ -19005,10 +19261,10 @@
       </c>
       <c r="B163" s="25"/>
       <c r="C163" s="25"/>
-      <c r="D163" s="48"/>
-      <c r="E163" s="48"/>
-      <c r="F163" s="48"/>
-      <c r="G163" s="48"/>
+      <c r="D163" s="50"/>
+      <c r="E163" s="50"/>
+      <c r="F163" s="50"/>
+      <c r="G163" s="50"/>
       <c r="H163" s="25"/>
       <c r="I163" s="25"/>
       <c r="J163" s="25"/>
@@ -19027,10 +19283,10 @@
       </c>
       <c r="B164" s="25"/>
       <c r="C164" s="25"/>
-      <c r="D164" s="48"/>
-      <c r="E164" s="48"/>
-      <c r="F164" s="48"/>
-      <c r="G164" s="48"/>
+      <c r="D164" s="50"/>
+      <c r="E164" s="50"/>
+      <c r="F164" s="50"/>
+      <c r="G164" s="50"/>
       <c r="H164" s="25"/>
       <c r="I164" s="25"/>
       <c r="J164" s="25"/>
@@ -19049,10 +19305,10 @@
       </c>
       <c r="B165" s="25"/>
       <c r="C165" s="25"/>
-      <c r="D165" s="48"/>
-      <c r="E165" s="48"/>
-      <c r="F165" s="48"/>
-      <c r="G165" s="48"/>
+      <c r="D165" s="50"/>
+      <c r="E165" s="50"/>
+      <c r="F165" s="50"/>
+      <c r="G165" s="50"/>
       <c r="H165" s="25"/>
       <c r="I165" s="25"/>
       <c r="J165" s="25"/>
@@ -19071,10 +19327,10 @@
       </c>
       <c r="B166" s="25"/>
       <c r="C166" s="25"/>
-      <c r="D166" s="48"/>
-      <c r="E166" s="48"/>
-      <c r="F166" s="48"/>
-      <c r="G166" s="48"/>
+      <c r="D166" s="50"/>
+      <c r="E166" s="50"/>
+      <c r="F166" s="50"/>
+      <c r="G166" s="50"/>
       <c r="H166" s="25"/>
       <c r="I166" s="25"/>
       <c r="J166" s="25"/>
@@ -19093,10 +19349,10 @@
       </c>
       <c r="B167" s="25"/>
       <c r="C167" s="25"/>
-      <c r="D167" s="48"/>
-      <c r="E167" s="48"/>
-      <c r="F167" s="48"/>
-      <c r="G167" s="48"/>
+      <c r="D167" s="50"/>
+      <c r="E167" s="50"/>
+      <c r="F167" s="50"/>
+      <c r="G167" s="50"/>
       <c r="H167" s="25"/>
       <c r="I167" s="25"/>
       <c r="J167" s="25"/>
@@ -19115,10 +19371,10 @@
       </c>
       <c r="B168" s="25"/>
       <c r="C168" s="25"/>
-      <c r="D168" s="48"/>
-      <c r="E168" s="48"/>
-      <c r="F168" s="48"/>
-      <c r="G168" s="48"/>
+      <c r="D168" s="50"/>
+      <c r="E168" s="50"/>
+      <c r="F168" s="50"/>
+      <c r="G168" s="50"/>
       <c r="H168" s="25"/>
       <c r="I168" s="25"/>
       <c r="J168" s="25"/>
@@ -19137,10 +19393,10 @@
       </c>
       <c r="B169" s="25"/>
       <c r="C169" s="25"/>
-      <c r="D169" s="48"/>
-      <c r="E169" s="48"/>
-      <c r="F169" s="48"/>
-      <c r="G169" s="48"/>
+      <c r="D169" s="50"/>
+      <c r="E169" s="50"/>
+      <c r="F169" s="50"/>
+      <c r="G169" s="50"/>
       <c r="H169" s="25"/>
       <c r="I169" s="25"/>
       <c r="J169" s="25"/>
@@ -19159,10 +19415,10 @@
       </c>
       <c r="B170" s="25"/>
       <c r="C170" s="25"/>
-      <c r="D170" s="48"/>
-      <c r="E170" s="48"/>
-      <c r="F170" s="48"/>
-      <c r="G170" s="48"/>
+      <c r="D170" s="50"/>
+      <c r="E170" s="50"/>
+      <c r="F170" s="50"/>
+      <c r="G170" s="50"/>
       <c r="H170" s="25"/>
       <c r="I170" s="25"/>
       <c r="J170" s="25"/>
@@ -19181,10 +19437,10 @@
       </c>
       <c r="B171" s="25"/>
       <c r="C171" s="25"/>
-      <c r="D171" s="48"/>
-      <c r="E171" s="48"/>
-      <c r="F171" s="48"/>
-      <c r="G171" s="48"/>
+      <c r="D171" s="50"/>
+      <c r="E171" s="50"/>
+      <c r="F171" s="50"/>
+      <c r="G171" s="50"/>
       <c r="H171" s="25"/>
       <c r="I171" s="25"/>
       <c r="J171" s="25"/>
@@ -19203,10 +19459,10 @@
       </c>
       <c r="B172" s="25"/>
       <c r="C172" s="25"/>
-      <c r="D172" s="48"/>
-      <c r="E172" s="48"/>
-      <c r="F172" s="48"/>
-      <c r="G172" s="48"/>
+      <c r="D172" s="50"/>
+      <c r="E172" s="50"/>
+      <c r="F172" s="50"/>
+      <c r="G172" s="50"/>
       <c r="H172" s="25"/>
       <c r="I172" s="25"/>
       <c r="J172" s="25"/>
@@ -19225,10 +19481,10 @@
       </c>
       <c r="B173" s="25"/>
       <c r="C173" s="25"/>
-      <c r="D173" s="48"/>
-      <c r="E173" s="48"/>
-      <c r="F173" s="48"/>
-      <c r="G173" s="48"/>
+      <c r="D173" s="50"/>
+      <c r="E173" s="50"/>
+      <c r="F173" s="50"/>
+      <c r="G173" s="50"/>
       <c r="H173" s="25"/>
       <c r="I173" s="25"/>
       <c r="J173" s="25"/>
@@ -19247,10 +19503,10 @@
       </c>
       <c r="B174" s="25"/>
       <c r="C174" s="25"/>
-      <c r="D174" s="48"/>
-      <c r="E174" s="48"/>
-      <c r="F174" s="48"/>
-      <c r="G174" s="48"/>
+      <c r="D174" s="50"/>
+      <c r="E174" s="50"/>
+      <c r="F174" s="50"/>
+      <c r="G174" s="50"/>
       <c r="H174" s="25"/>
       <c r="I174" s="25"/>
       <c r="J174" s="25"/>
@@ -19269,10 +19525,10 @@
       </c>
       <c r="B175" s="25"/>
       <c r="C175" s="25"/>
-      <c r="D175" s="48"/>
-      <c r="E175" s="48"/>
-      <c r="F175" s="48"/>
-      <c r="G175" s="48"/>
+      <c r="D175" s="50"/>
+      <c r="E175" s="50"/>
+      <c r="F175" s="50"/>
+      <c r="G175" s="50"/>
       <c r="H175" s="25"/>
       <c r="I175" s="25"/>
       <c r="J175" s="25"/>
@@ -19291,10 +19547,10 @@
       </c>
       <c r="B176" s="25"/>
       <c r="C176" s="25"/>
-      <c r="D176" s="48"/>
-      <c r="E176" s="48"/>
-      <c r="F176" s="48"/>
-      <c r="G176" s="48"/>
+      <c r="D176" s="50"/>
+      <c r="E176" s="50"/>
+      <c r="F176" s="50"/>
+      <c r="G176" s="50"/>
       <c r="H176" s="25"/>
       <c r="I176" s="25"/>
       <c r="J176" s="25"/>
@@ -19313,10 +19569,10 @@
       </c>
       <c r="B177" s="25"/>
       <c r="C177" s="25"/>
-      <c r="D177" s="48"/>
-      <c r="E177" s="48"/>
-      <c r="F177" s="48"/>
-      <c r="G177" s="48"/>
+      <c r="D177" s="50"/>
+      <c r="E177" s="50"/>
+      <c r="F177" s="50"/>
+      <c r="G177" s="50"/>
       <c r="H177" s="25"/>
       <c r="I177" s="25"/>
       <c r="J177" s="25"/>
@@ -19335,10 +19591,10 @@
       </c>
       <c r="B178" s="25"/>
       <c r="C178" s="25"/>
-      <c r="D178" s="48"/>
-      <c r="E178" s="48"/>
-      <c r="F178" s="48"/>
-      <c r="G178" s="48"/>
+      <c r="D178" s="50"/>
+      <c r="E178" s="50"/>
+      <c r="F178" s="50"/>
+      <c r="G178" s="50"/>
       <c r="H178" s="25"/>
       <c r="I178" s="25"/>
       <c r="J178" s="25"/>
@@ -19357,10 +19613,10 @@
       </c>
       <c r="B179" s="25"/>
       <c r="C179" s="25"/>
-      <c r="D179" s="48"/>
-      <c r="E179" s="48"/>
-      <c r="F179" s="48"/>
-      <c r="G179" s="48"/>
+      <c r="D179" s="50"/>
+      <c r="E179" s="50"/>
+      <c r="F179" s="50"/>
+      <c r="G179" s="50"/>
       <c r="H179" s="25"/>
       <c r="I179" s="25"/>
       <c r="J179" s="25"/>
@@ -19379,10 +19635,10 @@
       </c>
       <c r="B180" s="25"/>
       <c r="C180" s="25"/>
-      <c r="D180" s="48"/>
-      <c r="E180" s="48"/>
-      <c r="F180" s="48"/>
-      <c r="G180" s="48"/>
+      <c r="D180" s="50"/>
+      <c r="E180" s="50"/>
+      <c r="F180" s="50"/>
+      <c r="G180" s="50"/>
       <c r="H180" s="25"/>
       <c r="I180" s="25"/>
       <c r="J180" s="25"/>
@@ -19401,10 +19657,10 @@
       </c>
       <c r="B181" s="25"/>
       <c r="C181" s="25"/>
-      <c r="D181" s="48"/>
-      <c r="E181" s="48"/>
-      <c r="F181" s="48"/>
-      <c r="G181" s="48"/>
+      <c r="D181" s="50"/>
+      <c r="E181" s="50"/>
+      <c r="F181" s="50"/>
+      <c r="G181" s="50"/>
       <c r="H181" s="25"/>
       <c r="I181" s="25"/>
       <c r="J181" s="25"/>
@@ -19423,10 +19679,10 @@
       </c>
       <c r="B182" s="25"/>
       <c r="C182" s="25"/>
-      <c r="D182" s="48"/>
-      <c r="E182" s="48"/>
-      <c r="F182" s="48"/>
-      <c r="G182" s="48"/>
+      <c r="D182" s="50"/>
+      <c r="E182" s="50"/>
+      <c r="F182" s="50"/>
+      <c r="G182" s="50"/>
       <c r="H182" s="25"/>
       <c r="I182" s="25"/>
       <c r="J182" s="25"/>
@@ -19445,10 +19701,10 @@
       </c>
       <c r="B183" s="25"/>
       <c r="C183" s="25"/>
-      <c r="D183" s="48"/>
-      <c r="E183" s="48"/>
-      <c r="F183" s="48"/>
-      <c r="G183" s="48"/>
+      <c r="D183" s="50"/>
+      <c r="E183" s="50"/>
+      <c r="F183" s="50"/>
+      <c r="G183" s="50"/>
       <c r="H183" s="25"/>
       <c r="I183" s="25"/>
       <c r="J183" s="25"/>
@@ -19467,10 +19723,10 @@
       </c>
       <c r="B184" s="25"/>
       <c r="C184" s="25"/>
-      <c r="D184" s="48"/>
-      <c r="E184" s="48"/>
-      <c r="F184" s="48"/>
-      <c r="G184" s="48"/>
+      <c r="D184" s="50"/>
+      <c r="E184" s="50"/>
+      <c r="F184" s="50"/>
+      <c r="G184" s="50"/>
       <c r="H184" s="25"/>
       <c r="I184" s="25"/>
       <c r="J184" s="25"/>
@@ -19489,10 +19745,10 @@
       </c>
       <c r="B185" s="25"/>
       <c r="C185" s="25"/>
-      <c r="D185" s="48"/>
-      <c r="E185" s="48"/>
-      <c r="F185" s="48"/>
-      <c r="G185" s="48"/>
+      <c r="D185" s="50"/>
+      <c r="E185" s="50"/>
+      <c r="F185" s="50"/>
+      <c r="G185" s="50"/>
       <c r="H185" s="25"/>
       <c r="I185" s="25"/>
       <c r="J185" s="25"/>
@@ -19511,10 +19767,10 @@
       </c>
       <c r="B186" s="25"/>
       <c r="C186" s="25"/>
-      <c r="D186" s="48"/>
-      <c r="E186" s="48"/>
-      <c r="F186" s="48"/>
-      <c r="G186" s="48"/>
+      <c r="D186" s="50"/>
+      <c r="E186" s="50"/>
+      <c r="F186" s="50"/>
+      <c r="G186" s="50"/>
       <c r="H186" s="25"/>
       <c r="I186" s="25"/>
       <c r="J186" s="25"/>
@@ -19533,10 +19789,10 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="25"/>
-      <c r="D187" s="48"/>
-      <c r="E187" s="48"/>
-      <c r="F187" s="48"/>
-      <c r="G187" s="48"/>
+      <c r="D187" s="50"/>
+      <c r="E187" s="50"/>
+      <c r="F187" s="50"/>
+      <c r="G187" s="50"/>
       <c r="H187" s="25"/>
       <c r="I187" s="25"/>
       <c r="J187" s="25"/>
@@ -19555,10 +19811,10 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="25"/>
-      <c r="D188" s="48"/>
-      <c r="E188" s="48"/>
-      <c r="F188" s="48"/>
-      <c r="G188" s="48"/>
+      <c r="D188" s="50"/>
+      <c r="E188" s="50"/>
+      <c r="F188" s="50"/>
+      <c r="G188" s="50"/>
       <c r="H188" s="25"/>
       <c r="I188" s="25"/>
       <c r="J188" s="25"/>
@@ -19577,10 +19833,10 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="25"/>
-      <c r="D189" s="48"/>
-      <c r="E189" s="48"/>
-      <c r="F189" s="48"/>
-      <c r="G189" s="48"/>
+      <c r="D189" s="50"/>
+      <c r="E189" s="50"/>
+      <c r="F189" s="50"/>
+      <c r="G189" s="50"/>
       <c r="H189" s="25"/>
       <c r="I189" s="25"/>
       <c r="J189" s="25"/>
@@ -19599,10 +19855,10 @@
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="25"/>
-      <c r="D190" s="48"/>
-      <c r="E190" s="48"/>
-      <c r="F190" s="48"/>
-      <c r="G190" s="48"/>
+      <c r="D190" s="50"/>
+      <c r="E190" s="50"/>
+      <c r="F190" s="50"/>
+      <c r="G190" s="50"/>
       <c r="H190" s="25"/>
       <c r="I190" s="25"/>
       <c r="J190" s="25"/>
@@ -19621,10 +19877,10 @@
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="25"/>
-      <c r="D191" s="48"/>
-      <c r="E191" s="48"/>
-      <c r="F191" s="48"/>
-      <c r="G191" s="48"/>
+      <c r="D191" s="50"/>
+      <c r="E191" s="50"/>
+      <c r="F191" s="50"/>
+      <c r="G191" s="50"/>
       <c r="H191" s="25"/>
       <c r="I191" s="25"/>
       <c r="J191" s="25"/>
@@ -19643,10 +19899,10 @@
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="25"/>
-      <c r="D192" s="48"/>
-      <c r="E192" s="48"/>
-      <c r="F192" s="48"/>
-      <c r="G192" s="48"/>
+      <c r="D192" s="50"/>
+      <c r="E192" s="50"/>
+      <c r="F192" s="50"/>
+      <c r="G192" s="50"/>
       <c r="H192" s="25"/>
       <c r="I192" s="25"/>
       <c r="J192" s="25"/>
@@ -19665,10 +19921,10 @@
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="25"/>
-      <c r="D193" s="48"/>
-      <c r="E193" s="48"/>
-      <c r="F193" s="48"/>
-      <c r="G193" s="48"/>
+      <c r="D193" s="50"/>
+      <c r="E193" s="50"/>
+      <c r="F193" s="50"/>
+      <c r="G193" s="50"/>
       <c r="H193" s="25"/>
       <c r="I193" s="25"/>
       <c r="J193" s="25"/>
@@ -19687,10 +19943,10 @@
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="25"/>
-      <c r="D194" s="48"/>
-      <c r="E194" s="48"/>
-      <c r="F194" s="48"/>
-      <c r="G194" s="48"/>
+      <c r="D194" s="50"/>
+      <c r="E194" s="50"/>
+      <c r="F194" s="50"/>
+      <c r="G194" s="50"/>
       <c r="H194" s="25"/>
       <c r="I194" s="25"/>
       <c r="J194" s="25"/>
@@ -19709,10 +19965,10 @@
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="25"/>
-      <c r="D195" s="48"/>
-      <c r="E195" s="48"/>
-      <c r="F195" s="48"/>
-      <c r="G195" s="48"/>
+      <c r="D195" s="50"/>
+      <c r="E195" s="50"/>
+      <c r="F195" s="50"/>
+      <c r="G195" s="50"/>
       <c r="H195" s="25"/>
       <c r="I195" s="25"/>
       <c r="J195" s="25"/>
@@ -19731,10 +19987,10 @@
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="25"/>
-      <c r="D196" s="48"/>
-      <c r="E196" s="48"/>
-      <c r="F196" s="48"/>
-      <c r="G196" s="48"/>
+      <c r="D196" s="50"/>
+      <c r="E196" s="50"/>
+      <c r="F196" s="50"/>
+      <c r="G196" s="50"/>
       <c r="H196" s="25"/>
       <c r="I196" s="25"/>
       <c r="J196" s="25"/>
@@ -19753,10 +20009,10 @@
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="25"/>
-      <c r="D197" s="48"/>
-      <c r="E197" s="48"/>
-      <c r="F197" s="48"/>
-      <c r="G197" s="48"/>
+      <c r="D197" s="50"/>
+      <c r="E197" s="50"/>
+      <c r="F197" s="50"/>
+      <c r="G197" s="50"/>
       <c r="H197" s="25"/>
       <c r="I197" s="25"/>
       <c r="J197" s="25"/>
@@ -19775,10 +20031,10 @@
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="25"/>
-      <c r="D198" s="48"/>
-      <c r="E198" s="48"/>
-      <c r="F198" s="48"/>
-      <c r="G198" s="48"/>
+      <c r="D198" s="50"/>
+      <c r="E198" s="50"/>
+      <c r="F198" s="50"/>
+      <c r="G198" s="50"/>
       <c r="H198" s="25"/>
       <c r="I198" s="25"/>
       <c r="J198" s="25"/>
@@ -19797,10 +20053,10 @@
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="25"/>
-      <c r="D199" s="48"/>
-      <c r="E199" s="48"/>
-      <c r="F199" s="48"/>
-      <c r="G199" s="48"/>
+      <c r="D199" s="50"/>
+      <c r="E199" s="50"/>
+      <c r="F199" s="50"/>
+      <c r="G199" s="50"/>
       <c r="H199" s="25"/>
       <c r="I199" s="25"/>
       <c r="J199" s="25"/>
@@ -19819,10 +20075,10 @@
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="25"/>
-      <c r="D200" s="48"/>
-      <c r="E200" s="48"/>
-      <c r="F200" s="48"/>
-      <c r="G200" s="48"/>
+      <c r="D200" s="50"/>
+      <c r="E200" s="50"/>
+      <c r="F200" s="50"/>
+      <c r="G200" s="50"/>
       <c r="H200" s="25"/>
       <c r="I200" s="25"/>
       <c r="J200" s="25"/>
@@ -19841,10 +20097,10 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="25"/>
-      <c r="D201" s="48"/>
-      <c r="E201" s="48"/>
-      <c r="F201" s="48"/>
-      <c r="G201" s="48"/>
+      <c r="D201" s="50"/>
+      <c r="E201" s="50"/>
+      <c r="F201" s="50"/>
+      <c r="G201" s="50"/>
       <c r="H201" s="25"/>
       <c r="I201" s="25"/>
       <c r="J201" s="25"/>
@@ -19863,10 +20119,10 @@
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="25"/>
-      <c r="D202" s="48"/>
-      <c r="E202" s="48"/>
-      <c r="F202" s="48"/>
-      <c r="G202" s="48"/>
+      <c r="D202" s="50"/>
+      <c r="E202" s="50"/>
+      <c r="F202" s="50"/>
+      <c r="G202" s="50"/>
       <c r="H202" s="25"/>
       <c r="I202" s="25"/>
       <c r="J202" s="25"/>
@@ -19885,10 +20141,10 @@
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="25"/>
-      <c r="D203" s="48"/>
-      <c r="E203" s="48"/>
-      <c r="F203" s="48"/>
-      <c r="G203" s="48"/>
+      <c r="D203" s="50"/>
+      <c r="E203" s="50"/>
+      <c r="F203" s="50"/>
+      <c r="G203" s="50"/>
       <c r="H203" s="25"/>
       <c r="I203" s="25"/>
       <c r="J203" s="25"/>
@@ -19907,10 +20163,10 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="25"/>
-      <c r="D204" s="48"/>
-      <c r="E204" s="48"/>
-      <c r="F204" s="48"/>
-      <c r="G204" s="48"/>
+      <c r="D204" s="50"/>
+      <c r="E204" s="50"/>
+      <c r="F204" s="50"/>
+      <c r="G204" s="50"/>
       <c r="H204" s="25"/>
       <c r="I204" s="25"/>
       <c r="J204" s="25"/>
@@ -19929,10 +20185,10 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="25"/>
-      <c r="D205" s="48"/>
-      <c r="E205" s="48"/>
-      <c r="F205" s="48"/>
-      <c r="G205" s="48"/>
+      <c r="D205" s="50"/>
+      <c r="E205" s="50"/>
+      <c r="F205" s="50"/>
+      <c r="G205" s="50"/>
       <c r="H205" s="25"/>
       <c r="I205" s="25"/>
       <c r="J205" s="25"/>
@@ -19951,10 +20207,10 @@
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="25"/>
-      <c r="D206" s="48"/>
-      <c r="E206" s="48"/>
-      <c r="F206" s="48"/>
-      <c r="G206" s="48"/>
+      <c r="D206" s="50"/>
+      <c r="E206" s="50"/>
+      <c r="F206" s="50"/>
+      <c r="G206" s="50"/>
       <c r="H206" s="25"/>
       <c r="I206" s="25"/>
       <c r="J206" s="25"/>
@@ -19973,10 +20229,10 @@
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="25"/>
-      <c r="D207" s="48"/>
-      <c r="E207" s="48"/>
-      <c r="F207" s="48"/>
-      <c r="G207" s="48"/>
+      <c r="D207" s="50"/>
+      <c r="E207" s="50"/>
+      <c r="F207" s="50"/>
+      <c r="G207" s="50"/>
       <c r="H207" s="25"/>
       <c r="I207" s="25"/>
       <c r="J207" s="25"/>
@@ -19995,10 +20251,10 @@
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="25"/>
-      <c r="D208" s="48"/>
-      <c r="E208" s="48"/>
-      <c r="F208" s="48"/>
-      <c r="G208" s="48"/>
+      <c r="D208" s="50"/>
+      <c r="E208" s="50"/>
+      <c r="F208" s="50"/>
+      <c r="G208" s="50"/>
       <c r="H208" s="25"/>
       <c r="I208" s="25"/>
       <c r="J208" s="25"/>
@@ -20017,10 +20273,10 @@
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="25"/>
-      <c r="D209" s="48"/>
-      <c r="E209" s="48"/>
-      <c r="F209" s="48"/>
-      <c r="G209" s="48"/>
+      <c r="D209" s="50"/>
+      <c r="E209" s="50"/>
+      <c r="F209" s="50"/>
+      <c r="G209" s="50"/>
       <c r="H209" s="25"/>
       <c r="I209" s="25"/>
       <c r="J209" s="25"/>
@@ -20039,10 +20295,10 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="25"/>
-      <c r="D210" s="48"/>
-      <c r="E210" s="48"/>
-      <c r="F210" s="48"/>
-      <c r="G210" s="48"/>
+      <c r="D210" s="50"/>
+      <c r="E210" s="50"/>
+      <c r="F210" s="50"/>
+      <c r="G210" s="50"/>
       <c r="H210" s="25"/>
       <c r="I210" s="25"/>
       <c r="J210" s="25"/>
@@ -20061,10 +20317,10 @@
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="25"/>
-      <c r="D211" s="48"/>
-      <c r="E211" s="48"/>
-      <c r="F211" s="48"/>
-      <c r="G211" s="48"/>
+      <c r="D211" s="50"/>
+      <c r="E211" s="50"/>
+      <c r="F211" s="50"/>
+      <c r="G211" s="50"/>
       <c r="H211" s="25"/>
       <c r="I211" s="25"/>
       <c r="J211" s="25"/>
@@ -20083,10 +20339,10 @@
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="25"/>
-      <c r="D212" s="48"/>
-      <c r="E212" s="48"/>
-      <c r="F212" s="48"/>
-      <c r="G212" s="48"/>
+      <c r="D212" s="50"/>
+      <c r="E212" s="50"/>
+      <c r="F212" s="50"/>
+      <c r="G212" s="50"/>
       <c r="H212" s="25"/>
       <c r="I212" s="25"/>
       <c r="J212" s="25"/>
@@ -20105,10 +20361,10 @@
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="25"/>
-      <c r="D213" s="48"/>
-      <c r="E213" s="48"/>
-      <c r="F213" s="48"/>
-      <c r="G213" s="48"/>
+      <c r="D213" s="50"/>
+      <c r="E213" s="50"/>
+      <c r="F213" s="50"/>
+      <c r="G213" s="50"/>
       <c r="H213" s="25"/>
       <c r="I213" s="25"/>
       <c r="J213" s="25"/>
@@ -20127,10 +20383,10 @@
       </c>
       <c r="B214" s="25"/>
       <c r="C214" s="25"/>
-      <c r="D214" s="48"/>
-      <c r="E214" s="48"/>
-      <c r="F214" s="48"/>
-      <c r="G214" s="48"/>
+      <c r="D214" s="50"/>
+      <c r="E214" s="50"/>
+      <c r="F214" s="50"/>
+      <c r="G214" s="50"/>
       <c r="H214" s="25"/>
       <c r="I214" s="25"/>
       <c r="J214" s="25"/>
@@ -20149,10 +20405,10 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="25"/>
-      <c r="D215" s="48"/>
-      <c r="E215" s="48"/>
-      <c r="F215" s="48"/>
-      <c r="G215" s="48"/>
+      <c r="D215" s="50"/>
+      <c r="E215" s="50"/>
+      <c r="F215" s="50"/>
+      <c r="G215" s="50"/>
       <c r="H215" s="25"/>
       <c r="I215" s="25"/>
       <c r="J215" s="25"/>
@@ -20171,10 +20427,10 @@
       </c>
       <c r="B216" s="25"/>
       <c r="C216" s="25"/>
-      <c r="D216" s="48"/>
-      <c r="E216" s="48"/>
-      <c r="F216" s="48"/>
-      <c r="G216" s="48"/>
+      <c r="D216" s="50"/>
+      <c r="E216" s="50"/>
+      <c r="F216" s="50"/>
+      <c r="G216" s="50"/>
       <c r="H216" s="25"/>
       <c r="I216" s="25"/>
       <c r="J216" s="25"/>
@@ -20193,10 +20449,10 @@
       </c>
       <c r="B217" s="25"/>
       <c r="C217" s="25"/>
-      <c r="D217" s="48"/>
-      <c r="E217" s="48"/>
-      <c r="F217" s="48"/>
-      <c r="G217" s="48"/>
+      <c r="D217" s="50"/>
+      <c r="E217" s="50"/>
+      <c r="F217" s="50"/>
+      <c r="G217" s="50"/>
       <c r="H217" s="25"/>
       <c r="I217" s="25"/>
       <c r="J217" s="25"/>
@@ -20215,10 +20471,10 @@
       </c>
       <c r="B218" s="25"/>
       <c r="C218" s="25"/>
-      <c r="D218" s="48"/>
-      <c r="E218" s="48"/>
-      <c r="F218" s="48"/>
-      <c r="G218" s="48"/>
+      <c r="D218" s="50"/>
+      <c r="E218" s="50"/>
+      <c r="F218" s="50"/>
+      <c r="G218" s="50"/>
       <c r="H218" s="25"/>
       <c r="I218" s="25"/>
       <c r="J218" s="25"/>
@@ -20237,10 +20493,10 @@
       </c>
       <c r="B219" s="25"/>
       <c r="C219" s="25"/>
-      <c r="D219" s="48"/>
-      <c r="E219" s="48"/>
-      <c r="F219" s="48"/>
-      <c r="G219" s="48"/>
+      <c r="D219" s="50"/>
+      <c r="E219" s="50"/>
+      <c r="F219" s="50"/>
+      <c r="G219" s="50"/>
       <c r="H219" s="25"/>
       <c r="I219" s="25"/>
       <c r="J219" s="25"/>
@@ -20259,10 +20515,10 @@
       </c>
       <c r="B220" s="26"/>
       <c r="C220" s="25"/>
-      <c r="D220" s="48"/>
-      <c r="E220" s="48"/>
-      <c r="F220" s="48"/>
-      <c r="G220" s="48"/>
+      <c r="D220" s="50"/>
+      <c r="E220" s="50"/>
+      <c r="F220" s="50"/>
+      <c r="G220" s="50"/>
       <c r="H220" s="25"/>
       <c r="I220" s="25"/>
       <c r="J220" s="25"/>
@@ -20281,10 +20537,10 @@
       </c>
       <c r="B221" s="25"/>
       <c r="C221" s="25"/>
-      <c r="D221" s="48"/>
-      <c r="E221" s="48"/>
-      <c r="F221" s="48"/>
-      <c r="G221" s="48"/>
+      <c r="D221" s="50"/>
+      <c r="E221" s="50"/>
+      <c r="F221" s="50"/>
+      <c r="G221" s="50"/>
       <c r="H221" s="25"/>
       <c r="I221" s="25"/>
       <c r="J221" s="25"/>
@@ -20303,10 +20559,10 @@
       </c>
       <c r="B222" s="25"/>
       <c r="C222" s="25"/>
-      <c r="D222" s="48"/>
-      <c r="E222" s="48"/>
-      <c r="F222" s="48"/>
-      <c r="G222" s="48"/>
+      <c r="D222" s="50"/>
+      <c r="E222" s="50"/>
+      <c r="F222" s="50"/>
+      <c r="G222" s="50"/>
       <c r="H222" s="25"/>
       <c r="I222" s="25"/>
       <c r="J222" s="25"/>
@@ -20325,10 +20581,10 @@
       </c>
       <c r="B223" s="25"/>
       <c r="C223" s="25"/>
-      <c r="D223" s="48"/>
-      <c r="E223" s="48"/>
-      <c r="F223" s="48"/>
-      <c r="G223" s="48"/>
+      <c r="D223" s="50"/>
+      <c r="E223" s="50"/>
+      <c r="F223" s="50"/>
+      <c r="G223" s="50"/>
       <c r="H223" s="25"/>
       <c r="I223" s="25"/>
       <c r="J223" s="25"/>
@@ -20347,10 +20603,10 @@
       </c>
       <c r="B224" s="25"/>
       <c r="C224" s="25"/>
-      <c r="D224" s="48"/>
-      <c r="E224" s="48"/>
-      <c r="F224" s="48"/>
-      <c r="G224" s="48"/>
+      <c r="D224" s="50"/>
+      <c r="E224" s="50"/>
+      <c r="F224" s="50"/>
+      <c r="G224" s="50"/>
       <c r="H224" s="25"/>
       <c r="I224" s="25"/>
       <c r="J224" s="25"/>
@@ -20369,10 +20625,10 @@
       </c>
       <c r="B225" s="26"/>
       <c r="C225" s="25"/>
-      <c r="D225" s="48"/>
-      <c r="E225" s="48"/>
-      <c r="F225" s="48"/>
-      <c r="G225" s="48"/>
+      <c r="D225" s="50"/>
+      <c r="E225" s="50"/>
+      <c r="F225" s="50"/>
+      <c r="G225" s="50"/>
       <c r="H225" s="25"/>
       <c r="I225" s="25"/>
       <c r="J225" s="25"/>
@@ -20391,10 +20647,10 @@
       </c>
       <c r="B226" s="25"/>
       <c r="C226" s="25"/>
-      <c r="D226" s="48"/>
-      <c r="E226" s="48"/>
-      <c r="F226" s="48"/>
-      <c r="G226" s="48"/>
+      <c r="D226" s="50"/>
+      <c r="E226" s="50"/>
+      <c r="F226" s="50"/>
+      <c r="G226" s="50"/>
       <c r="H226" s="25"/>
       <c r="I226" s="25"/>
       <c r="J226" s="25"/>
@@ -20413,10 +20669,10 @@
       </c>
       <c r="B227" s="25"/>
       <c r="C227" s="25"/>
-      <c r="D227" s="48"/>
-      <c r="E227" s="48"/>
-      <c r="F227" s="48"/>
-      <c r="G227" s="48"/>
+      <c r="D227" s="50"/>
+      <c r="E227" s="50"/>
+      <c r="F227" s="50"/>
+      <c r="G227" s="50"/>
       <c r="H227" s="25"/>
       <c r="I227" s="25"/>
       <c r="J227" s="25"/>
@@ -20435,10 +20691,10 @@
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="25"/>
-      <c r="D228" s="48"/>
-      <c r="E228" s="48"/>
-      <c r="F228" s="48"/>
-      <c r="G228" s="48"/>
+      <c r="D228" s="50"/>
+      <c r="E228" s="50"/>
+      <c r="F228" s="50"/>
+      <c r="G228" s="50"/>
       <c r="H228" s="25"/>
       <c r="I228" s="25"/>
       <c r="J228" s="25"/>
@@ -20457,10 +20713,10 @@
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="25"/>
-      <c r="D229" s="48"/>
-      <c r="E229" s="48"/>
-      <c r="F229" s="48"/>
-      <c r="G229" s="48"/>
+      <c r="D229" s="50"/>
+      <c r="E229" s="50"/>
+      <c r="F229" s="50"/>
+      <c r="G229" s="50"/>
       <c r="H229" s="25"/>
       <c r="I229" s="25"/>
       <c r="J229" s="25"/>
@@ -20479,10 +20735,10 @@
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="25"/>
-      <c r="D230" s="48"/>
-      <c r="E230" s="48"/>
-      <c r="F230" s="48"/>
-      <c r="G230" s="48"/>
+      <c r="D230" s="50"/>
+      <c r="E230" s="50"/>
+      <c r="F230" s="50"/>
+      <c r="G230" s="50"/>
       <c r="H230" s="25"/>
       <c r="I230" s="25"/>
       <c r="J230" s="25"/>
@@ -20501,10 +20757,10 @@
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="25"/>
-      <c r="D231" s="48"/>
-      <c r="E231" s="48"/>
-      <c r="F231" s="48"/>
-      <c r="G231" s="48"/>
+      <c r="D231" s="50"/>
+      <c r="E231" s="50"/>
+      <c r="F231" s="50"/>
+      <c r="G231" s="50"/>
       <c r="H231" s="25"/>
       <c r="I231" s="25"/>
       <c r="J231" s="25"/>
@@ -20523,10 +20779,10 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="25"/>
-      <c r="D232" s="48"/>
-      <c r="E232" s="48"/>
-      <c r="F232" s="48"/>
-      <c r="G232" s="48"/>
+      <c r="D232" s="50"/>
+      <c r="E232" s="50"/>
+      <c r="F232" s="50"/>
+      <c r="G232" s="50"/>
       <c r="H232" s="25"/>
       <c r="I232" s="25"/>
       <c r="J232" s="25"/>
@@ -20545,10 +20801,10 @@
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="25"/>
-      <c r="D233" s="48"/>
-      <c r="E233" s="48"/>
-      <c r="F233" s="48"/>
-      <c r="G233" s="48"/>
+      <c r="D233" s="50"/>
+      <c r="E233" s="50"/>
+      <c r="F233" s="50"/>
+      <c r="G233" s="50"/>
       <c r="H233" s="25"/>
       <c r="I233" s="25"/>
       <c r="J233" s="25"/>
@@ -20567,10 +20823,10 @@
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="25"/>
-      <c r="D234" s="48"/>
-      <c r="E234" s="48"/>
-      <c r="F234" s="48"/>
-      <c r="G234" s="48"/>
+      <c r="D234" s="50"/>
+      <c r="E234" s="50"/>
+      <c r="F234" s="50"/>
+      <c r="G234" s="50"/>
       <c r="H234" s="25"/>
       <c r="I234" s="25"/>
       <c r="J234" s="25"/>
@@ -20589,10 +20845,10 @@
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="25"/>
-      <c r="D235" s="48"/>
-      <c r="E235" s="48"/>
-      <c r="F235" s="48"/>
-      <c r="G235" s="48"/>
+      <c r="D235" s="50"/>
+      <c r="E235" s="50"/>
+      <c r="F235" s="50"/>
+      <c r="G235" s="50"/>
       <c r="H235" s="25"/>
       <c r="I235" s="25"/>
       <c r="J235" s="25"/>
@@ -20611,10 +20867,10 @@
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="25"/>
-      <c r="D236" s="48"/>
-      <c r="E236" s="48"/>
-      <c r="F236" s="48"/>
-      <c r="G236" s="48"/>
+      <c r="D236" s="50"/>
+      <c r="E236" s="50"/>
+      <c r="F236" s="50"/>
+      <c r="G236" s="50"/>
       <c r="H236" s="25"/>
       <c r="I236" s="25"/>
       <c r="J236" s="25"/>
@@ -20633,10 +20889,10 @@
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="25"/>
-      <c r="D237" s="48"/>
-      <c r="E237" s="48"/>
-      <c r="F237" s="48"/>
-      <c r="G237" s="48"/>
+      <c r="D237" s="50"/>
+      <c r="E237" s="50"/>
+      <c r="F237" s="50"/>
+      <c r="G237" s="50"/>
       <c r="H237" s="25"/>
       <c r="I237" s="25"/>
       <c r="J237" s="25"/>
@@ -20655,10 +20911,10 @@
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="25"/>
-      <c r="D238" s="48"/>
-      <c r="E238" s="48"/>
-      <c r="F238" s="48"/>
-      <c r="G238" s="48"/>
+      <c r="D238" s="50"/>
+      <c r="E238" s="50"/>
+      <c r="F238" s="50"/>
+      <c r="G238" s="50"/>
       <c r="H238" s="25"/>
       <c r="I238" s="25"/>
       <c r="J238" s="25"/>
@@ -20677,10 +20933,10 @@
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="25"/>
-      <c r="D239" s="48"/>
-      <c r="E239" s="48"/>
-      <c r="F239" s="48"/>
-      <c r="G239" s="48"/>
+      <c r="D239" s="50"/>
+      <c r="E239" s="50"/>
+      <c r="F239" s="50"/>
+      <c r="G239" s="50"/>
       <c r="H239" s="25"/>
       <c r="I239" s="25"/>
       <c r="J239" s="25"/>
@@ -20699,10 +20955,10 @@
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="25"/>
-      <c r="D240" s="48"/>
-      <c r="E240" s="48"/>
-      <c r="F240" s="48"/>
-      <c r="G240" s="48"/>
+      <c r="D240" s="50"/>
+      <c r="E240" s="50"/>
+      <c r="F240" s="50"/>
+      <c r="G240" s="50"/>
       <c r="H240" s="25"/>
       <c r="I240" s="25"/>
       <c r="J240" s="25"/>
@@ -20721,10 +20977,10 @@
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="25"/>
-      <c r="D241" s="48"/>
-      <c r="E241" s="48"/>
-      <c r="F241" s="48"/>
-      <c r="G241" s="48"/>
+      <c r="D241" s="50"/>
+      <c r="E241" s="50"/>
+      <c r="F241" s="50"/>
+      <c r="G241" s="50"/>
       <c r="H241" s="25"/>
       <c r="I241" s="25"/>
       <c r="J241" s="25"/>
@@ -20743,10 +20999,10 @@
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="25"/>
-      <c r="D242" s="48"/>
-      <c r="E242" s="48"/>
-      <c r="F242" s="48"/>
-      <c r="G242" s="48"/>
+      <c r="D242" s="50"/>
+      <c r="E242" s="50"/>
+      <c r="F242" s="50"/>
+      <c r="G242" s="50"/>
       <c r="H242" s="25"/>
       <c r="I242" s="25"/>
       <c r="J242" s="25"/>
@@ -20765,10 +21021,10 @@
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="25"/>
-      <c r="D243" s="48"/>
-      <c r="E243" s="48"/>
-      <c r="F243" s="48"/>
-      <c r="G243" s="48"/>
+      <c r="D243" s="50"/>
+      <c r="E243" s="50"/>
+      <c r="F243" s="50"/>
+      <c r="G243" s="50"/>
       <c r="H243" s="25"/>
       <c r="I243" s="25"/>
       <c r="J243" s="25"/>
@@ -20787,10 +21043,10 @@
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="25"/>
-      <c r="D244" s="48"/>
-      <c r="E244" s="48"/>
-      <c r="F244" s="48"/>
-      <c r="G244" s="48"/>
+      <c r="D244" s="50"/>
+      <c r="E244" s="50"/>
+      <c r="F244" s="50"/>
+      <c r="G244" s="50"/>
       <c r="H244" s="25"/>
       <c r="I244" s="25"/>
       <c r="J244" s="25"/>
@@ -20809,10 +21065,10 @@
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="25"/>
-      <c r="D245" s="48"/>
-      <c r="E245" s="48"/>
-      <c r="F245" s="48"/>
-      <c r="G245" s="48"/>
+      <c r="D245" s="50"/>
+      <c r="E245" s="50"/>
+      <c r="F245" s="50"/>
+      <c r="G245" s="50"/>
       <c r="H245" s="25"/>
       <c r="I245" s="25"/>
       <c r="J245" s="25"/>
@@ -20831,10 +21087,10 @@
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="25"/>
-      <c r="D246" s="48"/>
-      <c r="E246" s="48"/>
-      <c r="F246" s="48"/>
-      <c r="G246" s="48"/>
+      <c r="D246" s="50"/>
+      <c r="E246" s="50"/>
+      <c r="F246" s="50"/>
+      <c r="G246" s="50"/>
       <c r="H246" s="25"/>
       <c r="I246" s="25"/>
       <c r="J246" s="25"/>
@@ -20853,10 +21109,10 @@
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="25"/>
-      <c r="D247" s="48"/>
-      <c r="E247" s="48"/>
-      <c r="F247" s="48"/>
-      <c r="G247" s="48"/>
+      <c r="D247" s="50"/>
+      <c r="E247" s="50"/>
+      <c r="F247" s="50"/>
+      <c r="G247" s="50"/>
       <c r="H247" s="25"/>
       <c r="I247" s="25"/>
       <c r="J247" s="25"/>
@@ -20875,10 +21131,10 @@
       </c>
       <c r="B248" s="25"/>
       <c r="C248" s="25"/>
-      <c r="D248" s="48"/>
-      <c r="E248" s="48"/>
-      <c r="F248" s="48"/>
-      <c r="G248" s="48"/>
+      <c r="D248" s="50"/>
+      <c r="E248" s="50"/>
+      <c r="F248" s="50"/>
+      <c r="G248" s="50"/>
       <c r="H248" s="25"/>
       <c r="I248" s="25"/>
       <c r="J248" s="25"/>
@@ -20897,10 +21153,10 @@
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="25"/>
-      <c r="D249" s="48"/>
-      <c r="E249" s="48"/>
-      <c r="F249" s="48"/>
-      <c r="G249" s="48"/>
+      <c r="D249" s="50"/>
+      <c r="E249" s="50"/>
+      <c r="F249" s="50"/>
+      <c r="G249" s="50"/>
       <c r="H249" s="25"/>
       <c r="I249" s="25"/>
       <c r="J249" s="25"/>
@@ -20919,10 +21175,10 @@
       </c>
       <c r="B250" s="25"/>
       <c r="C250" s="25"/>
-      <c r="D250" s="48"/>
-      <c r="E250" s="48"/>
-      <c r="F250" s="48"/>
-      <c r="G250" s="48"/>
+      <c r="D250" s="50"/>
+      <c r="E250" s="50"/>
+      <c r="F250" s="50"/>
+      <c r="G250" s="50"/>
       <c r="H250" s="25"/>
       <c r="I250" s="25"/>
       <c r="J250" s="25"/>
@@ -20941,10 +21197,10 @@
       </c>
       <c r="B251" s="25"/>
       <c r="C251" s="25"/>
-      <c r="D251" s="48"/>
-      <c r="E251" s="48"/>
-      <c r="F251" s="48"/>
-      <c r="G251" s="48"/>
+      <c r="D251" s="50"/>
+      <c r="E251" s="50"/>
+      <c r="F251" s="50"/>
+      <c r="G251" s="50"/>
       <c r="H251" s="25"/>
       <c r="I251" s="25"/>
       <c r="J251" s="25"/>
@@ -20963,10 +21219,10 @@
       </c>
       <c r="B252" s="25"/>
       <c r="C252" s="25"/>
-      <c r="D252" s="48"/>
-      <c r="E252" s="48"/>
-      <c r="F252" s="48"/>
-      <c r="G252" s="48"/>
+      <c r="D252" s="50"/>
+      <c r="E252" s="50"/>
+      <c r="F252" s="50"/>
+      <c r="G252" s="50"/>
       <c r="H252" s="25"/>
       <c r="I252" s="25"/>
       <c r="J252" s="25"/>
@@ -20985,10 +21241,10 @@
       </c>
       <c r="B253" s="26"/>
       <c r="C253" s="25"/>
-      <c r="D253" s="48"/>
-      <c r="E253" s="48"/>
-      <c r="F253" s="48"/>
-      <c r="G253" s="48"/>
+      <c r="D253" s="50"/>
+      <c r="E253" s="50"/>
+      <c r="F253" s="50"/>
+      <c r="G253" s="50"/>
       <c r="H253" s="25"/>
       <c r="I253" s="25"/>
       <c r="J253" s="25"/>
@@ -21007,10 +21263,10 @@
       </c>
       <c r="B254" s="25"/>
       <c r="C254" s="25"/>
-      <c r="D254" s="48"/>
-      <c r="E254" s="48"/>
-      <c r="F254" s="48"/>
-      <c r="G254" s="48"/>
+      <c r="D254" s="50"/>
+      <c r="E254" s="50"/>
+      <c r="F254" s="50"/>
+      <c r="G254" s="50"/>
       <c r="H254" s="25"/>
       <c r="I254" s="25"/>
       <c r="J254" s="25"/>
@@ -21029,10 +21285,10 @@
       </c>
       <c r="B255" s="25"/>
       <c r="C255" s="25"/>
-      <c r="D255" s="48"/>
-      <c r="E255" s="48"/>
-      <c r="F255" s="48"/>
-      <c r="G255" s="48"/>
+      <c r="D255" s="50"/>
+      <c r="E255" s="50"/>
+      <c r="F255" s="50"/>
+      <c r="G255" s="50"/>
       <c r="H255" s="25"/>
       <c r="I255" s="25"/>
       <c r="J255" s="25"/>
@@ -21051,10 +21307,10 @@
       </c>
       <c r="B256" s="25"/>
       <c r="C256" s="25"/>
-      <c r="D256" s="48"/>
-      <c r="E256" s="48"/>
-      <c r="F256" s="48"/>
-      <c r="G256" s="48"/>
+      <c r="D256" s="50"/>
+      <c r="E256" s="50"/>
+      <c r="F256" s="50"/>
+      <c r="G256" s="50"/>
       <c r="H256" s="25"/>
       <c r="I256" s="25"/>
       <c r="J256" s="25"/>
@@ -21073,10 +21329,10 @@
       </c>
       <c r="B257" s="27"/>
       <c r="C257" s="25"/>
-      <c r="D257" s="48"/>
-      <c r="E257" s="48"/>
-      <c r="F257" s="48"/>
-      <c r="G257" s="48"/>
+      <c r="D257" s="50"/>
+      <c r="E257" s="50"/>
+      <c r="F257" s="50"/>
+      <c r="G257" s="50"/>
       <c r="H257" s="25"/>
       <c r="I257" s="25"/>
       <c r="J257" s="25"/>
@@ -21095,10 +21351,10 @@
       </c>
       <c r="B258" s="27"/>
       <c r="C258" s="25"/>
-      <c r="D258" s="48"/>
-      <c r="E258" s="48"/>
-      <c r="F258" s="48"/>
-      <c r="G258" s="48"/>
+      <c r="D258" s="50"/>
+      <c r="E258" s="50"/>
+      <c r="F258" s="50"/>
+      <c r="G258" s="50"/>
       <c r="H258" s="25"/>
       <c r="I258" s="25"/>
       <c r="J258" s="25"/>
@@ -21117,10 +21373,10 @@
       </c>
       <c r="B259" s="27"/>
       <c r="C259" s="25"/>
-      <c r="D259" s="48"/>
-      <c r="E259" s="48"/>
-      <c r="F259" s="48"/>
-      <c r="G259" s="48"/>
+      <c r="D259" s="50"/>
+      <c r="E259" s="50"/>
+      <c r="F259" s="50"/>
+      <c r="G259" s="50"/>
       <c r="H259" s="25"/>
       <c r="I259" s="25"/>
       <c r="J259" s="25"/>
@@ -21139,10 +21395,10 @@
       </c>
       <c r="B260" s="27"/>
       <c r="C260" s="25"/>
-      <c r="D260" s="48"/>
-      <c r="E260" s="48"/>
-      <c r="F260" s="48"/>
-      <c r="G260" s="48"/>
+      <c r="D260" s="50"/>
+      <c r="E260" s="50"/>
+      <c r="F260" s="50"/>
+      <c r="G260" s="50"/>
       <c r="H260" s="25"/>
       <c r="I260" s="25"/>
       <c r="J260" s="25"/>
@@ -21161,10 +21417,10 @@
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="25"/>
-      <c r="D261" s="48"/>
-      <c r="E261" s="48"/>
-      <c r="F261" s="48"/>
-      <c r="G261" s="48"/>
+      <c r="D261" s="50"/>
+      <c r="E261" s="50"/>
+      <c r="F261" s="50"/>
+      <c r="G261" s="50"/>
       <c r="H261" s="25"/>
       <c r="I261" s="25"/>
       <c r="J261" s="25"/>
@@ -21183,10 +21439,10 @@
       </c>
       <c r="B262" s="27"/>
       <c r="C262" s="25"/>
-      <c r="D262" s="48"/>
-      <c r="E262" s="48"/>
-      <c r="F262" s="48"/>
-      <c r="G262" s="48"/>
+      <c r="D262" s="50"/>
+      <c r="E262" s="50"/>
+      <c r="F262" s="50"/>
+      <c r="G262" s="50"/>
       <c r="H262" s="25"/>
       <c r="I262" s="25"/>
       <c r="J262" s="25"/>
@@ -21205,10 +21461,10 @@
       </c>
       <c r="B263" s="25"/>
       <c r="C263" s="25"/>
-      <c r="D263" s="48"/>
-      <c r="E263" s="48"/>
-      <c r="F263" s="48"/>
-      <c r="G263" s="48"/>
+      <c r="D263" s="50"/>
+      <c r="E263" s="50"/>
+      <c r="F263" s="50"/>
+      <c r="G263" s="50"/>
       <c r="H263" s="25"/>
       <c r="I263" s="25"/>
       <c r="J263" s="25"/>
@@ -21227,10 +21483,10 @@
       </c>
       <c r="B264" s="25"/>
       <c r="C264" s="25"/>
-      <c r="D264" s="48"/>
-      <c r="E264" s="48"/>
-      <c r="F264" s="48"/>
-      <c r="G264" s="48"/>
+      <c r="D264" s="50"/>
+      <c r="E264" s="50"/>
+      <c r="F264" s="50"/>
+      <c r="G264" s="50"/>
       <c r="H264" s="25"/>
       <c r="I264" s="25"/>
       <c r="J264" s="25"/>
@@ -21249,10 +21505,10 @@
       </c>
       <c r="B265" s="25"/>
       <c r="C265" s="25"/>
-      <c r="D265" s="48"/>
-      <c r="E265" s="48"/>
-      <c r="F265" s="48"/>
-      <c r="G265" s="48"/>
+      <c r="D265" s="50"/>
+      <c r="E265" s="50"/>
+      <c r="F265" s="50"/>
+      <c r="G265" s="50"/>
       <c r="H265" s="25"/>
       <c r="I265" s="25"/>
       <c r="J265" s="25"/>
@@ -21271,10 +21527,10 @@
       </c>
       <c r="B266" s="25"/>
       <c r="C266" s="25"/>
-      <c r="D266" s="48"/>
-      <c r="E266" s="48"/>
-      <c r="F266" s="48"/>
-      <c r="G266" s="48"/>
+      <c r="D266" s="50"/>
+      <c r="E266" s="50"/>
+      <c r="F266" s="50"/>
+      <c r="G266" s="50"/>
       <c r="H266" s="25"/>
       <c r="I266" s="25"/>
       <c r="J266" s="25"/>
@@ -21293,10 +21549,10 @@
       </c>
       <c r="B267" s="25"/>
       <c r="C267" s="25"/>
-      <c r="D267" s="48"/>
-      <c r="E267" s="48"/>
-      <c r="F267" s="48"/>
-      <c r="G267" s="48"/>
+      <c r="D267" s="50"/>
+      <c r="E267" s="50"/>
+      <c r="F267" s="50"/>
+      <c r="G267" s="50"/>
       <c r="H267" s="25"/>
       <c r="I267" s="25"/>
       <c r="J267" s="25"/>
@@ -21315,10 +21571,10 @@
       </c>
       <c r="B268" s="25"/>
       <c r="C268" s="25"/>
-      <c r="D268" s="48"/>
-      <c r="E268" s="48"/>
-      <c r="F268" s="48"/>
-      <c r="G268" s="48"/>
+      <c r="D268" s="50"/>
+      <c r="E268" s="50"/>
+      <c r="F268" s="50"/>
+      <c r="G268" s="50"/>
       <c r="H268" s="25"/>
       <c r="I268" s="25"/>
       <c r="J268" s="25"/>
@@ -21337,10 +21593,10 @@
       </c>
       <c r="B269" s="25"/>
       <c r="C269" s="25"/>
-      <c r="D269" s="48"/>
-      <c r="E269" s="48"/>
-      <c r="F269" s="48"/>
-      <c r="G269" s="48"/>
+      <c r="D269" s="50"/>
+      <c r="E269" s="50"/>
+      <c r="F269" s="50"/>
+      <c r="G269" s="50"/>
       <c r="H269" s="25"/>
       <c r="I269" s="25"/>
       <c r="J269" s="25"/>
@@ -21359,10 +21615,10 @@
       </c>
       <c r="B270" s="25"/>
       <c r="C270" s="25"/>
-      <c r="D270" s="48"/>
-      <c r="E270" s="48"/>
-      <c r="F270" s="48"/>
-      <c r="G270" s="48"/>
+      <c r="D270" s="50"/>
+      <c r="E270" s="50"/>
+      <c r="F270" s="50"/>
+      <c r="G270" s="50"/>
       <c r="H270" s="25"/>
       <c r="I270" s="25"/>
       <c r="J270" s="25"/>
@@ -21381,10 +21637,10 @@
       </c>
       <c r="B271" s="25"/>
       <c r="C271" s="25"/>
-      <c r="D271" s="48"/>
-      <c r="E271" s="48"/>
-      <c r="F271" s="48"/>
-      <c r="G271" s="48"/>
+      <c r="D271" s="50"/>
+      <c r="E271" s="50"/>
+      <c r="F271" s="50"/>
+      <c r="G271" s="50"/>
       <c r="H271" s="25"/>
       <c r="I271" s="25"/>
       <c r="J271" s="25"/>
@@ -21403,10 +21659,10 @@
       </c>
       <c r="B272" s="25"/>
       <c r="C272" s="25"/>
-      <c r="D272" s="48"/>
-      <c r="E272" s="48"/>
-      <c r="F272" s="48"/>
-      <c r="G272" s="48"/>
+      <c r="D272" s="50"/>
+      <c r="E272" s="50"/>
+      <c r="F272" s="50"/>
+      <c r="G272" s="50"/>
       <c r="H272" s="25"/>
       <c r="I272" s="25"/>
       <c r="J272" s="25"/>
@@ -21425,10 +21681,10 @@
       </c>
       <c r="B273" s="33"/>
       <c r="C273" s="33"/>
-      <c r="D273" s="51"/>
-      <c r="E273" s="51"/>
-      <c r="F273" s="51"/>
-      <c r="G273" s="51"/>
+      <c r="D273" s="53"/>
+      <c r="E273" s="53"/>
+      <c r="F273" s="53"/>
+      <c r="G273" s="53"/>
       <c r="H273" s="33"/>
       <c r="I273" s="33"/>
       <c r="J273" s="33"/>
@@ -21447,10 +21703,10 @@
       </c>
       <c r="B274" s="25"/>
       <c r="C274" s="25"/>
-      <c r="D274" s="48"/>
-      <c r="E274" s="48"/>
-      <c r="F274" s="48"/>
-      <c r="G274" s="48"/>
+      <c r="D274" s="50"/>
+      <c r="E274" s="50"/>
+      <c r="F274" s="50"/>
+      <c r="G274" s="50"/>
       <c r="H274" s="25"/>
       <c r="I274" s="25"/>
       <c r="J274" s="25"/>
@@ -21469,10 +21725,10 @@
       </c>
       <c r="B275" s="26"/>
       <c r="C275" s="25"/>
-      <c r="D275" s="48"/>
-      <c r="E275" s="48"/>
-      <c r="F275" s="48"/>
-      <c r="G275" s="48"/>
+      <c r="D275" s="50"/>
+      <c r="E275" s="50"/>
+      <c r="F275" s="50"/>
+      <c r="G275" s="50"/>
       <c r="H275" s="25"/>
       <c r="I275" s="25"/>
       <c r="J275" s="25"/>
@@ -21491,10 +21747,10 @@
       </c>
       <c r="B276" s="25"/>
       <c r="C276" s="25"/>
-      <c r="D276" s="48"/>
-      <c r="E276" s="48"/>
-      <c r="F276" s="48"/>
-      <c r="G276" s="48"/>
+      <c r="D276" s="50"/>
+      <c r="E276" s="50"/>
+      <c r="F276" s="50"/>
+      <c r="G276" s="50"/>
       <c r="H276" s="25"/>
       <c r="I276" s="25"/>
       <c r="J276" s="25"/>
@@ -21513,10 +21769,10 @@
       </c>
       <c r="B277" s="25"/>
       <c r="C277" s="25"/>
-      <c r="D277" s="48"/>
-      <c r="E277" s="48"/>
-      <c r="F277" s="48"/>
-      <c r="G277" s="48"/>
+      <c r="D277" s="50"/>
+      <c r="E277" s="50"/>
+      <c r="F277" s="50"/>
+      <c r="G277" s="50"/>
       <c r="H277" s="25"/>
       <c r="I277" s="25"/>
       <c r="J277" s="25"/>
@@ -21535,10 +21791,10 @@
       </c>
       <c r="B278" s="4"/>
       <c r="C278" s="25"/>
-      <c r="D278" s="48"/>
-      <c r="E278" s="48"/>
-      <c r="F278" s="48"/>
-      <c r="G278" s="48"/>
+      <c r="D278" s="50"/>
+      <c r="E278" s="50"/>
+      <c r="F278" s="50"/>
+      <c r="G278" s="50"/>
       <c r="H278" s="25"/>
       <c r="I278" s="25"/>
       <c r="J278" s="25"/>
@@ -21557,10 +21813,10 @@
       </c>
       <c r="B279" s="4"/>
       <c r="C279" s="25"/>
-      <c r="D279" s="48"/>
-      <c r="E279" s="48"/>
-      <c r="F279" s="48"/>
-      <c r="G279" s="48"/>
+      <c r="D279" s="50"/>
+      <c r="E279" s="50"/>
+      <c r="F279" s="50"/>
+      <c r="G279" s="50"/>
       <c r="H279" s="25"/>
       <c r="I279" s="25"/>
       <c r="J279" s="25"/>
@@ -21579,10 +21835,10 @@
       </c>
       <c r="B280" s="4"/>
       <c r="C280" s="25"/>
-      <c r="D280" s="48"/>
-      <c r="E280" s="48"/>
-      <c r="F280" s="48"/>
-      <c r="G280" s="48"/>
+      <c r="D280" s="50"/>
+      <c r="E280" s="50"/>
+      <c r="F280" s="50"/>
+      <c r="G280" s="50"/>
       <c r="H280" s="25"/>
       <c r="I280" s="25"/>
       <c r="J280" s="25"/>
@@ -21601,10 +21857,10 @@
       </c>
       <c r="B281" s="4"/>
       <c r="C281" s="25"/>
-      <c r="D281" s="48"/>
-      <c r="E281" s="48"/>
-      <c r="F281" s="48"/>
-      <c r="G281" s="48"/>
+      <c r="D281" s="50"/>
+      <c r="E281" s="50"/>
+      <c r="F281" s="50"/>
+      <c r="G281" s="50"/>
       <c r="H281" s="25"/>
       <c r="I281" s="25"/>
       <c r="J281" s="25"/>
@@ -21623,10 +21879,10 @@
       </c>
       <c r="B282" s="4"/>
       <c r="C282" s="25"/>
-      <c r="D282" s="48"/>
-      <c r="E282" s="48"/>
-      <c r="F282" s="48"/>
-      <c r="G282" s="48"/>
+      <c r="D282" s="50"/>
+      <c r="E282" s="50"/>
+      <c r="F282" s="50"/>
+      <c r="G282" s="50"/>
       <c r="H282" s="25"/>
       <c r="I282" s="25"/>
       <c r="J282" s="25"/>
@@ -21645,10 +21901,10 @@
       </c>
       <c r="B283" s="4"/>
       <c r="C283" s="25"/>
-      <c r="D283" s="48"/>
-      <c r="E283" s="48"/>
-      <c r="F283" s="48"/>
-      <c r="G283" s="48"/>
+      <c r="D283" s="50"/>
+      <c r="E283" s="50"/>
+      <c r="F283" s="50"/>
+      <c r="G283" s="50"/>
       <c r="H283" s="25"/>
       <c r="I283" s="25"/>
       <c r="J283" s="25"/>
@@ -21667,10 +21923,10 @@
       </c>
       <c r="B284" s="4"/>
       <c r="C284" s="25"/>
-      <c r="D284" s="48"/>
-      <c r="E284" s="48"/>
-      <c r="F284" s="48"/>
-      <c r="G284" s="48"/>
+      <c r="D284" s="50"/>
+      <c r="E284" s="50"/>
+      <c r="F284" s="50"/>
+      <c r="G284" s="50"/>
       <c r="H284" s="25"/>
       <c r="I284" s="25"/>
       <c r="J284" s="25"/>
@@ -21689,10 +21945,10 @@
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="25"/>
-      <c r="D285" s="48"/>
-      <c r="E285" s="48"/>
-      <c r="F285" s="48"/>
-      <c r="G285" s="48"/>
+      <c r="D285" s="50"/>
+      <c r="E285" s="50"/>
+      <c r="F285" s="50"/>
+      <c r="G285" s="50"/>
       <c r="H285" s="25"/>
       <c r="I285" s="25"/>
       <c r="J285" s="25"/>
@@ -21711,10 +21967,10 @@
       </c>
       <c r="B286" s="4"/>
       <c r="C286" s="25"/>
-      <c r="D286" s="48"/>
-      <c r="E286" s="48"/>
-      <c r="F286" s="48"/>
-      <c r="G286" s="48"/>
+      <c r="D286" s="50"/>
+      <c r="E286" s="50"/>
+      <c r="F286" s="50"/>
+      <c r="G286" s="50"/>
       <c r="H286" s="25"/>
       <c r="I286" s="25"/>
       <c r="J286" s="25"/>
@@ -21733,10 +21989,10 @@
       </c>
       <c r="B287" s="4"/>
       <c r="C287" s="25"/>
-      <c r="D287" s="48"/>
-      <c r="E287" s="48"/>
-      <c r="F287" s="48"/>
-      <c r="G287" s="48"/>
+      <c r="D287" s="50"/>
+      <c r="E287" s="50"/>
+      <c r="F287" s="50"/>
+      <c r="G287" s="50"/>
       <c r="H287" s="25"/>
       <c r="I287" s="25"/>
       <c r="J287" s="25"/>
@@ -21755,10 +22011,10 @@
       </c>
       <c r="B288" s="4"/>
       <c r="C288" s="25"/>
-      <c r="D288" s="48"/>
-      <c r="E288" s="48"/>
-      <c r="F288" s="48"/>
-      <c r="G288" s="48"/>
+      <c r="D288" s="50"/>
+      <c r="E288" s="50"/>
+      <c r="F288" s="50"/>
+      <c r="G288" s="50"/>
       <c r="H288" s="25"/>
       <c r="I288" s="25"/>
       <c r="J288" s="25"/>
@@ -21777,10 +22033,10 @@
       </c>
       <c r="B289" s="4"/>
       <c r="C289" s="25"/>
-      <c r="D289" s="48"/>
-      <c r="E289" s="48"/>
-      <c r="F289" s="48"/>
-      <c r="G289" s="48"/>
+      <c r="D289" s="50"/>
+      <c r="E289" s="50"/>
+      <c r="F289" s="50"/>
+      <c r="G289" s="50"/>
       <c r="H289" s="25"/>
       <c r="I289" s="25"/>
       <c r="J289" s="25"/>
@@ -21799,10 +22055,10 @@
       </c>
       <c r="B290" s="4"/>
       <c r="C290" s="25"/>
-      <c r="D290" s="48"/>
-      <c r="E290" s="48"/>
-      <c r="F290" s="48"/>
-      <c r="G290" s="48"/>
+      <c r="D290" s="50"/>
+      <c r="E290" s="50"/>
+      <c r="F290" s="50"/>
+      <c r="G290" s="50"/>
       <c r="H290" s="25"/>
       <c r="I290" s="25"/>
       <c r="J290" s="25"/>
@@ -21821,10 +22077,10 @@
       </c>
       <c r="B291" s="4"/>
       <c r="C291" s="25"/>
-      <c r="D291" s="48"/>
-      <c r="E291" s="48"/>
-      <c r="F291" s="48"/>
-      <c r="G291" s="48"/>
+      <c r="D291" s="50"/>
+      <c r="E291" s="50"/>
+      <c r="F291" s="50"/>
+      <c r="G291" s="50"/>
       <c r="H291" s="25"/>
       <c r="I291" s="25"/>
       <c r="J291" s="25"/>
@@ -21843,10 +22099,10 @@
       </c>
       <c r="B292" s="4"/>
       <c r="C292" s="25"/>
-      <c r="D292" s="48"/>
-      <c r="E292" s="48"/>
-      <c r="F292" s="48"/>
-      <c r="G292" s="48"/>
+      <c r="D292" s="50"/>
+      <c r="E292" s="50"/>
+      <c r="F292" s="50"/>
+      <c r="G292" s="50"/>
       <c r="H292" s="25"/>
       <c r="I292" s="25"/>
       <c r="J292" s="25"/>
@@ -21865,10 +22121,10 @@
       </c>
       <c r="B293" s="4"/>
       <c r="C293" s="25"/>
-      <c r="D293" s="48"/>
-      <c r="E293" s="48"/>
-      <c r="F293" s="48"/>
-      <c r="G293" s="48"/>
+      <c r="D293" s="50"/>
+      <c r="E293" s="50"/>
+      <c r="F293" s="50"/>
+      <c r="G293" s="50"/>
       <c r="H293" s="25"/>
       <c r="I293" s="25"/>
       <c r="J293" s="25"/>
@@ -21887,10 +22143,10 @@
       </c>
       <c r="B294" s="4"/>
       <c r="C294" s="25"/>
-      <c r="D294" s="48"/>
-      <c r="E294" s="48"/>
-      <c r="F294" s="48"/>
-      <c r="G294" s="48"/>
+      <c r="D294" s="50"/>
+      <c r="E294" s="50"/>
+      <c r="F294" s="50"/>
+      <c r="G294" s="50"/>
       <c r="H294" s="25"/>
       <c r="I294" s="25"/>
       <c r="J294" s="25"/>
@@ -21907,10 +22163,10 @@
       <c r="A295" s="6"/>
       <c r="B295" s="4"/>
       <c r="C295" s="25"/>
-      <c r="D295" s="48"/>
-      <c r="E295" s="48"/>
-      <c r="F295" s="48"/>
-      <c r="G295" s="48"/>
+      <c r="D295" s="50"/>
+      <c r="E295" s="50"/>
+      <c r="F295" s="50"/>
+      <c r="G295" s="50"/>
       <c r="H295" s="25"/>
       <c r="I295" s="25"/>
       <c r="J295" s="25"/>
@@ -34437,7 +34693,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596B674C-51A8-4E57-8BA2-717CECB2C7E9}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="1"/>
@@ -34455,34 +34711,738 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>850</v>
+        <v>1069</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>848</v>
+        <v>1070</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>840</v>
+        <v>1071</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>791</v>
+      </c>
+      <c r="B9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>859</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B14" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>844</v>
+      </c>
+      <c r="B16" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>842</v>
+      </c>
+      <c r="B17" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B19" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B21" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B22" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B24" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B25" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B26" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B27" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B28" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B30" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>897</v>
+      </c>
+      <c r="B31" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>878</v>
+      </c>
+      <c r="B32" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>895</v>
+      </c>
+      <c r="B33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>885</v>
+      </c>
+      <c r="B34" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B37" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B39" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B41" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B42" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>894</v>
+      </c>
+      <c r="B43" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>894</v>
+      </c>
+      <c r="B44" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B45" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B48" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B49" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B50" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B51" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>908</v>
+      </c>
+      <c r="B54" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>910</v>
+      </c>
+      <c r="B55" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>850</v>
+      </c>
+      <c r="B56" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B57" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B58" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>848</v>
+      </c>
+      <c r="B59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B60" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B61" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B62" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>803</v>
+      </c>
+      <c r="B63" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B64" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>1054</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B66" t="s">
         <v>1053</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>840</v>
+      </c>
+      <c r="B67" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B68" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B69" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B70" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B72" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B73" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B75" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B80" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B82" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>920</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B87" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B88" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B89" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B91" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B92" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B93" t="s">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -36614,8 +37574,8 @@
       <c r="C4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E4" t="s">
-        <v>1061</v>
+      <c r="E4" s="47" t="s">
+        <v>1064</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>1049</v>
@@ -36643,11 +37603,11 @@
       <c r="C5" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="47" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>1062</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>1063</v>
       </c>
       <c r="J5" t="s">
         <v>217</v>
@@ -36745,6 +37705,9 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>133</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>1063</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>226</v>
@@ -37602,7 +38565,10 @@
         <v>234</v>
       </c>
       <c r="D64" s="7"/>
-      <c r="F64" s="8" t="s">
+      <c r="E64" s="47" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F64" s="48" t="s">
         <v>235</v>
       </c>
       <c r="J64" t="s">
@@ -37629,7 +38595,10 @@
         <v>239</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="F65" s="8" t="s">
+      <c r="E65" s="47" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F65" s="48" t="s">
         <v>205</v>
       </c>
       <c r="J65" t="s">
@@ -37653,6 +38622,12 @@
         <v>232</v>
       </c>
       <c r="D66" s="7"/>
+      <c r="E66" s="47" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>1068</v>
+      </c>
       <c r="J66" t="s">
         <v>241</v>
       </c>
@@ -50229,21 +51204,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010083E57EAE9BC9A0458C5C954CF42F5AD9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="caa032575f5f0605ed1a3a296ef65efb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fbea295-10ff-4638-90f5-98b4e1418f17" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a196ec5621f6db080099f2c0d678a929" ns2:_="">
     <xsd:import namespace="7fbea295-10ff-4638-90f5-98b4e1418f17"/>
@@ -50381,31 +51341,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C62074-BDFC-4D1E-BF7A-C2FEEAF5CCCC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7fbea295-10ff-4638-90f5-98b4e1418f17"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{111E1904-64D7-484E-9D74-DC48E42EDD39}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50421,4 +51372,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C62074-BDFC-4D1E-BF7A-C2FEEAF5CCCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7fbea295-10ff-4638-90f5-98b4e1418f17"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GeneralizationRules100K.xlsx
+++ b/GeneralizationRules100K.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Intersourcing\Malyasia\Gen_Carto\Gen_Carto\ArcgisPro_GenCarto\GenCarto_Dev\share_dev_100K_main\Dev_Gencarto_100K\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E4BCEA-2744-48A9-B454-12E6B12D5690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426197CE-261C-41B3-852A-0BA3C24A84A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="16" r:id="rId1"/>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9533" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9537" uniqueCount="1152">
   <si>
     <t>Please read the following instructions carefully</t>
   </si>
@@ -4228,6 +4228,18 @@
   </si>
   <si>
     <t>Cliff_Precipitous_L</t>
+  </si>
+  <si>
+    <t>Utility_powerline_val</t>
+  </si>
+  <si>
+    <t>Utility_aggregate_val</t>
+  </si>
+  <si>
+    <t>dataprep_delete_dngl_sql</t>
+  </si>
+  <si>
+    <t>NAM = '' Or NAM = ' ' Or NAM IS NULL</t>
   </si>
 </sst>
 </file>
@@ -4553,10 +4565,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -8345,7 +8357,7 @@
       <c r="G77" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="H77" s="51"/>
+      <c r="H77" s="52"/>
       <c r="I77" s="50"/>
       <c r="J77" s="25" t="s">
         <v>697</v>
@@ -8384,7 +8396,7 @@
       <c r="G78" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="H78" s="51"/>
+      <c r="H78" s="52"/>
       <c r="I78" s="50"/>
       <c r="J78" s="25"/>
       <c r="K78" s="25" t="s">
@@ -11789,7 +11801,7 @@
       <c r="E204" s="25"/>
       <c r="F204" s="25"/>
       <c r="G204" s="29"/>
-      <c r="H204" s="51"/>
+      <c r="H204" s="52"/>
       <c r="I204" s="50"/>
       <c r="J204" s="25"/>
       <c r="K204" s="37"/>
@@ -11820,8 +11832,8 @@
       <c r="G205" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="H205" s="52"/>
-      <c r="I205" s="52"/>
+      <c r="H205" s="51"/>
+      <c r="I205" s="51"/>
       <c r="J205" s="41" t="s">
         <v>697</v>
       </c>
@@ -15271,148 +15283,114 @@
     </row>
   </sheetData>
   <mergeCells count="264">
-    <mergeCell ref="H337:I337"/>
-    <mergeCell ref="H338:I338"/>
-    <mergeCell ref="H339:I339"/>
-    <mergeCell ref="H340:I340"/>
-    <mergeCell ref="H331:I331"/>
-    <mergeCell ref="H332:I332"/>
-    <mergeCell ref="H333:I333"/>
-    <mergeCell ref="H334:I334"/>
-    <mergeCell ref="H335:I335"/>
-    <mergeCell ref="H336:I336"/>
-    <mergeCell ref="H325:I325"/>
-    <mergeCell ref="H326:I326"/>
-    <mergeCell ref="H327:I327"/>
-    <mergeCell ref="H328:I328"/>
-    <mergeCell ref="H329:I329"/>
-    <mergeCell ref="H330:I330"/>
-    <mergeCell ref="H319:I319"/>
-    <mergeCell ref="H320:I320"/>
-    <mergeCell ref="H321:I321"/>
-    <mergeCell ref="H322:I322"/>
-    <mergeCell ref="H323:I323"/>
-    <mergeCell ref="H324:I324"/>
-    <mergeCell ref="H313:I313"/>
-    <mergeCell ref="H314:I314"/>
-    <mergeCell ref="H315:I315"/>
-    <mergeCell ref="H316:I316"/>
-    <mergeCell ref="H317:I317"/>
-    <mergeCell ref="H318:I318"/>
-    <mergeCell ref="H307:I307"/>
-    <mergeCell ref="H308:I308"/>
-    <mergeCell ref="H309:I309"/>
-    <mergeCell ref="H310:I310"/>
-    <mergeCell ref="H311:I311"/>
-    <mergeCell ref="H312:I312"/>
-    <mergeCell ref="H301:I301"/>
-    <mergeCell ref="H302:I302"/>
-    <mergeCell ref="H303:I303"/>
-    <mergeCell ref="H304:I304"/>
-    <mergeCell ref="H305:I305"/>
-    <mergeCell ref="H306:I306"/>
-    <mergeCell ref="H295:I295"/>
-    <mergeCell ref="H296:I296"/>
-    <mergeCell ref="H297:I297"/>
-    <mergeCell ref="H298:I298"/>
-    <mergeCell ref="H299:I299"/>
-    <mergeCell ref="H300:I300"/>
-    <mergeCell ref="H289:I289"/>
-    <mergeCell ref="H290:I290"/>
-    <mergeCell ref="H291:I291"/>
-    <mergeCell ref="H292:I292"/>
-    <mergeCell ref="H293:I293"/>
-    <mergeCell ref="H294:I294"/>
-    <mergeCell ref="H283:I283"/>
-    <mergeCell ref="H284:I284"/>
-    <mergeCell ref="H285:I285"/>
-    <mergeCell ref="H286:I286"/>
-    <mergeCell ref="H287:I287"/>
-    <mergeCell ref="H288:I288"/>
-    <mergeCell ref="H277:I277"/>
-    <mergeCell ref="H278:I278"/>
-    <mergeCell ref="H279:I279"/>
-    <mergeCell ref="H280:I280"/>
-    <mergeCell ref="H281:I281"/>
-    <mergeCell ref="H282:I282"/>
-    <mergeCell ref="H271:I271"/>
-    <mergeCell ref="H272:I272"/>
-    <mergeCell ref="H273:I273"/>
-    <mergeCell ref="H274:I274"/>
-    <mergeCell ref="H275:I275"/>
-    <mergeCell ref="H276:I276"/>
-    <mergeCell ref="H265:I265"/>
-    <mergeCell ref="H266:I266"/>
-    <mergeCell ref="H267:I267"/>
-    <mergeCell ref="H268:I268"/>
-    <mergeCell ref="H269:I269"/>
-    <mergeCell ref="H270:I270"/>
-    <mergeCell ref="H259:I259"/>
-    <mergeCell ref="H260:I260"/>
-    <mergeCell ref="H261:I261"/>
-    <mergeCell ref="H262:I262"/>
-    <mergeCell ref="H263:I263"/>
-    <mergeCell ref="H264:I264"/>
-    <mergeCell ref="H253:I253"/>
-    <mergeCell ref="H254:I254"/>
-    <mergeCell ref="H255:I255"/>
-    <mergeCell ref="H256:I256"/>
-    <mergeCell ref="H257:I257"/>
-    <mergeCell ref="H258:I258"/>
-    <mergeCell ref="H247:I247"/>
-    <mergeCell ref="H248:I248"/>
-    <mergeCell ref="H249:I249"/>
-    <mergeCell ref="H250:I250"/>
-    <mergeCell ref="H251:I251"/>
-    <mergeCell ref="H252:I252"/>
-    <mergeCell ref="H241:I241"/>
-    <mergeCell ref="H242:I242"/>
-    <mergeCell ref="H243:I243"/>
-    <mergeCell ref="H244:I244"/>
-    <mergeCell ref="H245:I245"/>
-    <mergeCell ref="H246:I246"/>
-    <mergeCell ref="H235:I235"/>
-    <mergeCell ref="H236:I236"/>
-    <mergeCell ref="H237:I237"/>
-    <mergeCell ref="H238:I238"/>
-    <mergeCell ref="H239:I239"/>
-    <mergeCell ref="H240:I240"/>
-    <mergeCell ref="H229:I229"/>
-    <mergeCell ref="H230:I230"/>
-    <mergeCell ref="H231:I231"/>
-    <mergeCell ref="H232:I232"/>
-    <mergeCell ref="H233:I233"/>
-    <mergeCell ref="H234:I234"/>
-    <mergeCell ref="H223:I223"/>
-    <mergeCell ref="H224:I224"/>
-    <mergeCell ref="H225:I225"/>
-    <mergeCell ref="H226:I226"/>
-    <mergeCell ref="H227:I227"/>
-    <mergeCell ref="H228:I228"/>
-    <mergeCell ref="H217:I217"/>
-    <mergeCell ref="H218:I218"/>
-    <mergeCell ref="H219:I219"/>
-    <mergeCell ref="H220:I220"/>
-    <mergeCell ref="H221:I221"/>
-    <mergeCell ref="H222:I222"/>
-    <mergeCell ref="H211:I211"/>
-    <mergeCell ref="H212:I212"/>
-    <mergeCell ref="H213:I213"/>
-    <mergeCell ref="H214:I214"/>
-    <mergeCell ref="H215:I215"/>
-    <mergeCell ref="H216:I216"/>
-    <mergeCell ref="H205:I205"/>
-    <mergeCell ref="H206:I206"/>
-    <mergeCell ref="H207:I207"/>
-    <mergeCell ref="H208:I208"/>
-    <mergeCell ref="H209:I209"/>
-    <mergeCell ref="H210:I210"/>
-    <mergeCell ref="H199:I199"/>
-    <mergeCell ref="H200:I200"/>
-    <mergeCell ref="H201:I201"/>
-    <mergeCell ref="H202:I202"/>
-    <mergeCell ref="H203:I203"/>
-    <mergeCell ref="H204:I204"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="H110:I110"/>
+    <mergeCell ref="H111:I111"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H119:I119"/>
+    <mergeCell ref="H120:I120"/>
+    <mergeCell ref="H121:I121"/>
+    <mergeCell ref="H122:I122"/>
+    <mergeCell ref="H123:I123"/>
+    <mergeCell ref="H124:I124"/>
+    <mergeCell ref="H113:I113"/>
+    <mergeCell ref="H114:I114"/>
+    <mergeCell ref="H115:I115"/>
+    <mergeCell ref="H116:I116"/>
+    <mergeCell ref="H117:I117"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="H135:I135"/>
+    <mergeCell ref="H136:I136"/>
+    <mergeCell ref="H125:I125"/>
+    <mergeCell ref="H126:I126"/>
+    <mergeCell ref="H127:I127"/>
+    <mergeCell ref="H128:I128"/>
+    <mergeCell ref="H129:I129"/>
+    <mergeCell ref="H130:I130"/>
+    <mergeCell ref="H143:I143"/>
+    <mergeCell ref="H144:I144"/>
+    <mergeCell ref="H145:I145"/>
+    <mergeCell ref="H146:I146"/>
+    <mergeCell ref="H147:I147"/>
+    <mergeCell ref="H148:I148"/>
+    <mergeCell ref="H137:I137"/>
+    <mergeCell ref="H138:I138"/>
+    <mergeCell ref="H139:I139"/>
+    <mergeCell ref="H140:I140"/>
+    <mergeCell ref="H141:I141"/>
+    <mergeCell ref="H142:I142"/>
+    <mergeCell ref="H155:I155"/>
+    <mergeCell ref="H156:I156"/>
+    <mergeCell ref="H157:I157"/>
+    <mergeCell ref="H158:I158"/>
+    <mergeCell ref="H159:I159"/>
+    <mergeCell ref="H160:I160"/>
+    <mergeCell ref="H149:I149"/>
+    <mergeCell ref="H150:I150"/>
+    <mergeCell ref="H151:I151"/>
+    <mergeCell ref="H152:I152"/>
+    <mergeCell ref="H153:I153"/>
+    <mergeCell ref="H154:I154"/>
+    <mergeCell ref="H167:I167"/>
+    <mergeCell ref="H168:I168"/>
+    <mergeCell ref="H169:I169"/>
+    <mergeCell ref="H170:I170"/>
+    <mergeCell ref="H171:I171"/>
+    <mergeCell ref="H172:I172"/>
+    <mergeCell ref="H161:I161"/>
+    <mergeCell ref="H162:I162"/>
+    <mergeCell ref="H163:I163"/>
+    <mergeCell ref="H164:I164"/>
+    <mergeCell ref="H165:I165"/>
+    <mergeCell ref="H166:I166"/>
+    <mergeCell ref="H179:I179"/>
+    <mergeCell ref="H180:I180"/>
+    <mergeCell ref="H181:I181"/>
+    <mergeCell ref="H182:I182"/>
+    <mergeCell ref="H183:I183"/>
+    <mergeCell ref="H184:I184"/>
+    <mergeCell ref="H173:I173"/>
+    <mergeCell ref="H174:I174"/>
+    <mergeCell ref="H175:I175"/>
+    <mergeCell ref="H176:I176"/>
+    <mergeCell ref="H177:I177"/>
+    <mergeCell ref="H178:I178"/>
     <mergeCell ref="H193:I193"/>
     <mergeCell ref="H194:I194"/>
     <mergeCell ref="H195:I195"/>
@@ -15427,114 +15405,148 @@
     <mergeCell ref="H188:I188"/>
     <mergeCell ref="H189:I189"/>
     <mergeCell ref="H190:I190"/>
-    <mergeCell ref="H179:I179"/>
-    <mergeCell ref="H180:I180"/>
-    <mergeCell ref="H181:I181"/>
-    <mergeCell ref="H182:I182"/>
-    <mergeCell ref="H183:I183"/>
-    <mergeCell ref="H184:I184"/>
-    <mergeCell ref="H173:I173"/>
-    <mergeCell ref="H174:I174"/>
-    <mergeCell ref="H175:I175"/>
-    <mergeCell ref="H176:I176"/>
-    <mergeCell ref="H177:I177"/>
-    <mergeCell ref="H178:I178"/>
-    <mergeCell ref="H167:I167"/>
-    <mergeCell ref="H168:I168"/>
-    <mergeCell ref="H169:I169"/>
-    <mergeCell ref="H170:I170"/>
-    <mergeCell ref="H171:I171"/>
-    <mergeCell ref="H172:I172"/>
-    <mergeCell ref="H161:I161"/>
-    <mergeCell ref="H162:I162"/>
-    <mergeCell ref="H163:I163"/>
-    <mergeCell ref="H164:I164"/>
-    <mergeCell ref="H165:I165"/>
-    <mergeCell ref="H166:I166"/>
-    <mergeCell ref="H155:I155"/>
-    <mergeCell ref="H156:I156"/>
-    <mergeCell ref="H157:I157"/>
-    <mergeCell ref="H158:I158"/>
-    <mergeCell ref="H159:I159"/>
-    <mergeCell ref="H160:I160"/>
-    <mergeCell ref="H149:I149"/>
-    <mergeCell ref="H150:I150"/>
-    <mergeCell ref="H151:I151"/>
-    <mergeCell ref="H152:I152"/>
-    <mergeCell ref="H153:I153"/>
-    <mergeCell ref="H154:I154"/>
-    <mergeCell ref="H143:I143"/>
-    <mergeCell ref="H144:I144"/>
-    <mergeCell ref="H145:I145"/>
-    <mergeCell ref="H146:I146"/>
-    <mergeCell ref="H147:I147"/>
-    <mergeCell ref="H148:I148"/>
-    <mergeCell ref="H137:I137"/>
-    <mergeCell ref="H138:I138"/>
-    <mergeCell ref="H139:I139"/>
-    <mergeCell ref="H140:I140"/>
-    <mergeCell ref="H141:I141"/>
-    <mergeCell ref="H142:I142"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="H132:I132"/>
-    <mergeCell ref="H133:I133"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="H135:I135"/>
-    <mergeCell ref="H136:I136"/>
-    <mergeCell ref="H125:I125"/>
-    <mergeCell ref="H126:I126"/>
-    <mergeCell ref="H127:I127"/>
-    <mergeCell ref="H128:I128"/>
-    <mergeCell ref="H129:I129"/>
-    <mergeCell ref="H130:I130"/>
-    <mergeCell ref="H119:I119"/>
-    <mergeCell ref="H120:I120"/>
-    <mergeCell ref="H121:I121"/>
-    <mergeCell ref="H122:I122"/>
-    <mergeCell ref="H123:I123"/>
-    <mergeCell ref="H124:I124"/>
-    <mergeCell ref="H113:I113"/>
-    <mergeCell ref="H114:I114"/>
-    <mergeCell ref="H115:I115"/>
-    <mergeCell ref="H116:I116"/>
-    <mergeCell ref="H117:I117"/>
-    <mergeCell ref="H118:I118"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="H111:I111"/>
-    <mergeCell ref="H112:I112"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="H97:I97"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="H99:I99"/>
-    <mergeCell ref="H100:I100"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H205:I205"/>
+    <mergeCell ref="H206:I206"/>
+    <mergeCell ref="H207:I207"/>
+    <mergeCell ref="H208:I208"/>
+    <mergeCell ref="H209:I209"/>
+    <mergeCell ref="H210:I210"/>
+    <mergeCell ref="H199:I199"/>
+    <mergeCell ref="H200:I200"/>
+    <mergeCell ref="H201:I201"/>
+    <mergeCell ref="H202:I202"/>
+    <mergeCell ref="H203:I203"/>
+    <mergeCell ref="H204:I204"/>
+    <mergeCell ref="H217:I217"/>
+    <mergeCell ref="H218:I218"/>
+    <mergeCell ref="H219:I219"/>
+    <mergeCell ref="H220:I220"/>
+    <mergeCell ref="H221:I221"/>
+    <mergeCell ref="H222:I222"/>
+    <mergeCell ref="H211:I211"/>
+    <mergeCell ref="H212:I212"/>
+    <mergeCell ref="H213:I213"/>
+    <mergeCell ref="H214:I214"/>
+    <mergeCell ref="H215:I215"/>
+    <mergeCell ref="H216:I216"/>
+    <mergeCell ref="H229:I229"/>
+    <mergeCell ref="H230:I230"/>
+    <mergeCell ref="H231:I231"/>
+    <mergeCell ref="H232:I232"/>
+    <mergeCell ref="H233:I233"/>
+    <mergeCell ref="H234:I234"/>
+    <mergeCell ref="H223:I223"/>
+    <mergeCell ref="H224:I224"/>
+    <mergeCell ref="H225:I225"/>
+    <mergeCell ref="H226:I226"/>
+    <mergeCell ref="H227:I227"/>
+    <mergeCell ref="H228:I228"/>
+    <mergeCell ref="H241:I241"/>
+    <mergeCell ref="H242:I242"/>
+    <mergeCell ref="H243:I243"/>
+    <mergeCell ref="H244:I244"/>
+    <mergeCell ref="H245:I245"/>
+    <mergeCell ref="H246:I246"/>
+    <mergeCell ref="H235:I235"/>
+    <mergeCell ref="H236:I236"/>
+    <mergeCell ref="H237:I237"/>
+    <mergeCell ref="H238:I238"/>
+    <mergeCell ref="H239:I239"/>
+    <mergeCell ref="H240:I240"/>
+    <mergeCell ref="H253:I253"/>
+    <mergeCell ref="H254:I254"/>
+    <mergeCell ref="H255:I255"/>
+    <mergeCell ref="H256:I256"/>
+    <mergeCell ref="H257:I257"/>
+    <mergeCell ref="H258:I258"/>
+    <mergeCell ref="H247:I247"/>
+    <mergeCell ref="H248:I248"/>
+    <mergeCell ref="H249:I249"/>
+    <mergeCell ref="H250:I250"/>
+    <mergeCell ref="H251:I251"/>
+    <mergeCell ref="H252:I252"/>
+    <mergeCell ref="H265:I265"/>
+    <mergeCell ref="H266:I266"/>
+    <mergeCell ref="H267:I267"/>
+    <mergeCell ref="H268:I268"/>
+    <mergeCell ref="H269:I269"/>
+    <mergeCell ref="H270:I270"/>
+    <mergeCell ref="H259:I259"/>
+    <mergeCell ref="H260:I260"/>
+    <mergeCell ref="H261:I261"/>
+    <mergeCell ref="H262:I262"/>
+    <mergeCell ref="H263:I263"/>
+    <mergeCell ref="H264:I264"/>
+    <mergeCell ref="H277:I277"/>
+    <mergeCell ref="H278:I278"/>
+    <mergeCell ref="H279:I279"/>
+    <mergeCell ref="H280:I280"/>
+    <mergeCell ref="H281:I281"/>
+    <mergeCell ref="H282:I282"/>
+    <mergeCell ref="H271:I271"/>
+    <mergeCell ref="H272:I272"/>
+    <mergeCell ref="H273:I273"/>
+    <mergeCell ref="H274:I274"/>
+    <mergeCell ref="H275:I275"/>
+    <mergeCell ref="H276:I276"/>
+    <mergeCell ref="H289:I289"/>
+    <mergeCell ref="H290:I290"/>
+    <mergeCell ref="H291:I291"/>
+    <mergeCell ref="H292:I292"/>
+    <mergeCell ref="H293:I293"/>
+    <mergeCell ref="H294:I294"/>
+    <mergeCell ref="H283:I283"/>
+    <mergeCell ref="H284:I284"/>
+    <mergeCell ref="H285:I285"/>
+    <mergeCell ref="H286:I286"/>
+    <mergeCell ref="H287:I287"/>
+    <mergeCell ref="H288:I288"/>
+    <mergeCell ref="H301:I301"/>
+    <mergeCell ref="H302:I302"/>
+    <mergeCell ref="H303:I303"/>
+    <mergeCell ref="H304:I304"/>
+    <mergeCell ref="H305:I305"/>
+    <mergeCell ref="H306:I306"/>
+    <mergeCell ref="H295:I295"/>
+    <mergeCell ref="H296:I296"/>
+    <mergeCell ref="H297:I297"/>
+    <mergeCell ref="H298:I298"/>
+    <mergeCell ref="H299:I299"/>
+    <mergeCell ref="H300:I300"/>
+    <mergeCell ref="H313:I313"/>
+    <mergeCell ref="H314:I314"/>
+    <mergeCell ref="H315:I315"/>
+    <mergeCell ref="H316:I316"/>
+    <mergeCell ref="H317:I317"/>
+    <mergeCell ref="H318:I318"/>
+    <mergeCell ref="H307:I307"/>
+    <mergeCell ref="H308:I308"/>
+    <mergeCell ref="H309:I309"/>
+    <mergeCell ref="H310:I310"/>
+    <mergeCell ref="H311:I311"/>
+    <mergeCell ref="H312:I312"/>
+    <mergeCell ref="H325:I325"/>
+    <mergeCell ref="H326:I326"/>
+    <mergeCell ref="H327:I327"/>
+    <mergeCell ref="H328:I328"/>
+    <mergeCell ref="H329:I329"/>
+    <mergeCell ref="H330:I330"/>
+    <mergeCell ref="H319:I319"/>
+    <mergeCell ref="H320:I320"/>
+    <mergeCell ref="H321:I321"/>
+    <mergeCell ref="H322:I322"/>
+    <mergeCell ref="H323:I323"/>
+    <mergeCell ref="H324:I324"/>
+    <mergeCell ref="H337:I337"/>
+    <mergeCell ref="H338:I338"/>
+    <mergeCell ref="H339:I339"/>
+    <mergeCell ref="H340:I340"/>
+    <mergeCell ref="H331:I331"/>
+    <mergeCell ref="H332:I332"/>
+    <mergeCell ref="H333:I333"/>
+    <mergeCell ref="H334:I334"/>
+    <mergeCell ref="H335:I335"/>
+    <mergeCell ref="H336:I336"/>
   </mergeCells>
   <conditionalFormatting sqref="A82:A191">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
@@ -15633,7 +15645,7 @@
       <c r="C2" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="50"/>
       <c r="F2" s="50"/>
       <c r="G2" s="50"/>
@@ -18075,7 +18087,7 @@
       <c r="C112" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D112" s="51"/>
+      <c r="D112" s="52"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
       <c r="G112" s="50"/>
@@ -18321,7 +18333,7 @@
       <c r="C122" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D122" s="51"/>
+      <c r="D122" s="52"/>
       <c r="E122" s="50"/>
       <c r="F122" s="50"/>
       <c r="G122" s="50"/>
@@ -18823,7 +18835,7 @@
       <c r="C144" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D144" s="51"/>
+      <c r="D144" s="52"/>
       <c r="E144" s="50"/>
       <c r="F144" s="50"/>
       <c r="G144" s="50"/>
@@ -22179,562 +22191,6 @@
     </row>
   </sheetData>
   <mergeCells count="580">
-    <mergeCell ref="D185:E185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="D186:E186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="D187:E187"/>
-    <mergeCell ref="F187:G187"/>
-    <mergeCell ref="D191:E191"/>
-    <mergeCell ref="F191:G191"/>
-    <mergeCell ref="D192:E192"/>
-    <mergeCell ref="F192:G192"/>
-    <mergeCell ref="D193:E193"/>
-    <mergeCell ref="F193:G193"/>
-    <mergeCell ref="D188:E188"/>
-    <mergeCell ref="F188:G188"/>
-    <mergeCell ref="D189:E189"/>
-    <mergeCell ref="F189:G189"/>
-    <mergeCell ref="D190:E190"/>
-    <mergeCell ref="F190:G190"/>
-    <mergeCell ref="D197:E197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="D198:E198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="D199:E199"/>
-    <mergeCell ref="F199:G199"/>
-    <mergeCell ref="D194:E194"/>
-    <mergeCell ref="F194:G194"/>
-    <mergeCell ref="D195:E195"/>
-    <mergeCell ref="F195:G195"/>
-    <mergeCell ref="D196:E196"/>
-    <mergeCell ref="F196:G196"/>
-    <mergeCell ref="D203:E203"/>
-    <mergeCell ref="F203:G203"/>
-    <mergeCell ref="D204:E204"/>
-    <mergeCell ref="F204:G204"/>
-    <mergeCell ref="D205:E205"/>
-    <mergeCell ref="F205:G205"/>
-    <mergeCell ref="D200:E200"/>
-    <mergeCell ref="F200:G200"/>
-    <mergeCell ref="D201:E201"/>
-    <mergeCell ref="F201:G201"/>
-    <mergeCell ref="D202:E202"/>
-    <mergeCell ref="F202:G202"/>
-    <mergeCell ref="D209:E209"/>
-    <mergeCell ref="F209:G209"/>
-    <mergeCell ref="D210:E210"/>
-    <mergeCell ref="F210:G210"/>
-    <mergeCell ref="D211:E211"/>
-    <mergeCell ref="F211:G211"/>
-    <mergeCell ref="D206:E206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="D207:E207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="D208:E208"/>
-    <mergeCell ref="F208:G208"/>
-    <mergeCell ref="D215:E215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="D216:E216"/>
-    <mergeCell ref="F216:G216"/>
-    <mergeCell ref="D217:E217"/>
-    <mergeCell ref="F217:G217"/>
-    <mergeCell ref="D212:E212"/>
-    <mergeCell ref="F212:G212"/>
-    <mergeCell ref="D213:E213"/>
-    <mergeCell ref="F213:G213"/>
-    <mergeCell ref="D214:E214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="D221:E221"/>
-    <mergeCell ref="F221:G221"/>
-    <mergeCell ref="D222:E222"/>
-    <mergeCell ref="F222:G222"/>
-    <mergeCell ref="D223:E223"/>
-    <mergeCell ref="F223:G223"/>
-    <mergeCell ref="D218:E218"/>
-    <mergeCell ref="F218:G218"/>
-    <mergeCell ref="D219:E219"/>
-    <mergeCell ref="F219:G219"/>
-    <mergeCell ref="D220:E220"/>
-    <mergeCell ref="F220:G220"/>
-    <mergeCell ref="D227:E227"/>
-    <mergeCell ref="F227:G227"/>
-    <mergeCell ref="D228:E228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="D229:E229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="D224:E224"/>
-    <mergeCell ref="F224:G224"/>
-    <mergeCell ref="D225:E225"/>
-    <mergeCell ref="F225:G225"/>
-    <mergeCell ref="D226:E226"/>
-    <mergeCell ref="F226:G226"/>
-    <mergeCell ref="D233:E233"/>
-    <mergeCell ref="F233:G233"/>
-    <mergeCell ref="D234:E234"/>
-    <mergeCell ref="F234:G234"/>
-    <mergeCell ref="D235:E235"/>
-    <mergeCell ref="F235:G235"/>
-    <mergeCell ref="D230:E230"/>
-    <mergeCell ref="F230:G230"/>
-    <mergeCell ref="D231:E231"/>
-    <mergeCell ref="F231:G231"/>
-    <mergeCell ref="D232:E232"/>
-    <mergeCell ref="F232:G232"/>
-    <mergeCell ref="D239:E239"/>
-    <mergeCell ref="F239:G239"/>
-    <mergeCell ref="D240:E240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="D241:E241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="D236:E236"/>
-    <mergeCell ref="F236:G236"/>
-    <mergeCell ref="D237:E237"/>
-    <mergeCell ref="F237:G237"/>
-    <mergeCell ref="D238:E238"/>
-    <mergeCell ref="F238:G238"/>
-    <mergeCell ref="D245:E245"/>
-    <mergeCell ref="F245:G245"/>
-    <mergeCell ref="D246:E246"/>
-    <mergeCell ref="F246:G246"/>
-    <mergeCell ref="D247:E247"/>
-    <mergeCell ref="F247:G247"/>
-    <mergeCell ref="D242:E242"/>
-    <mergeCell ref="F242:G242"/>
-    <mergeCell ref="D243:E243"/>
-    <mergeCell ref="F243:G243"/>
-    <mergeCell ref="D244:E244"/>
-    <mergeCell ref="F244:G244"/>
-    <mergeCell ref="D251:E251"/>
-    <mergeCell ref="F251:G251"/>
-    <mergeCell ref="D252:E252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="D253:E253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="D248:E248"/>
-    <mergeCell ref="F248:G248"/>
-    <mergeCell ref="D249:E249"/>
-    <mergeCell ref="F249:G249"/>
-    <mergeCell ref="D250:E250"/>
-    <mergeCell ref="F250:G250"/>
-    <mergeCell ref="D257:E257"/>
-    <mergeCell ref="F257:G257"/>
-    <mergeCell ref="D258:E258"/>
-    <mergeCell ref="F258:G258"/>
-    <mergeCell ref="D259:E259"/>
-    <mergeCell ref="F259:G259"/>
-    <mergeCell ref="D254:E254"/>
-    <mergeCell ref="F254:G254"/>
-    <mergeCell ref="D255:E255"/>
-    <mergeCell ref="F255:G255"/>
-    <mergeCell ref="D256:E256"/>
-    <mergeCell ref="F256:G256"/>
-    <mergeCell ref="D263:E263"/>
-    <mergeCell ref="F263:G263"/>
-    <mergeCell ref="D264:E264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="D265:E265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="D260:E260"/>
-    <mergeCell ref="F260:G260"/>
-    <mergeCell ref="D261:E261"/>
-    <mergeCell ref="F261:G261"/>
-    <mergeCell ref="D262:E262"/>
-    <mergeCell ref="F262:G262"/>
-    <mergeCell ref="D269:E269"/>
-    <mergeCell ref="F269:G269"/>
-    <mergeCell ref="D270:E270"/>
-    <mergeCell ref="F270:G270"/>
-    <mergeCell ref="D271:E271"/>
-    <mergeCell ref="F271:G271"/>
-    <mergeCell ref="D266:E266"/>
-    <mergeCell ref="F266:G266"/>
-    <mergeCell ref="D267:E267"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="D268:E268"/>
-    <mergeCell ref="F268:G268"/>
-    <mergeCell ref="D275:E275"/>
-    <mergeCell ref="F275:G275"/>
-    <mergeCell ref="D276:E276"/>
-    <mergeCell ref="F276:G276"/>
-    <mergeCell ref="D277:E277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="D272:E272"/>
-    <mergeCell ref="F272:G272"/>
-    <mergeCell ref="D273:E273"/>
-    <mergeCell ref="F273:G273"/>
-    <mergeCell ref="D274:E274"/>
-    <mergeCell ref="F274:G274"/>
-    <mergeCell ref="D281:E281"/>
-    <mergeCell ref="F281:G281"/>
-    <mergeCell ref="D282:E282"/>
-    <mergeCell ref="F282:G282"/>
-    <mergeCell ref="D283:E283"/>
-    <mergeCell ref="F283:G283"/>
-    <mergeCell ref="D278:E278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="D279:E279"/>
-    <mergeCell ref="F279:G279"/>
-    <mergeCell ref="D280:E280"/>
-    <mergeCell ref="F280:G280"/>
-    <mergeCell ref="D288:E288"/>
-    <mergeCell ref="F288:G288"/>
-    <mergeCell ref="D289:E289"/>
-    <mergeCell ref="F289:G289"/>
-    <mergeCell ref="D284:E284"/>
-    <mergeCell ref="F284:G284"/>
-    <mergeCell ref="D285:E285"/>
-    <mergeCell ref="F285:G285"/>
-    <mergeCell ref="D286:E286"/>
-    <mergeCell ref="F286:G286"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="D110:E110"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="D111:E111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="D112:E112"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="D113:E113"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="D114:E114"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="D115:E115"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="D116:E116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="D117:E117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="D118:E118"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="D119:E119"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="D120:E120"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="D121:E121"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="D123:E123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="D124:E124"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="D126:E126"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="D127:E127"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="D128:E128"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="D129:E129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="D135:E135"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="D136:E136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="D137:E137"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="D138:E138"/>
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="D139:E139"/>
-    <mergeCell ref="F139:G139"/>
-    <mergeCell ref="D140:E140"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="D141:E141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="D142:E142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="D143:E143"/>
-    <mergeCell ref="F143:G143"/>
-    <mergeCell ref="D144:E144"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="D145:E145"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="D146:E146"/>
-    <mergeCell ref="F146:G146"/>
-    <mergeCell ref="D147:E147"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="D148:E148"/>
-    <mergeCell ref="F148:G148"/>
-    <mergeCell ref="D149:E149"/>
-    <mergeCell ref="F149:G149"/>
-    <mergeCell ref="D150:E150"/>
-    <mergeCell ref="F150:G150"/>
-    <mergeCell ref="D151:E151"/>
-    <mergeCell ref="F151:G151"/>
-    <mergeCell ref="D152:E152"/>
-    <mergeCell ref="F152:G152"/>
-    <mergeCell ref="D153:E153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="D154:E154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="D155:E155"/>
-    <mergeCell ref="F155:G155"/>
-    <mergeCell ref="D156:E156"/>
-    <mergeCell ref="F156:G156"/>
-    <mergeCell ref="D157:E157"/>
-    <mergeCell ref="F157:G157"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="F158:G158"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="F159:G159"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="F160:G160"/>
-    <mergeCell ref="D161:E161"/>
-    <mergeCell ref="F161:G161"/>
-    <mergeCell ref="D162:E162"/>
-    <mergeCell ref="F162:G162"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="F163:G163"/>
-    <mergeCell ref="D164:E164"/>
-    <mergeCell ref="F164:G164"/>
-    <mergeCell ref="D165:E165"/>
-    <mergeCell ref="F165:G165"/>
-    <mergeCell ref="D166:E166"/>
-    <mergeCell ref="F166:G166"/>
-    <mergeCell ref="D167:E167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="D168:E168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="D169:E169"/>
-    <mergeCell ref="F169:G169"/>
-    <mergeCell ref="D170:E170"/>
-    <mergeCell ref="F170:G170"/>
-    <mergeCell ref="D171:E171"/>
-    <mergeCell ref="F171:G171"/>
-    <mergeCell ref="D172:E172"/>
-    <mergeCell ref="F172:G172"/>
-    <mergeCell ref="D173:E173"/>
-    <mergeCell ref="F173:G173"/>
-    <mergeCell ref="D174:E174"/>
-    <mergeCell ref="F174:G174"/>
-    <mergeCell ref="D175:E175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="D176:E176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="D177:E177"/>
-    <mergeCell ref="F177:G177"/>
-    <mergeCell ref="D178:E178"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="F179:G179"/>
     <mergeCell ref="D295:E295"/>
     <mergeCell ref="F295:G295"/>
     <mergeCell ref="D180:E180"/>
@@ -22759,6 +22215,562 @@
     <mergeCell ref="F292:G292"/>
     <mergeCell ref="D287:E287"/>
     <mergeCell ref="F287:G287"/>
+    <mergeCell ref="D175:E175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="D176:E176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="D177:E177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="D178:E178"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="D179:E179"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="D170:E170"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="D171:E171"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="D172:E172"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="D173:E173"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="D174:E174"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="D165:E165"/>
+    <mergeCell ref="F165:G165"/>
+    <mergeCell ref="D166:E166"/>
+    <mergeCell ref="F166:G166"/>
+    <mergeCell ref="D167:E167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="D168:E168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="D169:E169"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="D164:E164"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="D155:E155"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="D150:E150"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="D151:E151"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="D152:E152"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="D153:E153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="D154:E154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="D145:E145"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="D146:E146"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="D147:E147"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="D148:E148"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="D149:E149"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="D140:E140"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="D141:E141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="D142:E142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="D143:E143"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="D136:E136"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="D137:E137"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="D138:E138"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="D139:E139"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="D126:E126"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="D127:E127"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="D128:E128"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="D129:E129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="D123:E123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="D124:E124"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="D115:E115"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="D116:E116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="D117:E117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="D118:E118"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="D119:E119"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="D110:E110"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="D111:E111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="D112:E112"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="D113:E113"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="D114:E114"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D288:E288"/>
+    <mergeCell ref="F288:G288"/>
+    <mergeCell ref="D289:E289"/>
+    <mergeCell ref="F289:G289"/>
+    <mergeCell ref="D284:E284"/>
+    <mergeCell ref="F284:G284"/>
+    <mergeCell ref="D285:E285"/>
+    <mergeCell ref="F285:G285"/>
+    <mergeCell ref="D286:E286"/>
+    <mergeCell ref="F286:G286"/>
+    <mergeCell ref="D281:E281"/>
+    <mergeCell ref="F281:G281"/>
+    <mergeCell ref="D282:E282"/>
+    <mergeCell ref="F282:G282"/>
+    <mergeCell ref="D283:E283"/>
+    <mergeCell ref="F283:G283"/>
+    <mergeCell ref="D278:E278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="D279:E279"/>
+    <mergeCell ref="F279:G279"/>
+    <mergeCell ref="D280:E280"/>
+    <mergeCell ref="F280:G280"/>
+    <mergeCell ref="D275:E275"/>
+    <mergeCell ref="F275:G275"/>
+    <mergeCell ref="D276:E276"/>
+    <mergeCell ref="F276:G276"/>
+    <mergeCell ref="D277:E277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="D272:E272"/>
+    <mergeCell ref="F272:G272"/>
+    <mergeCell ref="D273:E273"/>
+    <mergeCell ref="F273:G273"/>
+    <mergeCell ref="D274:E274"/>
+    <mergeCell ref="F274:G274"/>
+    <mergeCell ref="D269:E269"/>
+    <mergeCell ref="F269:G269"/>
+    <mergeCell ref="D270:E270"/>
+    <mergeCell ref="F270:G270"/>
+    <mergeCell ref="D271:E271"/>
+    <mergeCell ref="F271:G271"/>
+    <mergeCell ref="D266:E266"/>
+    <mergeCell ref="F266:G266"/>
+    <mergeCell ref="D267:E267"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="D268:E268"/>
+    <mergeCell ref="F268:G268"/>
+    <mergeCell ref="D263:E263"/>
+    <mergeCell ref="F263:G263"/>
+    <mergeCell ref="D264:E264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="D265:E265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="D260:E260"/>
+    <mergeCell ref="F260:G260"/>
+    <mergeCell ref="D261:E261"/>
+    <mergeCell ref="F261:G261"/>
+    <mergeCell ref="D262:E262"/>
+    <mergeCell ref="F262:G262"/>
+    <mergeCell ref="D257:E257"/>
+    <mergeCell ref="F257:G257"/>
+    <mergeCell ref="D258:E258"/>
+    <mergeCell ref="F258:G258"/>
+    <mergeCell ref="D259:E259"/>
+    <mergeCell ref="F259:G259"/>
+    <mergeCell ref="D254:E254"/>
+    <mergeCell ref="F254:G254"/>
+    <mergeCell ref="D255:E255"/>
+    <mergeCell ref="F255:G255"/>
+    <mergeCell ref="D256:E256"/>
+    <mergeCell ref="F256:G256"/>
+    <mergeCell ref="D251:E251"/>
+    <mergeCell ref="F251:G251"/>
+    <mergeCell ref="D252:E252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="D253:E253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="D248:E248"/>
+    <mergeCell ref="F248:G248"/>
+    <mergeCell ref="D249:E249"/>
+    <mergeCell ref="F249:G249"/>
+    <mergeCell ref="D250:E250"/>
+    <mergeCell ref="F250:G250"/>
+    <mergeCell ref="D245:E245"/>
+    <mergeCell ref="F245:G245"/>
+    <mergeCell ref="D246:E246"/>
+    <mergeCell ref="F246:G246"/>
+    <mergeCell ref="D247:E247"/>
+    <mergeCell ref="F247:G247"/>
+    <mergeCell ref="D242:E242"/>
+    <mergeCell ref="F242:G242"/>
+    <mergeCell ref="D243:E243"/>
+    <mergeCell ref="F243:G243"/>
+    <mergeCell ref="D244:E244"/>
+    <mergeCell ref="F244:G244"/>
+    <mergeCell ref="D239:E239"/>
+    <mergeCell ref="F239:G239"/>
+    <mergeCell ref="D240:E240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="D241:E241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="D236:E236"/>
+    <mergeCell ref="F236:G236"/>
+    <mergeCell ref="D237:E237"/>
+    <mergeCell ref="F237:G237"/>
+    <mergeCell ref="D238:E238"/>
+    <mergeCell ref="F238:G238"/>
+    <mergeCell ref="D233:E233"/>
+    <mergeCell ref="F233:G233"/>
+    <mergeCell ref="D234:E234"/>
+    <mergeCell ref="F234:G234"/>
+    <mergeCell ref="D235:E235"/>
+    <mergeCell ref="F235:G235"/>
+    <mergeCell ref="D230:E230"/>
+    <mergeCell ref="F230:G230"/>
+    <mergeCell ref="D231:E231"/>
+    <mergeCell ref="F231:G231"/>
+    <mergeCell ref="D232:E232"/>
+    <mergeCell ref="F232:G232"/>
+    <mergeCell ref="D227:E227"/>
+    <mergeCell ref="F227:G227"/>
+    <mergeCell ref="D228:E228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="D229:E229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="D224:E224"/>
+    <mergeCell ref="F224:G224"/>
+    <mergeCell ref="D225:E225"/>
+    <mergeCell ref="F225:G225"/>
+    <mergeCell ref="D226:E226"/>
+    <mergeCell ref="F226:G226"/>
+    <mergeCell ref="D221:E221"/>
+    <mergeCell ref="F221:G221"/>
+    <mergeCell ref="D222:E222"/>
+    <mergeCell ref="F222:G222"/>
+    <mergeCell ref="D223:E223"/>
+    <mergeCell ref="F223:G223"/>
+    <mergeCell ref="D218:E218"/>
+    <mergeCell ref="F218:G218"/>
+    <mergeCell ref="D219:E219"/>
+    <mergeCell ref="F219:G219"/>
+    <mergeCell ref="D220:E220"/>
+    <mergeCell ref="F220:G220"/>
+    <mergeCell ref="D215:E215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="D216:E216"/>
+    <mergeCell ref="F216:G216"/>
+    <mergeCell ref="D217:E217"/>
+    <mergeCell ref="F217:G217"/>
+    <mergeCell ref="D212:E212"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="D213:E213"/>
+    <mergeCell ref="F213:G213"/>
+    <mergeCell ref="D214:E214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="D209:E209"/>
+    <mergeCell ref="F209:G209"/>
+    <mergeCell ref="D210:E210"/>
+    <mergeCell ref="F210:G210"/>
+    <mergeCell ref="D211:E211"/>
+    <mergeCell ref="F211:G211"/>
+    <mergeCell ref="D206:E206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="D207:E207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="D208:E208"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="D203:E203"/>
+    <mergeCell ref="F203:G203"/>
+    <mergeCell ref="D204:E204"/>
+    <mergeCell ref="F204:G204"/>
+    <mergeCell ref="D205:E205"/>
+    <mergeCell ref="F205:G205"/>
+    <mergeCell ref="D200:E200"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="D202:E202"/>
+    <mergeCell ref="F202:G202"/>
+    <mergeCell ref="D198:E198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="D199:E199"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="D194:E194"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="D195:E195"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="D196:E196"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="D193:E193"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="D188:E188"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="D189:E189"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="D190:E190"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="D197:E197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="D185:E185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="D186:E186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="D187:E187"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="D191:E191"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="D192:E192"/>
+    <mergeCell ref="F192:G192"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35973,6 +35985,12 @@
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1151</v>
       </c>
       <c r="N30" t="s">
         <v>56</v>
@@ -46000,6 +46018,12 @@
       <c r="A17" t="s">
         <v>1008</v>
       </c>
+      <c r="I17" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J17" s="8">
+        <v>20</v>
+      </c>
       <c r="N17" t="s">
         <v>228</v>
       </c>
@@ -46010,6 +46034,12 @@
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>247</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J18" s="8">
+        <v>200</v>
       </c>
       <c r="N18" t="s">
         <v>228</v>
@@ -51342,18 +51372,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -51375,14 +51405,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C62074-BDFC-4D1E-BF7A-C2FEEAF5CCCC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -51396,4 +51418,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GeneralizationRules100K.xlsx
+++ b/GeneralizationRules100K.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Intersourcing\Malyasia\Gen_Carto\Gen_Carto\ArcgisPro_GenCarto\GenCarto_Dev\share_dev_100K_main\Dev_Gencarto_100K\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426197CE-261C-41B3-852A-0BA3C24A84A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F7091D-614F-4DA2-BFC9-0939C3FDE15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="16" r:id="rId1"/>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9537" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9546" uniqueCount="1159">
   <si>
     <t>Please read the following instructions carefully</t>
   </si>
@@ -4240,6 +4240,27 @@
   </si>
   <si>
     <t>NAM = '' Or NAM = ' ' Or NAM IS NULL</t>
+  </si>
+  <si>
+    <t>Transport_Terrace_road_class_field</t>
+  </si>
+  <si>
+    <t>Transport_Terrace_road_class_type</t>
+  </si>
+  <si>
+    <t>Transport_delete_dangle_sql</t>
+  </si>
+  <si>
+    <t>Transport_ThinRoad_Carto_High_sql</t>
+  </si>
+  <si>
+    <t>RANK &gt;= 3 AND RANK IS NOT NULL</t>
+  </si>
+  <si>
+    <t>Transport_ThinRoad_Carto_low_sql</t>
+  </si>
+  <si>
+    <t>RANK &lt; 3 AND RANK IS NOT NULL</t>
   </si>
 </sst>
 </file>
@@ -4471,7 +4492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4565,11 +4586,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8357,7 +8379,7 @@
       <c r="G77" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="H77" s="52"/>
+      <c r="H77" s="51"/>
       <c r="I77" s="50"/>
       <c r="J77" s="25" t="s">
         <v>697</v>
@@ -8396,7 +8418,7 @@
       <c r="G78" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="H78" s="52"/>
+      <c r="H78" s="51"/>
       <c r="I78" s="50"/>
       <c r="J78" s="25"/>
       <c r="K78" s="25" t="s">
@@ -11801,7 +11823,7 @@
       <c r="E204" s="25"/>
       <c r="F204" s="25"/>
       <c r="G204" s="29"/>
-      <c r="H204" s="52"/>
+      <c r="H204" s="51"/>
       <c r="I204" s="50"/>
       <c r="J204" s="25"/>
       <c r="K204" s="37"/>
@@ -11832,8 +11854,8 @@
       <c r="G205" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="H205" s="51"/>
-      <c r="I205" s="51"/>
+      <c r="H205" s="52"/>
+      <c r="I205" s="52"/>
       <c r="J205" s="41" t="s">
         <v>697</v>
       </c>
@@ -15283,114 +15305,148 @@
     </row>
   </sheetData>
   <mergeCells count="264">
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="H97:I97"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="H99:I99"/>
-    <mergeCell ref="H100:I100"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="H111:I111"/>
-    <mergeCell ref="H112:I112"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H119:I119"/>
-    <mergeCell ref="H120:I120"/>
-    <mergeCell ref="H121:I121"/>
-    <mergeCell ref="H122:I122"/>
-    <mergeCell ref="H123:I123"/>
-    <mergeCell ref="H124:I124"/>
-    <mergeCell ref="H113:I113"/>
-    <mergeCell ref="H114:I114"/>
-    <mergeCell ref="H115:I115"/>
-    <mergeCell ref="H116:I116"/>
-    <mergeCell ref="H117:I117"/>
-    <mergeCell ref="H118:I118"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="H132:I132"/>
-    <mergeCell ref="H133:I133"/>
-    <mergeCell ref="H134:I134"/>
-    <mergeCell ref="H135:I135"/>
-    <mergeCell ref="H136:I136"/>
-    <mergeCell ref="H125:I125"/>
-    <mergeCell ref="H126:I126"/>
-    <mergeCell ref="H127:I127"/>
-    <mergeCell ref="H128:I128"/>
-    <mergeCell ref="H129:I129"/>
-    <mergeCell ref="H130:I130"/>
-    <mergeCell ref="H143:I143"/>
-    <mergeCell ref="H144:I144"/>
-    <mergeCell ref="H145:I145"/>
-    <mergeCell ref="H146:I146"/>
-    <mergeCell ref="H147:I147"/>
-    <mergeCell ref="H148:I148"/>
-    <mergeCell ref="H137:I137"/>
-    <mergeCell ref="H138:I138"/>
-    <mergeCell ref="H139:I139"/>
-    <mergeCell ref="H140:I140"/>
-    <mergeCell ref="H141:I141"/>
-    <mergeCell ref="H142:I142"/>
-    <mergeCell ref="H155:I155"/>
-    <mergeCell ref="H156:I156"/>
-    <mergeCell ref="H157:I157"/>
-    <mergeCell ref="H158:I158"/>
-    <mergeCell ref="H159:I159"/>
-    <mergeCell ref="H160:I160"/>
-    <mergeCell ref="H149:I149"/>
-    <mergeCell ref="H150:I150"/>
-    <mergeCell ref="H151:I151"/>
-    <mergeCell ref="H152:I152"/>
-    <mergeCell ref="H153:I153"/>
-    <mergeCell ref="H154:I154"/>
-    <mergeCell ref="H167:I167"/>
-    <mergeCell ref="H168:I168"/>
-    <mergeCell ref="H169:I169"/>
-    <mergeCell ref="H170:I170"/>
-    <mergeCell ref="H171:I171"/>
-    <mergeCell ref="H172:I172"/>
-    <mergeCell ref="H161:I161"/>
-    <mergeCell ref="H162:I162"/>
-    <mergeCell ref="H163:I163"/>
-    <mergeCell ref="H164:I164"/>
-    <mergeCell ref="H165:I165"/>
-    <mergeCell ref="H166:I166"/>
-    <mergeCell ref="H179:I179"/>
-    <mergeCell ref="H180:I180"/>
-    <mergeCell ref="H181:I181"/>
-    <mergeCell ref="H182:I182"/>
-    <mergeCell ref="H183:I183"/>
-    <mergeCell ref="H184:I184"/>
-    <mergeCell ref="H173:I173"/>
-    <mergeCell ref="H174:I174"/>
-    <mergeCell ref="H175:I175"/>
-    <mergeCell ref="H176:I176"/>
-    <mergeCell ref="H177:I177"/>
-    <mergeCell ref="H178:I178"/>
+    <mergeCell ref="H337:I337"/>
+    <mergeCell ref="H338:I338"/>
+    <mergeCell ref="H339:I339"/>
+    <mergeCell ref="H340:I340"/>
+    <mergeCell ref="H331:I331"/>
+    <mergeCell ref="H332:I332"/>
+    <mergeCell ref="H333:I333"/>
+    <mergeCell ref="H334:I334"/>
+    <mergeCell ref="H335:I335"/>
+    <mergeCell ref="H336:I336"/>
+    <mergeCell ref="H325:I325"/>
+    <mergeCell ref="H326:I326"/>
+    <mergeCell ref="H327:I327"/>
+    <mergeCell ref="H328:I328"/>
+    <mergeCell ref="H329:I329"/>
+    <mergeCell ref="H330:I330"/>
+    <mergeCell ref="H319:I319"/>
+    <mergeCell ref="H320:I320"/>
+    <mergeCell ref="H321:I321"/>
+    <mergeCell ref="H322:I322"/>
+    <mergeCell ref="H323:I323"/>
+    <mergeCell ref="H324:I324"/>
+    <mergeCell ref="H313:I313"/>
+    <mergeCell ref="H314:I314"/>
+    <mergeCell ref="H315:I315"/>
+    <mergeCell ref="H316:I316"/>
+    <mergeCell ref="H317:I317"/>
+    <mergeCell ref="H318:I318"/>
+    <mergeCell ref="H307:I307"/>
+    <mergeCell ref="H308:I308"/>
+    <mergeCell ref="H309:I309"/>
+    <mergeCell ref="H310:I310"/>
+    <mergeCell ref="H311:I311"/>
+    <mergeCell ref="H312:I312"/>
+    <mergeCell ref="H301:I301"/>
+    <mergeCell ref="H302:I302"/>
+    <mergeCell ref="H303:I303"/>
+    <mergeCell ref="H304:I304"/>
+    <mergeCell ref="H305:I305"/>
+    <mergeCell ref="H306:I306"/>
+    <mergeCell ref="H295:I295"/>
+    <mergeCell ref="H296:I296"/>
+    <mergeCell ref="H297:I297"/>
+    <mergeCell ref="H298:I298"/>
+    <mergeCell ref="H299:I299"/>
+    <mergeCell ref="H300:I300"/>
+    <mergeCell ref="H289:I289"/>
+    <mergeCell ref="H290:I290"/>
+    <mergeCell ref="H291:I291"/>
+    <mergeCell ref="H292:I292"/>
+    <mergeCell ref="H293:I293"/>
+    <mergeCell ref="H294:I294"/>
+    <mergeCell ref="H283:I283"/>
+    <mergeCell ref="H284:I284"/>
+    <mergeCell ref="H285:I285"/>
+    <mergeCell ref="H286:I286"/>
+    <mergeCell ref="H287:I287"/>
+    <mergeCell ref="H288:I288"/>
+    <mergeCell ref="H277:I277"/>
+    <mergeCell ref="H278:I278"/>
+    <mergeCell ref="H279:I279"/>
+    <mergeCell ref="H280:I280"/>
+    <mergeCell ref="H281:I281"/>
+    <mergeCell ref="H282:I282"/>
+    <mergeCell ref="H271:I271"/>
+    <mergeCell ref="H272:I272"/>
+    <mergeCell ref="H273:I273"/>
+    <mergeCell ref="H274:I274"/>
+    <mergeCell ref="H275:I275"/>
+    <mergeCell ref="H276:I276"/>
+    <mergeCell ref="H265:I265"/>
+    <mergeCell ref="H266:I266"/>
+    <mergeCell ref="H267:I267"/>
+    <mergeCell ref="H268:I268"/>
+    <mergeCell ref="H269:I269"/>
+    <mergeCell ref="H270:I270"/>
+    <mergeCell ref="H259:I259"/>
+    <mergeCell ref="H260:I260"/>
+    <mergeCell ref="H261:I261"/>
+    <mergeCell ref="H262:I262"/>
+    <mergeCell ref="H263:I263"/>
+    <mergeCell ref="H264:I264"/>
+    <mergeCell ref="H253:I253"/>
+    <mergeCell ref="H254:I254"/>
+    <mergeCell ref="H255:I255"/>
+    <mergeCell ref="H256:I256"/>
+    <mergeCell ref="H257:I257"/>
+    <mergeCell ref="H258:I258"/>
+    <mergeCell ref="H247:I247"/>
+    <mergeCell ref="H248:I248"/>
+    <mergeCell ref="H249:I249"/>
+    <mergeCell ref="H250:I250"/>
+    <mergeCell ref="H251:I251"/>
+    <mergeCell ref="H252:I252"/>
+    <mergeCell ref="H241:I241"/>
+    <mergeCell ref="H242:I242"/>
+    <mergeCell ref="H243:I243"/>
+    <mergeCell ref="H244:I244"/>
+    <mergeCell ref="H245:I245"/>
+    <mergeCell ref="H246:I246"/>
+    <mergeCell ref="H235:I235"/>
+    <mergeCell ref="H236:I236"/>
+    <mergeCell ref="H237:I237"/>
+    <mergeCell ref="H238:I238"/>
+    <mergeCell ref="H239:I239"/>
+    <mergeCell ref="H240:I240"/>
+    <mergeCell ref="H229:I229"/>
+    <mergeCell ref="H230:I230"/>
+    <mergeCell ref="H231:I231"/>
+    <mergeCell ref="H232:I232"/>
+    <mergeCell ref="H233:I233"/>
+    <mergeCell ref="H234:I234"/>
+    <mergeCell ref="H223:I223"/>
+    <mergeCell ref="H224:I224"/>
+    <mergeCell ref="H225:I225"/>
+    <mergeCell ref="H226:I226"/>
+    <mergeCell ref="H227:I227"/>
+    <mergeCell ref="H228:I228"/>
+    <mergeCell ref="H217:I217"/>
+    <mergeCell ref="H218:I218"/>
+    <mergeCell ref="H219:I219"/>
+    <mergeCell ref="H220:I220"/>
+    <mergeCell ref="H221:I221"/>
+    <mergeCell ref="H222:I222"/>
+    <mergeCell ref="H211:I211"/>
+    <mergeCell ref="H212:I212"/>
+    <mergeCell ref="H213:I213"/>
+    <mergeCell ref="H214:I214"/>
+    <mergeCell ref="H215:I215"/>
+    <mergeCell ref="H216:I216"/>
+    <mergeCell ref="H205:I205"/>
+    <mergeCell ref="H206:I206"/>
+    <mergeCell ref="H207:I207"/>
+    <mergeCell ref="H208:I208"/>
+    <mergeCell ref="H209:I209"/>
+    <mergeCell ref="H210:I210"/>
+    <mergeCell ref="H199:I199"/>
+    <mergeCell ref="H200:I200"/>
+    <mergeCell ref="H201:I201"/>
+    <mergeCell ref="H202:I202"/>
+    <mergeCell ref="H203:I203"/>
+    <mergeCell ref="H204:I204"/>
     <mergeCell ref="H193:I193"/>
     <mergeCell ref="H194:I194"/>
     <mergeCell ref="H195:I195"/>
@@ -15405,148 +15461,114 @@
     <mergeCell ref="H188:I188"/>
     <mergeCell ref="H189:I189"/>
     <mergeCell ref="H190:I190"/>
-    <mergeCell ref="H205:I205"/>
-    <mergeCell ref="H206:I206"/>
-    <mergeCell ref="H207:I207"/>
-    <mergeCell ref="H208:I208"/>
-    <mergeCell ref="H209:I209"/>
-    <mergeCell ref="H210:I210"/>
-    <mergeCell ref="H199:I199"/>
-    <mergeCell ref="H200:I200"/>
-    <mergeCell ref="H201:I201"/>
-    <mergeCell ref="H202:I202"/>
-    <mergeCell ref="H203:I203"/>
-    <mergeCell ref="H204:I204"/>
-    <mergeCell ref="H217:I217"/>
-    <mergeCell ref="H218:I218"/>
-    <mergeCell ref="H219:I219"/>
-    <mergeCell ref="H220:I220"/>
-    <mergeCell ref="H221:I221"/>
-    <mergeCell ref="H222:I222"/>
-    <mergeCell ref="H211:I211"/>
-    <mergeCell ref="H212:I212"/>
-    <mergeCell ref="H213:I213"/>
-    <mergeCell ref="H214:I214"/>
-    <mergeCell ref="H215:I215"/>
-    <mergeCell ref="H216:I216"/>
-    <mergeCell ref="H229:I229"/>
-    <mergeCell ref="H230:I230"/>
-    <mergeCell ref="H231:I231"/>
-    <mergeCell ref="H232:I232"/>
-    <mergeCell ref="H233:I233"/>
-    <mergeCell ref="H234:I234"/>
-    <mergeCell ref="H223:I223"/>
-    <mergeCell ref="H224:I224"/>
-    <mergeCell ref="H225:I225"/>
-    <mergeCell ref="H226:I226"/>
-    <mergeCell ref="H227:I227"/>
-    <mergeCell ref="H228:I228"/>
-    <mergeCell ref="H241:I241"/>
-    <mergeCell ref="H242:I242"/>
-    <mergeCell ref="H243:I243"/>
-    <mergeCell ref="H244:I244"/>
-    <mergeCell ref="H245:I245"/>
-    <mergeCell ref="H246:I246"/>
-    <mergeCell ref="H235:I235"/>
-    <mergeCell ref="H236:I236"/>
-    <mergeCell ref="H237:I237"/>
-    <mergeCell ref="H238:I238"/>
-    <mergeCell ref="H239:I239"/>
-    <mergeCell ref="H240:I240"/>
-    <mergeCell ref="H253:I253"/>
-    <mergeCell ref="H254:I254"/>
-    <mergeCell ref="H255:I255"/>
-    <mergeCell ref="H256:I256"/>
-    <mergeCell ref="H257:I257"/>
-    <mergeCell ref="H258:I258"/>
-    <mergeCell ref="H247:I247"/>
-    <mergeCell ref="H248:I248"/>
-    <mergeCell ref="H249:I249"/>
-    <mergeCell ref="H250:I250"/>
-    <mergeCell ref="H251:I251"/>
-    <mergeCell ref="H252:I252"/>
-    <mergeCell ref="H265:I265"/>
-    <mergeCell ref="H266:I266"/>
-    <mergeCell ref="H267:I267"/>
-    <mergeCell ref="H268:I268"/>
-    <mergeCell ref="H269:I269"/>
-    <mergeCell ref="H270:I270"/>
-    <mergeCell ref="H259:I259"/>
-    <mergeCell ref="H260:I260"/>
-    <mergeCell ref="H261:I261"/>
-    <mergeCell ref="H262:I262"/>
-    <mergeCell ref="H263:I263"/>
-    <mergeCell ref="H264:I264"/>
-    <mergeCell ref="H277:I277"/>
-    <mergeCell ref="H278:I278"/>
-    <mergeCell ref="H279:I279"/>
-    <mergeCell ref="H280:I280"/>
-    <mergeCell ref="H281:I281"/>
-    <mergeCell ref="H282:I282"/>
-    <mergeCell ref="H271:I271"/>
-    <mergeCell ref="H272:I272"/>
-    <mergeCell ref="H273:I273"/>
-    <mergeCell ref="H274:I274"/>
-    <mergeCell ref="H275:I275"/>
-    <mergeCell ref="H276:I276"/>
-    <mergeCell ref="H289:I289"/>
-    <mergeCell ref="H290:I290"/>
-    <mergeCell ref="H291:I291"/>
-    <mergeCell ref="H292:I292"/>
-    <mergeCell ref="H293:I293"/>
-    <mergeCell ref="H294:I294"/>
-    <mergeCell ref="H283:I283"/>
-    <mergeCell ref="H284:I284"/>
-    <mergeCell ref="H285:I285"/>
-    <mergeCell ref="H286:I286"/>
-    <mergeCell ref="H287:I287"/>
-    <mergeCell ref="H288:I288"/>
-    <mergeCell ref="H301:I301"/>
-    <mergeCell ref="H302:I302"/>
-    <mergeCell ref="H303:I303"/>
-    <mergeCell ref="H304:I304"/>
-    <mergeCell ref="H305:I305"/>
-    <mergeCell ref="H306:I306"/>
-    <mergeCell ref="H295:I295"/>
-    <mergeCell ref="H296:I296"/>
-    <mergeCell ref="H297:I297"/>
-    <mergeCell ref="H298:I298"/>
-    <mergeCell ref="H299:I299"/>
-    <mergeCell ref="H300:I300"/>
-    <mergeCell ref="H313:I313"/>
-    <mergeCell ref="H314:I314"/>
-    <mergeCell ref="H315:I315"/>
-    <mergeCell ref="H316:I316"/>
-    <mergeCell ref="H317:I317"/>
-    <mergeCell ref="H318:I318"/>
-    <mergeCell ref="H307:I307"/>
-    <mergeCell ref="H308:I308"/>
-    <mergeCell ref="H309:I309"/>
-    <mergeCell ref="H310:I310"/>
-    <mergeCell ref="H311:I311"/>
-    <mergeCell ref="H312:I312"/>
-    <mergeCell ref="H325:I325"/>
-    <mergeCell ref="H326:I326"/>
-    <mergeCell ref="H327:I327"/>
-    <mergeCell ref="H328:I328"/>
-    <mergeCell ref="H329:I329"/>
-    <mergeCell ref="H330:I330"/>
-    <mergeCell ref="H319:I319"/>
-    <mergeCell ref="H320:I320"/>
-    <mergeCell ref="H321:I321"/>
-    <mergeCell ref="H322:I322"/>
-    <mergeCell ref="H323:I323"/>
-    <mergeCell ref="H324:I324"/>
-    <mergeCell ref="H337:I337"/>
-    <mergeCell ref="H338:I338"/>
-    <mergeCell ref="H339:I339"/>
-    <mergeCell ref="H340:I340"/>
-    <mergeCell ref="H331:I331"/>
-    <mergeCell ref="H332:I332"/>
-    <mergeCell ref="H333:I333"/>
-    <mergeCell ref="H334:I334"/>
-    <mergeCell ref="H335:I335"/>
-    <mergeCell ref="H336:I336"/>
+    <mergeCell ref="H179:I179"/>
+    <mergeCell ref="H180:I180"/>
+    <mergeCell ref="H181:I181"/>
+    <mergeCell ref="H182:I182"/>
+    <mergeCell ref="H183:I183"/>
+    <mergeCell ref="H184:I184"/>
+    <mergeCell ref="H173:I173"/>
+    <mergeCell ref="H174:I174"/>
+    <mergeCell ref="H175:I175"/>
+    <mergeCell ref="H176:I176"/>
+    <mergeCell ref="H177:I177"/>
+    <mergeCell ref="H178:I178"/>
+    <mergeCell ref="H167:I167"/>
+    <mergeCell ref="H168:I168"/>
+    <mergeCell ref="H169:I169"/>
+    <mergeCell ref="H170:I170"/>
+    <mergeCell ref="H171:I171"/>
+    <mergeCell ref="H172:I172"/>
+    <mergeCell ref="H161:I161"/>
+    <mergeCell ref="H162:I162"/>
+    <mergeCell ref="H163:I163"/>
+    <mergeCell ref="H164:I164"/>
+    <mergeCell ref="H165:I165"/>
+    <mergeCell ref="H166:I166"/>
+    <mergeCell ref="H155:I155"/>
+    <mergeCell ref="H156:I156"/>
+    <mergeCell ref="H157:I157"/>
+    <mergeCell ref="H158:I158"/>
+    <mergeCell ref="H159:I159"/>
+    <mergeCell ref="H160:I160"/>
+    <mergeCell ref="H149:I149"/>
+    <mergeCell ref="H150:I150"/>
+    <mergeCell ref="H151:I151"/>
+    <mergeCell ref="H152:I152"/>
+    <mergeCell ref="H153:I153"/>
+    <mergeCell ref="H154:I154"/>
+    <mergeCell ref="H143:I143"/>
+    <mergeCell ref="H144:I144"/>
+    <mergeCell ref="H145:I145"/>
+    <mergeCell ref="H146:I146"/>
+    <mergeCell ref="H147:I147"/>
+    <mergeCell ref="H148:I148"/>
+    <mergeCell ref="H137:I137"/>
+    <mergeCell ref="H138:I138"/>
+    <mergeCell ref="H139:I139"/>
+    <mergeCell ref="H140:I140"/>
+    <mergeCell ref="H141:I141"/>
+    <mergeCell ref="H142:I142"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="H132:I132"/>
+    <mergeCell ref="H133:I133"/>
+    <mergeCell ref="H134:I134"/>
+    <mergeCell ref="H135:I135"/>
+    <mergeCell ref="H136:I136"/>
+    <mergeCell ref="H125:I125"/>
+    <mergeCell ref="H126:I126"/>
+    <mergeCell ref="H127:I127"/>
+    <mergeCell ref="H128:I128"/>
+    <mergeCell ref="H129:I129"/>
+    <mergeCell ref="H130:I130"/>
+    <mergeCell ref="H119:I119"/>
+    <mergeCell ref="H120:I120"/>
+    <mergeCell ref="H121:I121"/>
+    <mergeCell ref="H122:I122"/>
+    <mergeCell ref="H123:I123"/>
+    <mergeCell ref="H124:I124"/>
+    <mergeCell ref="H113:I113"/>
+    <mergeCell ref="H114:I114"/>
+    <mergeCell ref="H115:I115"/>
+    <mergeCell ref="H116:I116"/>
+    <mergeCell ref="H117:I117"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="H110:I110"/>
+    <mergeCell ref="H111:I111"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H82:I82"/>
   </mergeCells>
   <conditionalFormatting sqref="A82:A191">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
@@ -15645,7 +15667,7 @@
       <c r="C2" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D2" s="52"/>
+      <c r="D2" s="51"/>
       <c r="E2" s="50"/>
       <c r="F2" s="50"/>
       <c r="G2" s="50"/>
@@ -18087,7 +18109,7 @@
       <c r="C112" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D112" s="52"/>
+      <c r="D112" s="51"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
       <c r="G112" s="50"/>
@@ -18333,7 +18355,7 @@
       <c r="C122" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D122" s="52"/>
+      <c r="D122" s="51"/>
       <c r="E122" s="50"/>
       <c r="F122" s="50"/>
       <c r="G122" s="50"/>
@@ -18835,7 +18857,7 @@
       <c r="C144" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="D144" s="52"/>
+      <c r="D144" s="51"/>
       <c r="E144" s="50"/>
       <c r="F144" s="50"/>
       <c r="G144" s="50"/>
@@ -22191,6 +22213,562 @@
     </row>
   </sheetData>
   <mergeCells count="580">
+    <mergeCell ref="D185:E185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="D186:E186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="D187:E187"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="D191:E191"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="D192:E192"/>
+    <mergeCell ref="F192:G192"/>
+    <mergeCell ref="D193:E193"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="D188:E188"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="D189:E189"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="D190:E190"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="D197:E197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="D198:E198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="D199:E199"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="D194:E194"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="D195:E195"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="D196:E196"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="D203:E203"/>
+    <mergeCell ref="F203:G203"/>
+    <mergeCell ref="D204:E204"/>
+    <mergeCell ref="F204:G204"/>
+    <mergeCell ref="D205:E205"/>
+    <mergeCell ref="F205:G205"/>
+    <mergeCell ref="D200:E200"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="D201:E201"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="D202:E202"/>
+    <mergeCell ref="F202:G202"/>
+    <mergeCell ref="D209:E209"/>
+    <mergeCell ref="F209:G209"/>
+    <mergeCell ref="D210:E210"/>
+    <mergeCell ref="F210:G210"/>
+    <mergeCell ref="D211:E211"/>
+    <mergeCell ref="F211:G211"/>
+    <mergeCell ref="D206:E206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="D207:E207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="D208:E208"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="D215:E215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="D216:E216"/>
+    <mergeCell ref="F216:G216"/>
+    <mergeCell ref="D217:E217"/>
+    <mergeCell ref="F217:G217"/>
+    <mergeCell ref="D212:E212"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="D213:E213"/>
+    <mergeCell ref="F213:G213"/>
+    <mergeCell ref="D214:E214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="D221:E221"/>
+    <mergeCell ref="F221:G221"/>
+    <mergeCell ref="D222:E222"/>
+    <mergeCell ref="F222:G222"/>
+    <mergeCell ref="D223:E223"/>
+    <mergeCell ref="F223:G223"/>
+    <mergeCell ref="D218:E218"/>
+    <mergeCell ref="F218:G218"/>
+    <mergeCell ref="D219:E219"/>
+    <mergeCell ref="F219:G219"/>
+    <mergeCell ref="D220:E220"/>
+    <mergeCell ref="F220:G220"/>
+    <mergeCell ref="D227:E227"/>
+    <mergeCell ref="F227:G227"/>
+    <mergeCell ref="D228:E228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="D229:E229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="D224:E224"/>
+    <mergeCell ref="F224:G224"/>
+    <mergeCell ref="D225:E225"/>
+    <mergeCell ref="F225:G225"/>
+    <mergeCell ref="D226:E226"/>
+    <mergeCell ref="F226:G226"/>
+    <mergeCell ref="D233:E233"/>
+    <mergeCell ref="F233:G233"/>
+    <mergeCell ref="D234:E234"/>
+    <mergeCell ref="F234:G234"/>
+    <mergeCell ref="D235:E235"/>
+    <mergeCell ref="F235:G235"/>
+    <mergeCell ref="D230:E230"/>
+    <mergeCell ref="F230:G230"/>
+    <mergeCell ref="D231:E231"/>
+    <mergeCell ref="F231:G231"/>
+    <mergeCell ref="D232:E232"/>
+    <mergeCell ref="F232:G232"/>
+    <mergeCell ref="D239:E239"/>
+    <mergeCell ref="F239:G239"/>
+    <mergeCell ref="D240:E240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="D241:E241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="D236:E236"/>
+    <mergeCell ref="F236:G236"/>
+    <mergeCell ref="D237:E237"/>
+    <mergeCell ref="F237:G237"/>
+    <mergeCell ref="D238:E238"/>
+    <mergeCell ref="F238:G238"/>
+    <mergeCell ref="D245:E245"/>
+    <mergeCell ref="F245:G245"/>
+    <mergeCell ref="D246:E246"/>
+    <mergeCell ref="F246:G246"/>
+    <mergeCell ref="D247:E247"/>
+    <mergeCell ref="F247:G247"/>
+    <mergeCell ref="D242:E242"/>
+    <mergeCell ref="F242:G242"/>
+    <mergeCell ref="D243:E243"/>
+    <mergeCell ref="F243:G243"/>
+    <mergeCell ref="D244:E244"/>
+    <mergeCell ref="F244:G244"/>
+    <mergeCell ref="D251:E251"/>
+    <mergeCell ref="F251:G251"/>
+    <mergeCell ref="D252:E252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="D253:E253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="D248:E248"/>
+    <mergeCell ref="F248:G248"/>
+    <mergeCell ref="D249:E249"/>
+    <mergeCell ref="F249:G249"/>
+    <mergeCell ref="D250:E250"/>
+    <mergeCell ref="F250:G250"/>
+    <mergeCell ref="D257:E257"/>
+    <mergeCell ref="F257:G257"/>
+    <mergeCell ref="D258:E258"/>
+    <mergeCell ref="F258:G258"/>
+    <mergeCell ref="D259:E259"/>
+    <mergeCell ref="F259:G259"/>
+    <mergeCell ref="D254:E254"/>
+    <mergeCell ref="F254:G254"/>
+    <mergeCell ref="D255:E255"/>
+    <mergeCell ref="F255:G255"/>
+    <mergeCell ref="D256:E256"/>
+    <mergeCell ref="F256:G256"/>
+    <mergeCell ref="D263:E263"/>
+    <mergeCell ref="F263:G263"/>
+    <mergeCell ref="D264:E264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="D265:E265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="D260:E260"/>
+    <mergeCell ref="F260:G260"/>
+    <mergeCell ref="D261:E261"/>
+    <mergeCell ref="F261:G261"/>
+    <mergeCell ref="D262:E262"/>
+    <mergeCell ref="F262:G262"/>
+    <mergeCell ref="D269:E269"/>
+    <mergeCell ref="F269:G269"/>
+    <mergeCell ref="D270:E270"/>
+    <mergeCell ref="F270:G270"/>
+    <mergeCell ref="D271:E271"/>
+    <mergeCell ref="F271:G271"/>
+    <mergeCell ref="D266:E266"/>
+    <mergeCell ref="F266:G266"/>
+    <mergeCell ref="D267:E267"/>
+    <mergeCell ref="F267:G267"/>
+    <mergeCell ref="D268:E268"/>
+    <mergeCell ref="F268:G268"/>
+    <mergeCell ref="D275:E275"/>
+    <mergeCell ref="F275:G275"/>
+    <mergeCell ref="D276:E276"/>
+    <mergeCell ref="F276:G276"/>
+    <mergeCell ref="D277:E277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="D272:E272"/>
+    <mergeCell ref="F272:G272"/>
+    <mergeCell ref="D273:E273"/>
+    <mergeCell ref="F273:G273"/>
+    <mergeCell ref="D274:E274"/>
+    <mergeCell ref="F274:G274"/>
+    <mergeCell ref="D281:E281"/>
+    <mergeCell ref="F281:G281"/>
+    <mergeCell ref="D282:E282"/>
+    <mergeCell ref="F282:G282"/>
+    <mergeCell ref="D283:E283"/>
+    <mergeCell ref="F283:G283"/>
+    <mergeCell ref="D278:E278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="D279:E279"/>
+    <mergeCell ref="F279:G279"/>
+    <mergeCell ref="D280:E280"/>
+    <mergeCell ref="F280:G280"/>
+    <mergeCell ref="D288:E288"/>
+    <mergeCell ref="F288:G288"/>
+    <mergeCell ref="D289:E289"/>
+    <mergeCell ref="F289:G289"/>
+    <mergeCell ref="D284:E284"/>
+    <mergeCell ref="F284:G284"/>
+    <mergeCell ref="D285:E285"/>
+    <mergeCell ref="F285:G285"/>
+    <mergeCell ref="D286:E286"/>
+    <mergeCell ref="F286:G286"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="D110:E110"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="D111:E111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="D112:E112"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="D113:E113"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="D114:E114"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="D115:E115"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="D116:E116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="D117:E117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="D118:E118"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="D119:E119"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="D123:E123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="D124:E124"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="D126:E126"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="D127:E127"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="D128:E128"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="D129:E129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="D132:E132"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="D136:E136"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="D137:E137"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="D138:E138"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="D139:E139"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="D140:E140"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="D141:E141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="D142:E142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="D143:E143"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="D144:E144"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="D145:E145"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="D146:E146"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="D147:E147"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="D148:E148"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="D149:E149"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="D150:E150"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="D151:E151"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="D152:E152"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="D153:E153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="D154:E154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="D155:E155"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="D164:E164"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="D165:E165"/>
+    <mergeCell ref="F165:G165"/>
+    <mergeCell ref="D166:E166"/>
+    <mergeCell ref="F166:G166"/>
+    <mergeCell ref="D167:E167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="D168:E168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="D169:E169"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="D170:E170"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="D171:E171"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="D172:E172"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="D173:E173"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="D174:E174"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="D175:E175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="D176:E176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="D177:E177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="D178:E178"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="D179:E179"/>
+    <mergeCell ref="F179:G179"/>
     <mergeCell ref="D295:E295"/>
     <mergeCell ref="F295:G295"/>
     <mergeCell ref="D180:E180"/>
@@ -22215,562 +22793,6 @@
     <mergeCell ref="F292:G292"/>
     <mergeCell ref="D287:E287"/>
     <mergeCell ref="F287:G287"/>
-    <mergeCell ref="D175:E175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="D176:E176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="D177:E177"/>
-    <mergeCell ref="F177:G177"/>
-    <mergeCell ref="D178:E178"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="F179:G179"/>
-    <mergeCell ref="D170:E170"/>
-    <mergeCell ref="F170:G170"/>
-    <mergeCell ref="D171:E171"/>
-    <mergeCell ref="F171:G171"/>
-    <mergeCell ref="D172:E172"/>
-    <mergeCell ref="F172:G172"/>
-    <mergeCell ref="D173:E173"/>
-    <mergeCell ref="F173:G173"/>
-    <mergeCell ref="D174:E174"/>
-    <mergeCell ref="F174:G174"/>
-    <mergeCell ref="D165:E165"/>
-    <mergeCell ref="F165:G165"/>
-    <mergeCell ref="D166:E166"/>
-    <mergeCell ref="F166:G166"/>
-    <mergeCell ref="D167:E167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="D168:E168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="D169:E169"/>
-    <mergeCell ref="F169:G169"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="F160:G160"/>
-    <mergeCell ref="D161:E161"/>
-    <mergeCell ref="F161:G161"/>
-    <mergeCell ref="D162:E162"/>
-    <mergeCell ref="F162:G162"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="F163:G163"/>
-    <mergeCell ref="D164:E164"/>
-    <mergeCell ref="F164:G164"/>
-    <mergeCell ref="D155:E155"/>
-    <mergeCell ref="F155:G155"/>
-    <mergeCell ref="D156:E156"/>
-    <mergeCell ref="F156:G156"/>
-    <mergeCell ref="D157:E157"/>
-    <mergeCell ref="F157:G157"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="F158:G158"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="F159:G159"/>
-    <mergeCell ref="D150:E150"/>
-    <mergeCell ref="F150:G150"/>
-    <mergeCell ref="D151:E151"/>
-    <mergeCell ref="F151:G151"/>
-    <mergeCell ref="D152:E152"/>
-    <mergeCell ref="F152:G152"/>
-    <mergeCell ref="D153:E153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="D154:E154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="D145:E145"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="D146:E146"/>
-    <mergeCell ref="F146:G146"/>
-    <mergeCell ref="D147:E147"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="D148:E148"/>
-    <mergeCell ref="F148:G148"/>
-    <mergeCell ref="D149:E149"/>
-    <mergeCell ref="F149:G149"/>
-    <mergeCell ref="D140:E140"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="D141:E141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="D142:E142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="D143:E143"/>
-    <mergeCell ref="F143:G143"/>
-    <mergeCell ref="D144:E144"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="D135:E135"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="D136:E136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="D137:E137"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="D138:E138"/>
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="D139:E139"/>
-    <mergeCell ref="F139:G139"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="D132:E132"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="D133:E133"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="D134:E134"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="D126:E126"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="D127:E127"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="D128:E128"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="D129:E129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="D120:E120"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="D121:E121"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="D123:E123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="D124:E124"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="D115:E115"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="D116:E116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="D117:E117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="D118:E118"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="D119:E119"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="D110:E110"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="D111:E111"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="D112:E112"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="D113:E113"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="D114:E114"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D288:E288"/>
-    <mergeCell ref="F288:G288"/>
-    <mergeCell ref="D289:E289"/>
-    <mergeCell ref="F289:G289"/>
-    <mergeCell ref="D284:E284"/>
-    <mergeCell ref="F284:G284"/>
-    <mergeCell ref="D285:E285"/>
-    <mergeCell ref="F285:G285"/>
-    <mergeCell ref="D286:E286"/>
-    <mergeCell ref="F286:G286"/>
-    <mergeCell ref="D281:E281"/>
-    <mergeCell ref="F281:G281"/>
-    <mergeCell ref="D282:E282"/>
-    <mergeCell ref="F282:G282"/>
-    <mergeCell ref="D283:E283"/>
-    <mergeCell ref="F283:G283"/>
-    <mergeCell ref="D278:E278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="D279:E279"/>
-    <mergeCell ref="F279:G279"/>
-    <mergeCell ref="D280:E280"/>
-    <mergeCell ref="F280:G280"/>
-    <mergeCell ref="D275:E275"/>
-    <mergeCell ref="F275:G275"/>
-    <mergeCell ref="D276:E276"/>
-    <mergeCell ref="F276:G276"/>
-    <mergeCell ref="D277:E277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="D272:E272"/>
-    <mergeCell ref="F272:G272"/>
-    <mergeCell ref="D273:E273"/>
-    <mergeCell ref="F273:G273"/>
-    <mergeCell ref="D274:E274"/>
-    <mergeCell ref="F274:G274"/>
-    <mergeCell ref="D269:E269"/>
-    <mergeCell ref="F269:G269"/>
-    <mergeCell ref="D270:E270"/>
-    <mergeCell ref="F270:G270"/>
-    <mergeCell ref="D271:E271"/>
-    <mergeCell ref="F271:G271"/>
-    <mergeCell ref="D266:E266"/>
-    <mergeCell ref="F266:G266"/>
-    <mergeCell ref="D267:E267"/>
-    <mergeCell ref="F267:G267"/>
-    <mergeCell ref="D268:E268"/>
-    <mergeCell ref="F268:G268"/>
-    <mergeCell ref="D263:E263"/>
-    <mergeCell ref="F263:G263"/>
-    <mergeCell ref="D264:E264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="D265:E265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="D260:E260"/>
-    <mergeCell ref="F260:G260"/>
-    <mergeCell ref="D261:E261"/>
-    <mergeCell ref="F261:G261"/>
-    <mergeCell ref="D262:E262"/>
-    <mergeCell ref="F262:G262"/>
-    <mergeCell ref="D257:E257"/>
-    <mergeCell ref="F257:G257"/>
-    <mergeCell ref="D258:E258"/>
-    <mergeCell ref="F258:G258"/>
-    <mergeCell ref="D259:E259"/>
-    <mergeCell ref="F259:G259"/>
-    <mergeCell ref="D254:E254"/>
-    <mergeCell ref="F254:G254"/>
-    <mergeCell ref="D255:E255"/>
-    <mergeCell ref="F255:G255"/>
-    <mergeCell ref="D256:E256"/>
-    <mergeCell ref="F256:G256"/>
-    <mergeCell ref="D251:E251"/>
-    <mergeCell ref="F251:G251"/>
-    <mergeCell ref="D252:E252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="D253:E253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="D248:E248"/>
-    <mergeCell ref="F248:G248"/>
-    <mergeCell ref="D249:E249"/>
-    <mergeCell ref="F249:G249"/>
-    <mergeCell ref="D250:E250"/>
-    <mergeCell ref="F250:G250"/>
-    <mergeCell ref="D245:E245"/>
-    <mergeCell ref="F245:G245"/>
-    <mergeCell ref="D246:E246"/>
-    <mergeCell ref="F246:G246"/>
-    <mergeCell ref="D247:E247"/>
-    <mergeCell ref="F247:G247"/>
-    <mergeCell ref="D242:E242"/>
-    <mergeCell ref="F242:G242"/>
-    <mergeCell ref="D243:E243"/>
-    <mergeCell ref="F243:G243"/>
-    <mergeCell ref="D244:E244"/>
-    <mergeCell ref="F244:G244"/>
-    <mergeCell ref="D239:E239"/>
-    <mergeCell ref="F239:G239"/>
-    <mergeCell ref="D240:E240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="D241:E241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="D236:E236"/>
-    <mergeCell ref="F236:G236"/>
-    <mergeCell ref="D237:E237"/>
-    <mergeCell ref="F237:G237"/>
-    <mergeCell ref="D238:E238"/>
-    <mergeCell ref="F238:G238"/>
-    <mergeCell ref="D233:E233"/>
-    <mergeCell ref="F233:G233"/>
-    <mergeCell ref="D234:E234"/>
-    <mergeCell ref="F234:G234"/>
-    <mergeCell ref="D235:E235"/>
-    <mergeCell ref="F235:G235"/>
-    <mergeCell ref="D230:E230"/>
-    <mergeCell ref="F230:G230"/>
-    <mergeCell ref="D231:E231"/>
-    <mergeCell ref="F231:G231"/>
-    <mergeCell ref="D232:E232"/>
-    <mergeCell ref="F232:G232"/>
-    <mergeCell ref="D227:E227"/>
-    <mergeCell ref="F227:G227"/>
-    <mergeCell ref="D228:E228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="D229:E229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="D224:E224"/>
-    <mergeCell ref="F224:G224"/>
-    <mergeCell ref="D225:E225"/>
-    <mergeCell ref="F225:G225"/>
-    <mergeCell ref="D226:E226"/>
-    <mergeCell ref="F226:G226"/>
-    <mergeCell ref="D221:E221"/>
-    <mergeCell ref="F221:G221"/>
-    <mergeCell ref="D222:E222"/>
-    <mergeCell ref="F222:G222"/>
-    <mergeCell ref="D223:E223"/>
-    <mergeCell ref="F223:G223"/>
-    <mergeCell ref="D218:E218"/>
-    <mergeCell ref="F218:G218"/>
-    <mergeCell ref="D219:E219"/>
-    <mergeCell ref="F219:G219"/>
-    <mergeCell ref="D220:E220"/>
-    <mergeCell ref="F220:G220"/>
-    <mergeCell ref="D215:E215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="D216:E216"/>
-    <mergeCell ref="F216:G216"/>
-    <mergeCell ref="D217:E217"/>
-    <mergeCell ref="F217:G217"/>
-    <mergeCell ref="D212:E212"/>
-    <mergeCell ref="F212:G212"/>
-    <mergeCell ref="D213:E213"/>
-    <mergeCell ref="F213:G213"/>
-    <mergeCell ref="D214:E214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="D209:E209"/>
-    <mergeCell ref="F209:G209"/>
-    <mergeCell ref="D210:E210"/>
-    <mergeCell ref="F210:G210"/>
-    <mergeCell ref="D211:E211"/>
-    <mergeCell ref="F211:G211"/>
-    <mergeCell ref="D206:E206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="D207:E207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="D208:E208"/>
-    <mergeCell ref="F208:G208"/>
-    <mergeCell ref="D203:E203"/>
-    <mergeCell ref="F203:G203"/>
-    <mergeCell ref="D204:E204"/>
-    <mergeCell ref="F204:G204"/>
-    <mergeCell ref="D205:E205"/>
-    <mergeCell ref="F205:G205"/>
-    <mergeCell ref="D200:E200"/>
-    <mergeCell ref="F200:G200"/>
-    <mergeCell ref="D201:E201"/>
-    <mergeCell ref="F201:G201"/>
-    <mergeCell ref="D202:E202"/>
-    <mergeCell ref="F202:G202"/>
-    <mergeCell ref="D198:E198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="D199:E199"/>
-    <mergeCell ref="F199:G199"/>
-    <mergeCell ref="D194:E194"/>
-    <mergeCell ref="F194:G194"/>
-    <mergeCell ref="D195:E195"/>
-    <mergeCell ref="F195:G195"/>
-    <mergeCell ref="D196:E196"/>
-    <mergeCell ref="F196:G196"/>
-    <mergeCell ref="D193:E193"/>
-    <mergeCell ref="F193:G193"/>
-    <mergeCell ref="D188:E188"/>
-    <mergeCell ref="F188:G188"/>
-    <mergeCell ref="D189:E189"/>
-    <mergeCell ref="F189:G189"/>
-    <mergeCell ref="D190:E190"/>
-    <mergeCell ref="F190:G190"/>
-    <mergeCell ref="D197:E197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="D185:E185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="D186:E186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="D187:E187"/>
-    <mergeCell ref="F187:G187"/>
-    <mergeCell ref="D191:E191"/>
-    <mergeCell ref="F191:G191"/>
-    <mergeCell ref="D192:E192"/>
-    <mergeCell ref="F192:G192"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -37758,6 +37780,12 @@
         <v>226</v>
       </c>
       <c r="D11" s="7"/>
+      <c r="J11" s="54" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>1062</v>
+      </c>
       <c r="O11" t="s">
         <v>228</v>
       </c>
@@ -37773,6 +37801,12 @@
         <v>226</v>
       </c>
       <c r="D12" s="7"/>
+      <c r="J12" s="54" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K12" s="8">
+        <v>4</v>
+      </c>
       <c r="O12" t="s">
         <v>228</v>
       </c>
@@ -37788,6 +37822,12 @@
         <v>226</v>
       </c>
       <c r="D13" s="7"/>
+      <c r="J13" s="54" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>1151</v>
+      </c>
       <c r="O13" t="s">
         <v>228</v>
       </c>
@@ -37803,6 +37843,12 @@
         <v>226</v>
       </c>
       <c r="D14" s="7"/>
+      <c r="J14" s="54" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>1156</v>
+      </c>
       <c r="O14" t="s">
         <v>228</v>
       </c>
@@ -37818,6 +37864,12 @@
         <v>226</v>
       </c>
       <c r="D15" s="7"/>
+      <c r="J15" s="54" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>1158</v>
+      </c>
       <c r="O15" t="s">
         <v>228</v>
       </c>
@@ -51372,18 +51424,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -51405,6 +51457,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C62074-BDFC-4D1E-BF7A-C2FEEAF5CCCC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -51418,12 +51478,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBDDA5EB-1D06-4B1E-900F-CD5E292E684A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>